--- a/evolution/new_word_count_df.xlsx
+++ b/evolution/new_word_count_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D660"/>
+  <dimension ref="A1:C660"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,11 +444,6 @@
           <t>new_word_count</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Decade</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -460,11 +455,6 @@
       <c r="C2" t="n">
         <v>49</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -476,11 +466,6 @@
       <c r="C3" t="n">
         <v>41</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -492,11 +477,6 @@
       <c r="C4" t="n">
         <v>62</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -508,11 +488,6 @@
       <c r="C5" t="n">
         <v>50</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -524,11 +499,6 @@
       <c r="C6" t="n">
         <v>41</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -540,11 +510,6 @@
       <c r="C7" t="n">
         <v>66</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -556,11 +521,6 @@
       <c r="C8" t="n">
         <v>85</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -572,11 +532,6 @@
       <c r="C9" t="n">
         <v>25</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -588,11 +543,6 @@
       <c r="C10" t="n">
         <v>2</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -604,11 +554,6 @@
       <c r="C11" t="n">
         <v>58</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -620,11 +565,6 @@
       <c r="C12" t="n">
         <v>161</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -636,11 +576,6 @@
       <c r="C13" t="n">
         <v>75</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -652,11 +587,6 @@
       <c r="C14" t="n">
         <v>36</v>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -668,11 +598,6 @@
       <c r="C15" t="n">
         <v>74</v>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -684,11 +609,6 @@
       <c r="C16" t="n">
         <v>47</v>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -700,11 +620,6 @@
       <c r="C17" t="n">
         <v>50</v>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -716,11 +631,6 @@
       <c r="C18" t="n">
         <v>17</v>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -732,11 +642,6 @@
       <c r="C19" t="n">
         <v>28</v>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -748,11 +653,6 @@
       <c r="C20" t="n">
         <v>39</v>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -764,11 +664,6 @@
       <c r="C21" t="n">
         <v>39</v>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -780,11 +675,6 @@
       <c r="C22" t="n">
         <v>87</v>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -796,11 +686,6 @@
       <c r="C23" t="n">
         <v>35</v>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -812,11 +697,6 @@
       <c r="C24" t="n">
         <v>96</v>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -828,11 +708,6 @@
       <c r="C25" t="n">
         <v>49</v>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -844,11 +719,6 @@
       <c r="C26" t="n">
         <v>67</v>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -860,11 +730,6 @@
       <c r="C27" t="n">
         <v>13</v>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -876,11 +741,6 @@
       <c r="C28" t="n">
         <v>125</v>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -892,11 +752,6 @@
       <c r="C29" t="n">
         <v>134</v>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -908,11 +763,6 @@
       <c r="C30" t="n">
         <v>139</v>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -924,11 +774,6 @@
       <c r="C31" t="n">
         <v>204</v>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -940,11 +785,6 @@
       <c r="C32" t="n">
         <v>159</v>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -956,11 +796,6 @@
       <c r="C33" t="n">
         <v>131</v>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -972,11 +807,6 @@
       <c r="C34" t="n">
         <v>215</v>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -988,11 +818,6 @@
       <c r="C35" t="n">
         <v>102</v>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1004,11 +829,6 @@
       <c r="C36" t="n">
         <v>145</v>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1020,11 +840,6 @@
       <c r="C37" t="n">
         <v>191</v>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1036,11 +851,6 @@
       <c r="C38" t="n">
         <v>165</v>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1052,11 +862,6 @@
       <c r="C39" t="n">
         <v>170</v>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1068,11 +873,6 @@
       <c r="C40" t="n">
         <v>218</v>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1084,11 +884,6 @@
       <c r="C41" t="n">
         <v>171</v>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1100,11 +895,6 @@
       <c r="C42" t="n">
         <v>194</v>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1116,11 +906,6 @@
       <c r="C43" t="n">
         <v>382</v>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1132,11 +917,6 @@
       <c r="C44" t="n">
         <v>91</v>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1148,11 +928,6 @@
       <c r="C45" t="n">
         <v>49</v>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1164,11 +939,6 @@
       <c r="C46" t="n">
         <v>180</v>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1180,11 +950,6 @@
       <c r="C47" t="n">
         <v>47</v>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1196,11 +961,6 @@
       <c r="C48" t="n">
         <v>26</v>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1212,11 +972,6 @@
       <c r="C49" t="n">
         <v>18</v>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1228,11 +983,6 @@
       <c r="C50" t="n">
         <v>132</v>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1244,11 +994,6 @@
       <c r="C51" t="n">
         <v>47</v>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1260,11 +1005,6 @@
       <c r="C52" t="n">
         <v>111</v>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1276,11 +1016,6 @@
       <c r="C53" t="n">
         <v>76</v>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1292,11 +1027,6 @@
       <c r="C54" t="n">
         <v>31</v>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1308,11 +1038,6 @@
       <c r="C55" t="n">
         <v>99</v>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1324,11 +1049,6 @@
       <c r="C56" t="n">
         <v>68</v>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1340,11 +1060,6 @@
       <c r="C57" t="n">
         <v>36</v>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1356,11 +1071,6 @@
       <c r="C58" t="n">
         <v>123</v>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1372,11 +1082,6 @@
       <c r="C59" t="n">
         <v>130</v>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1388,11 +1093,6 @@
       <c r="C60" t="n">
         <v>192</v>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1404,11 +1104,6 @@
       <c r="C61" t="n">
         <v>123</v>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1420,11 +1115,6 @@
       <c r="C62" t="n">
         <v>152</v>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1436,11 +1126,6 @@
       <c r="C63" t="n">
         <v>217</v>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1452,11 +1137,6 @@
       <c r="C64" t="n">
         <v>167</v>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1468,11 +1148,6 @@
       <c r="C65" t="n">
         <v>190</v>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1484,11 +1159,6 @@
       <c r="C66" t="n">
         <v>175</v>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1500,11 +1170,6 @@
       <c r="C67" t="n">
         <v>234</v>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1516,11 +1181,6 @@
       <c r="C68" t="n">
         <v>550</v>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1532,11 +1192,6 @@
       <c r="C69" t="n">
         <v>419</v>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1548,11 +1203,6 @@
       <c r="C70" t="n">
         <v>420</v>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1564,11 +1214,6 @@
       <c r="C71" t="n">
         <v>636</v>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1580,11 +1225,6 @@
       <c r="C72" t="n">
         <v>702</v>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1596,11 +1236,6 @@
       <c r="C73" t="n">
         <v>5</v>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1612,11 +1247,6 @@
       <c r="C74" t="n">
         <v>6</v>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1628,11 +1258,6 @@
       <c r="C75" t="n">
         <v>147</v>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -1644,11 +1269,6 @@
       <c r="C76" t="n">
         <v>44</v>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1660,11 +1280,6 @@
       <c r="C77" t="n">
         <v>117</v>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1676,11 +1291,6 @@
       <c r="C78" t="n">
         <v>148</v>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -1692,11 +1302,6 @@
       <c r="C79" t="n">
         <v>40</v>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -1708,11 +1313,6 @@
       <c r="C80" t="n">
         <v>36</v>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -1724,11 +1324,6 @@
       <c r="C81" t="n">
         <v>72</v>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -1740,11 +1335,6 @@
       <c r="C82" t="n">
         <v>53</v>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -1756,11 +1346,6 @@
       <c r="C83" t="n">
         <v>25</v>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -1772,11 +1357,6 @@
       <c r="C84" t="n">
         <v>47</v>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -1788,11 +1368,6 @@
       <c r="C85" t="n">
         <v>71</v>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -1804,11 +1379,6 @@
       <c r="C86" t="n">
         <v>128</v>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -1820,11 +1390,6 @@
       <c r="C87" t="n">
         <v>112</v>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -1836,11 +1401,6 @@
       <c r="C88" t="n">
         <v>61</v>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -1852,11 +1412,6 @@
       <c r="C89" t="n">
         <v>55</v>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -1868,11 +1423,6 @@
       <c r="C90" t="n">
         <v>139</v>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -1884,11 +1434,6 @@
       <c r="C91" t="n">
         <v>115</v>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -1900,11 +1445,6 @@
       <c r="C92" t="n">
         <v>121</v>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -1916,11 +1456,6 @@
       <c r="C93" t="n">
         <v>110</v>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -1932,11 +1467,6 @@
       <c r="C94" t="n">
         <v>97</v>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -1948,11 +1478,6 @@
       <c r="C95" t="n">
         <v>41</v>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -1964,11 +1489,6 @@
       <c r="C96" t="n">
         <v>18</v>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -1980,11 +1500,6 @@
       <c r="C97" t="n">
         <v>74</v>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -1996,11 +1511,6 @@
       <c r="C98" t="n">
         <v>9</v>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -2012,11 +1522,6 @@
       <c r="C99" t="n">
         <v>94</v>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -2028,11 +1533,6 @@
       <c r="C100" t="n">
         <v>125</v>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -2044,11 +1544,6 @@
       <c r="C101" t="n">
         <v>69</v>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -2060,11 +1555,6 @@
       <c r="C102" t="n">
         <v>78</v>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -2076,11 +1566,6 @@
       <c r="C103" t="n">
         <v>209</v>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -2092,11 +1577,6 @@
       <c r="C104" t="n">
         <v>92</v>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -2108,11 +1588,6 @@
       <c r="C105" t="n">
         <v>197</v>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -2124,11 +1599,6 @@
       <c r="C106" t="n">
         <v>81</v>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -2140,11 +1610,6 @@
       <c r="C107" t="n">
         <v>122</v>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -2156,11 +1621,6 @@
       <c r="C108" t="n">
         <v>141</v>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -2172,11 +1632,6 @@
       <c r="C109" t="n">
         <v>82</v>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -2188,11 +1643,6 @@
       <c r="C110" t="n">
         <v>204</v>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -2204,11 +1654,6 @@
       <c r="C111" t="n">
         <v>109</v>
       </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -2220,11 +1665,6 @@
       <c r="C112" t="n">
         <v>171</v>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -2236,11 +1676,6 @@
       <c r="C113" t="n">
         <v>60</v>
       </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -2252,11 +1687,6 @@
       <c r="C114" t="n">
         <v>72</v>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -2268,11 +1698,6 @@
       <c r="C115" t="n">
         <v>151</v>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -2284,11 +1709,6 @@
       <c r="C116" t="n">
         <v>143</v>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -2300,11 +1720,6 @@
       <c r="C117" t="n">
         <v>6</v>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -2316,11 +1731,6 @@
       <c r="C118" t="n">
         <v>54</v>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -2332,11 +1742,6 @@
       <c r="C119" t="n">
         <v>52</v>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -2348,11 +1753,6 @@
       <c r="C120" t="n">
         <v>10</v>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -2364,11 +1764,6 @@
       <c r="C121" t="n">
         <v>52</v>
       </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -2380,11 +1775,6 @@
       <c r="C122" t="n">
         <v>52</v>
       </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -2396,11 +1786,6 @@
       <c r="C123" t="n">
         <v>22</v>
       </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -2412,11 +1797,6 @@
       <c r="C124" t="n">
         <v>92</v>
       </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -2428,11 +1808,6 @@
       <c r="C125" t="n">
         <v>86</v>
       </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -2444,11 +1819,6 @@
       <c r="C126" t="n">
         <v>77</v>
       </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -2460,11 +1830,6 @@
       <c r="C127" t="n">
         <v>70</v>
       </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -2476,11 +1841,6 @@
       <c r="C128" t="n">
         <v>130</v>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -2492,11 +1852,6 @@
       <c r="C129" t="n">
         <v>80</v>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -2508,11 +1863,6 @@
       <c r="C130" t="n">
         <v>113</v>
       </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -2524,11 +1874,6 @@
       <c r="C131" t="n">
         <v>140</v>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -2540,11 +1885,6 @@
       <c r="C132" t="n">
         <v>142</v>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -2556,11 +1896,6 @@
       <c r="C133" t="n">
         <v>86</v>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -2572,11 +1907,6 @@
       <c r="C134" t="n">
         <v>109</v>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -2588,11 +1918,6 @@
       <c r="C135" t="n">
         <v>80</v>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -2604,11 +1929,6 @@
       <c r="C136" t="n">
         <v>62</v>
       </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -2620,11 +1940,6 @@
       <c r="C137" t="n">
         <v>41</v>
       </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -2636,11 +1951,6 @@
       <c r="C138" t="n">
         <v>139</v>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -2652,11 +1962,6 @@
       <c r="C139" t="n">
         <v>147</v>
       </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -2668,11 +1973,6 @@
       <c r="C140" t="n">
         <v>135</v>
       </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -2684,11 +1984,6 @@
       <c r="C141" t="n">
         <v>131</v>
       </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -2700,11 +1995,6 @@
       <c r="C142" t="n">
         <v>81</v>
       </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -2716,11 +2006,6 @@
       <c r="C143" t="n">
         <v>166</v>
       </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -2732,11 +2017,6 @@
       <c r="C144" t="n">
         <v>156</v>
       </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -2748,11 +2028,6 @@
       <c r="C145" t="n">
         <v>155</v>
       </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -2764,11 +2039,6 @@
       <c r="C146" t="n">
         <v>179</v>
       </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -2780,11 +2050,6 @@
       <c r="C147" t="n">
         <v>78</v>
       </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -2796,11 +2061,6 @@
       <c r="C148" t="n">
         <v>176</v>
       </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -2812,11 +2072,6 @@
       <c r="C149" t="n">
         <v>333</v>
       </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -2828,11 +2083,6 @@
       <c r="C150" t="n">
         <v>60</v>
       </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -2844,11 +2094,6 @@
       <c r="C151" t="n">
         <v>101</v>
       </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -2860,11 +2105,6 @@
       <c r="C152" t="n">
         <v>67</v>
       </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -2876,11 +2116,6 @@
       <c r="C153" t="n">
         <v>32</v>
       </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -2892,11 +2127,6 @@
       <c r="C154" t="n">
         <v>26</v>
       </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -2908,11 +2138,6 @@
       <c r="C155" t="n">
         <v>121</v>
       </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -2924,11 +2149,6 @@
       <c r="C156" t="n">
         <v>35</v>
       </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -2940,11 +2160,6 @@
       <c r="C157" t="n">
         <v>28</v>
       </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -2956,11 +2171,6 @@
       <c r="C158" t="n">
         <v>32</v>
       </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -2972,11 +2182,6 @@
       <c r="C159" t="n">
         <v>30</v>
       </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -2988,11 +2193,6 @@
       <c r="C160" t="n">
         <v>106</v>
       </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -3004,11 +2204,6 @@
       <c r="C161" t="n">
         <v>48</v>
       </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -3020,11 +2215,6 @@
       <c r="C162" t="n">
         <v>40</v>
       </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -3036,11 +2226,6 @@
       <c r="C163" t="n">
         <v>86</v>
       </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -3052,11 +2237,6 @@
       <c r="C164" t="n">
         <v>36</v>
       </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -3068,11 +2248,6 @@
       <c r="C165" t="n">
         <v>45</v>
       </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -3084,11 +2259,6 @@
       <c r="C166" t="n">
         <v>184</v>
       </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -3100,11 +2270,6 @@
       <c r="C167" t="n">
         <v>44</v>
       </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -3116,11 +2281,6 @@
       <c r="C168" t="n">
         <v>117</v>
       </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -3132,11 +2292,6 @@
       <c r="C169" t="n">
         <v>208</v>
       </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -3148,11 +2303,6 @@
       <c r="C170" t="n">
         <v>58</v>
       </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -3164,11 +2314,6 @@
       <c r="C171" t="n">
         <v>305</v>
       </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -3180,11 +2325,6 @@
       <c r="C172" t="n">
         <v>295</v>
       </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -3196,11 +2336,6 @@
       <c r="C173" t="n">
         <v>102</v>
       </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -3212,11 +2347,6 @@
       <c r="C174" t="n">
         <v>326</v>
       </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -3228,11 +2358,6 @@
       <c r="C175" t="n">
         <v>286</v>
       </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -3244,11 +2369,6 @@
       <c r="C176" t="n">
         <v>191</v>
       </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -3260,11 +2380,6 @@
       <c r="C177" t="n">
         <v>295</v>
       </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -3276,11 +2391,6 @@
       <c r="C178" t="n">
         <v>353</v>
       </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -3292,11 +2402,6 @@
       <c r="C179" t="n">
         <v>349</v>
       </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -3308,11 +2413,6 @@
       <c r="C180" t="n">
         <v>518</v>
       </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -3324,11 +2424,6 @@
       <c r="C181" t="n">
         <v>459</v>
       </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -3340,11 +2435,6 @@
       <c r="C182" t="n">
         <v>445</v>
       </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -3356,11 +2446,6 @@
       <c r="C183" t="n">
         <v>11</v>
       </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -3372,11 +2457,6 @@
       <c r="C184" t="n">
         <v>11</v>
       </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -3388,11 +2468,6 @@
       <c r="C185" t="n">
         <v>108</v>
       </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -3404,11 +2479,6 @@
       <c r="C186" t="n">
         <v>72</v>
       </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -3420,11 +2490,6 @@
       <c r="C187" t="n">
         <v>47</v>
       </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -3436,11 +2501,6 @@
       <c r="C188" t="n">
         <v>54</v>
       </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -3452,11 +2512,6 @@
       <c r="C189" t="n">
         <v>46</v>
       </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -3468,11 +2523,6 @@
       <c r="C190" t="n">
         <v>104</v>
       </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -3484,11 +2534,6 @@
       <c r="C191" t="n">
         <v>55</v>
       </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -3500,11 +2545,6 @@
       <c r="C192" t="n">
         <v>76</v>
       </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -3516,11 +2556,6 @@
       <c r="C193" t="n">
         <v>51</v>
       </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -3532,11 +2567,6 @@
       <c r="C194" t="n">
         <v>63</v>
       </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -3548,11 +2578,6 @@
       <c r="C195" t="n">
         <v>107</v>
       </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -3564,11 +2589,6 @@
       <c r="C196" t="n">
         <v>35</v>
       </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -3580,11 +2600,6 @@
       <c r="C197" t="n">
         <v>95</v>
       </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -3596,11 +2611,6 @@
       <c r="C198" t="n">
         <v>25</v>
       </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -3612,11 +2622,6 @@
       <c r="C199" t="n">
         <v>61</v>
       </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -3628,11 +2633,6 @@
       <c r="C200" t="n">
         <v>56</v>
       </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -3644,11 +2644,6 @@
       <c r="C201" t="n">
         <v>87</v>
       </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -3660,11 +2655,6 @@
       <c r="C202" t="n">
         <v>66</v>
       </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -3676,11 +2666,6 @@
       <c r="C203" t="n">
         <v>127</v>
       </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -3692,11 +2677,6 @@
       <c r="C204" t="n">
         <v>211</v>
       </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -3708,11 +2688,6 @@
       <c r="C205" t="n">
         <v>89</v>
       </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -3724,11 +2699,6 @@
       <c r="C206" t="n">
         <v>106</v>
       </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -3740,11 +2710,6 @@
       <c r="C207" t="n">
         <v>74</v>
       </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -3756,11 +2721,6 @@
       <c r="C208" t="n">
         <v>127</v>
       </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -3772,11 +2732,6 @@
       <c r="C209" t="n">
         <v>88</v>
       </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -3788,11 +2743,6 @@
       <c r="C210" t="n">
         <v>104</v>
       </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -3804,11 +2754,6 @@
       <c r="C211" t="n">
         <v>159</v>
       </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -3820,11 +2765,6 @@
       <c r="C212" t="n">
         <v>115</v>
       </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -3836,11 +2776,6 @@
       <c r="C213" t="n">
         <v>162</v>
       </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -3852,11 +2787,6 @@
       <c r="C214" t="n">
         <v>228</v>
       </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -3868,11 +2798,6 @@
       <c r="C215" t="n">
         <v>348</v>
       </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -3884,11 +2809,6 @@
       <c r="C216" t="n">
         <v>7</v>
       </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -3900,11 +2820,6 @@
       <c r="C217" t="n">
         <v>54</v>
       </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -3916,11 +2831,6 @@
       <c r="C218" t="n">
         <v>2</v>
       </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -3932,11 +2842,6 @@
       <c r="C219" t="n">
         <v>10</v>
       </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -3948,11 +2853,6 @@
       <c r="C220" t="n">
         <v>10</v>
       </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -3964,11 +2864,6 @@
       <c r="C221" t="n">
         <v>6</v>
       </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -3980,11 +2875,6 @@
       <c r="C222" t="n">
         <v>65</v>
       </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -3996,11 +2886,6 @@
       <c r="C223" t="n">
         <v>162</v>
       </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -4012,11 +2897,6 @@
       <c r="C224" t="n">
         <v>81</v>
       </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -4028,11 +2908,6 @@
       <c r="C225" t="n">
         <v>91</v>
       </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -4044,11 +2919,6 @@
       <c r="C226" t="n">
         <v>52</v>
       </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -4060,11 +2930,6 @@
       <c r="C227" t="n">
         <v>141</v>
       </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -4076,11 +2941,6 @@
       <c r="C228" t="n">
         <v>15</v>
       </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -4092,11 +2952,6 @@
       <c r="C229" t="n">
         <v>113</v>
       </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -4108,11 +2963,6 @@
       <c r="C230" t="n">
         <v>49</v>
       </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -4124,11 +2974,6 @@
       <c r="C231" t="n">
         <v>49</v>
       </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -4140,11 +2985,6 @@
       <c r="C232" t="n">
         <v>29</v>
       </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -4156,11 +2996,6 @@
       <c r="C233" t="n">
         <v>23</v>
       </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -4172,11 +3007,6 @@
       <c r="C234" t="n">
         <v>20</v>
       </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -4188,11 +3018,6 @@
       <c r="C235" t="n">
         <v>108</v>
       </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -4204,11 +3029,6 @@
       <c r="C236" t="n">
         <v>176</v>
       </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -4220,11 +3040,6 @@
       <c r="C237" t="n">
         <v>191</v>
       </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -4236,11 +3051,6 @@
       <c r="C238" t="n">
         <v>141</v>
       </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -4252,11 +3062,6 @@
       <c r="C239" t="n">
         <v>249</v>
       </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -4268,11 +3073,6 @@
       <c r="C240" t="n">
         <v>106</v>
       </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -4284,11 +3084,6 @@
       <c r="C241" t="n">
         <v>153</v>
       </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -4300,11 +3095,6 @@
       <c r="C242" t="n">
         <v>99</v>
       </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -4316,11 +3106,6 @@
       <c r="C243" t="n">
         <v>183</v>
       </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -4332,11 +3117,6 @@
       <c r="C244" t="n">
         <v>121</v>
       </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -4348,11 +3128,6 @@
       <c r="C245" t="n">
         <v>95</v>
       </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -4364,11 +3139,6 @@
       <c r="C246" t="n">
         <v>259</v>
       </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -4380,11 +3150,6 @@
       <c r="C247" t="n">
         <v>75</v>
       </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -4396,11 +3161,6 @@
       <c r="C248" t="n">
         <v>294</v>
       </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -4412,11 +3172,6 @@
       <c r="C249" t="n">
         <v>194</v>
       </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -4428,11 +3183,6 @@
       <c r="C250" t="n">
         <v>65</v>
       </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -4444,11 +3194,6 @@
       <c r="C251" t="n">
         <v>45</v>
       </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -4460,11 +3205,6 @@
       <c r="C252" t="n">
         <v>81</v>
       </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -4476,11 +3216,6 @@
       <c r="C253" t="n">
         <v>45</v>
       </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -4492,11 +3227,6 @@
       <c r="C254" t="n">
         <v>75</v>
       </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -4508,11 +3238,6 @@
       <c r="C255" t="n">
         <v>96</v>
       </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -4524,11 +3249,6 @@
       <c r="C256" t="n">
         <v>30</v>
       </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -4540,11 +3260,6 @@
       <c r="C257" t="n">
         <v>34</v>
       </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -4556,11 +3271,6 @@
       <c r="C258" t="n">
         <v>55</v>
       </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -4572,11 +3282,6 @@
       <c r="C259" t="n">
         <v>247</v>
       </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -4588,11 +3293,6 @@
       <c r="C260" t="n">
         <v>24</v>
       </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -4604,11 +3304,6 @@
       <c r="C261" t="n">
         <v>271</v>
       </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -4620,11 +3315,6 @@
       <c r="C262" t="n">
         <v>78</v>
       </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -4636,11 +3326,6 @@
       <c r="C263" t="n">
         <v>114</v>
       </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -4652,11 +3337,6 @@
       <c r="C264" t="n">
         <v>146</v>
       </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -4668,11 +3348,6 @@
       <c r="C265" t="n">
         <v>134</v>
       </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -4684,11 +3359,6 @@
       <c r="C266" t="n">
         <v>94</v>
       </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -4700,11 +3370,6 @@
       <c r="C267" t="n">
         <v>43</v>
       </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -4716,11 +3381,6 @@
       <c r="C268" t="n">
         <v>26</v>
       </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -4732,11 +3392,6 @@
       <c r="C269" t="n">
         <v>184</v>
       </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -4748,11 +3403,6 @@
       <c r="C270" t="n">
         <v>68</v>
       </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -4764,11 +3414,6 @@
       <c r="C271" t="n">
         <v>97</v>
       </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -4780,11 +3425,6 @@
       <c r="C272" t="n">
         <v>29</v>
       </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -4796,11 +3436,6 @@
       <c r="C273" t="n">
         <v>53</v>
       </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -4812,11 +3447,6 @@
       <c r="C274" t="n">
         <v>98</v>
       </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -4828,11 +3458,6 @@
       <c r="C275" t="n">
         <v>210</v>
       </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -4844,11 +3469,6 @@
       <c r="C276" t="n">
         <v>118</v>
       </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -4860,11 +3480,6 @@
       <c r="C277" t="n">
         <v>120</v>
       </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -4876,11 +3491,6 @@
       <c r="C278" t="n">
         <v>65</v>
       </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -4892,11 +3502,6 @@
       <c r="C279" t="n">
         <v>105</v>
       </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -4908,11 +3513,6 @@
       <c r="C280" t="n">
         <v>119</v>
       </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -4924,11 +3524,6 @@
       <c r="C281" t="n">
         <v>236</v>
       </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -4940,11 +3535,6 @@
       <c r="C282" t="n">
         <v>283</v>
       </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -4956,11 +3546,6 @@
       <c r="C283" t="n">
         <v>183</v>
       </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -4972,11 +3557,6 @@
       <c r="C284" t="n">
         <v>117</v>
       </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -4988,11 +3568,6 @@
       <c r="C285" t="n">
         <v>407</v>
       </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -5004,11 +3579,6 @@
       <c r="C286" t="n">
         <v>211</v>
       </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -5020,11 +3590,6 @@
       <c r="C287" t="n">
         <v>72</v>
       </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -5036,11 +3601,6 @@
       <c r="C288" t="n">
         <v>54</v>
       </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -5052,11 +3612,6 @@
       <c r="C289" t="n">
         <v>136</v>
       </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -5068,11 +3623,6 @@
       <c r="C290" t="n">
         <v>203</v>
       </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -5084,11 +3634,6 @@
       <c r="C291" t="n">
         <v>19</v>
       </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -5100,11 +3645,6 @@
       <c r="C292" t="n">
         <v>59</v>
       </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -5116,11 +3656,6 @@
       <c r="C293" t="n">
         <v>70</v>
       </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -5132,11 +3667,6 @@
       <c r="C294" t="n">
         <v>20</v>
       </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -5148,11 +3678,6 @@
       <c r="C295" t="n">
         <v>71</v>
       </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -5164,11 +3689,6 @@
       <c r="C296" t="n">
         <v>5</v>
       </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -5180,11 +3700,6 @@
       <c r="C297" t="n">
         <v>18</v>
       </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -5196,11 +3711,6 @@
       <c r="C298" t="n">
         <v>31</v>
       </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -5212,11 +3722,6 @@
       <c r="C299" t="n">
         <v>50</v>
       </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -5228,11 +3733,6 @@
       <c r="C300" t="n">
         <v>68</v>
       </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -5244,11 +3744,6 @@
       <c r="C301" t="n">
         <v>109</v>
       </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -5260,11 +3755,6 @@
       <c r="C302" t="n">
         <v>184</v>
       </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -5276,11 +3766,6 @@
       <c r="C303" t="n">
         <v>108</v>
       </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -5292,11 +3777,6 @@
       <c r="C304" t="n">
         <v>130</v>
       </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -5308,11 +3788,6 @@
       <c r="C305" t="n">
         <v>42</v>
       </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -5324,11 +3799,6 @@
       <c r="C306" t="n">
         <v>191</v>
       </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -5340,11 +3810,6 @@
       <c r="C307" t="n">
         <v>122</v>
       </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -5356,11 +3821,6 @@
       <c r="C308" t="n">
         <v>115</v>
       </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -5372,11 +3832,6 @@
       <c r="C309" t="n">
         <v>137</v>
       </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -5388,11 +3843,6 @@
       <c r="C310" t="n">
         <v>137</v>
       </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -5404,11 +3854,6 @@
       <c r="C311" t="n">
         <v>112</v>
       </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -5420,11 +3865,6 @@
       <c r="C312" t="n">
         <v>132</v>
       </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -5436,11 +3876,6 @@
       <c r="C313" t="n">
         <v>225</v>
       </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -5452,11 +3887,6 @@
       <c r="C314" t="n">
         <v>62</v>
       </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -5468,11 +3898,6 @@
       <c r="C315" t="n">
         <v>39</v>
       </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -5484,11 +3909,6 @@
       <c r="C316" t="n">
         <v>98</v>
       </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -5500,11 +3920,6 @@
       <c r="C317" t="n">
         <v>53</v>
       </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -5516,11 +3931,6 @@
       <c r="C318" t="n">
         <v>37</v>
       </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -5532,11 +3942,6 @@
       <c r="C319" t="n">
         <v>56</v>
       </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -5548,11 +3953,6 @@
       <c r="C320" t="n">
         <v>71</v>
       </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -5564,11 +3964,6 @@
       <c r="C321" t="n">
         <v>29</v>
       </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -5580,11 +3975,6 @@
       <c r="C322" t="n">
         <v>25</v>
       </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -5596,11 +3986,6 @@
       <c r="C323" t="n">
         <v>39</v>
       </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -5612,11 +3997,6 @@
       <c r="C324" t="n">
         <v>75</v>
       </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -5628,11 +4008,6 @@
       <c r="C325" t="n">
         <v>119</v>
       </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -5644,11 +4019,6 @@
       <c r="C326" t="n">
         <v>198</v>
       </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -5660,11 +4030,6 @@
       <c r="C327" t="n">
         <v>92</v>
       </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -5676,11 +4041,6 @@
       <c r="C328" t="n">
         <v>66</v>
       </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -5692,11 +4052,6 @@
       <c r="C329" t="n">
         <v>131</v>
       </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -5708,11 +4063,6 @@
       <c r="C330" t="n">
         <v>158</v>
       </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -5724,11 +4074,6 @@
       <c r="C331" t="n">
         <v>78</v>
       </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -5740,11 +4085,6 @@
       <c r="C332" t="n">
         <v>210</v>
       </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -5756,11 +4096,6 @@
       <c r="C333" t="n">
         <v>69</v>
       </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -5772,11 +4107,6 @@
       <c r="C334" t="n">
         <v>330</v>
       </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -5788,11 +4118,6 @@
       <c r="C335" t="n">
         <v>12</v>
       </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -5804,11 +4129,6 @@
       <c r="C336" t="n">
         <v>3</v>
       </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -5820,11 +4140,6 @@
       <c r="C337" t="n">
         <v>6</v>
       </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -5836,11 +4151,6 @@
       <c r="C338" t="n">
         <v>5</v>
       </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -5852,11 +4162,6 @@
       <c r="C339" t="n">
         <v>42</v>
       </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -5868,11 +4173,6 @@
       <c r="C340" t="n">
         <v>2</v>
       </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -5884,11 +4184,6 @@
       <c r="C341" t="n">
         <v>13</v>
       </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -5900,11 +4195,6 @@
       <c r="C342" t="n">
         <v>35</v>
       </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -5916,11 +4206,6 @@
       <c r="C343" t="n">
         <v>126</v>
       </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -5932,11 +4217,6 @@
       <c r="C344" t="n">
         <v>19</v>
       </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -5948,11 +4228,6 @@
       <c r="C345" t="n">
         <v>97</v>
       </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -5964,11 +4239,6 @@
       <c r="C346" t="n">
         <v>53</v>
       </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -5980,11 +4250,6 @@
       <c r="C347" t="n">
         <v>16</v>
       </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -5996,11 +4261,6 @@
       <c r="C348" t="n">
         <v>94</v>
       </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -6012,11 +4272,6 @@
       <c r="C349" t="n">
         <v>53</v>
       </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -6028,11 +4283,6 @@
       <c r="C350" t="n">
         <v>34</v>
       </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -6044,11 +4294,6 @@
       <c r="C351" t="n">
         <v>43</v>
       </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -6060,11 +4305,6 @@
       <c r="C352" t="n">
         <v>53</v>
       </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -6076,11 +4316,6 @@
       <c r="C353" t="n">
         <v>50</v>
       </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -6092,11 +4327,6 @@
       <c r="C354" t="n">
         <v>82</v>
       </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -6108,11 +4338,6 @@
       <c r="C355" t="n">
         <v>99</v>
       </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -6124,11 +4349,6 @@
       <c r="C356" t="n">
         <v>65</v>
       </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -6140,11 +4360,6 @@
       <c r="C357" t="n">
         <v>168</v>
       </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -6156,11 +4371,6 @@
       <c r="C358" t="n">
         <v>234</v>
       </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -6172,11 +4382,6 @@
       <c r="C359" t="n">
         <v>197</v>
       </c>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -6188,11 +4393,6 @@
       <c r="C360" t="n">
         <v>201</v>
       </c>
-      <c r="D360" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -6204,11 +4404,6 @@
       <c r="C361" t="n">
         <v>153</v>
       </c>
-      <c r="D361" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -6220,11 +4415,6 @@
       <c r="C362" t="n">
         <v>50</v>
       </c>
-      <c r="D362" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -6236,11 +4426,6 @@
       <c r="C363" t="n">
         <v>232</v>
       </c>
-      <c r="D363" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -6252,11 +4437,6 @@
       <c r="C364" t="n">
         <v>26</v>
       </c>
-      <c r="D364" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -6268,11 +4448,6 @@
       <c r="C365" t="n">
         <v>164</v>
       </c>
-      <c r="D365" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -6284,11 +4459,6 @@
       <c r="C366" t="n">
         <v>51</v>
       </c>
-      <c r="D366" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -6300,11 +4470,6 @@
       <c r="C367" t="n">
         <v>41</v>
       </c>
-      <c r="D367" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -6316,11 +4481,6 @@
       <c r="C368" t="n">
         <v>136</v>
       </c>
-      <c r="D368" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -6332,11 +4492,6 @@
       <c r="C369" t="n">
         <v>7</v>
       </c>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -6348,11 +4503,6 @@
       <c r="C370" t="n">
         <v>78</v>
       </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -6364,11 +4514,6 @@
       <c r="C371" t="n">
         <v>69</v>
       </c>
-      <c r="D371" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -6380,11 +4525,6 @@
       <c r="C372" t="n">
         <v>24</v>
       </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -6396,11 +4536,6 @@
       <c r="C373" t="n">
         <v>45</v>
       </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -6412,11 +4547,6 @@
       <c r="C374" t="n">
         <v>120</v>
       </c>
-      <c r="D374" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -6428,11 +4558,6 @@
       <c r="C375" t="n">
         <v>45</v>
       </c>
-      <c r="D375" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -6444,11 +4569,6 @@
       <c r="C376" t="n">
         <v>15</v>
       </c>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -6460,11 +4580,6 @@
       <c r="C377" t="n">
         <v>29</v>
       </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -6476,11 +4591,6 @@
       <c r="C378" t="n">
         <v>51</v>
       </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -6492,11 +4602,6 @@
       <c r="C379" t="n">
         <v>41</v>
       </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -6508,11 +4613,6 @@
       <c r="C380" t="n">
         <v>54</v>
       </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -6524,11 +4624,6 @@
       <c r="C381" t="n">
         <v>103</v>
       </c>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -6540,11 +4635,6 @@
       <c r="C382" t="n">
         <v>53</v>
       </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -6556,11 +4646,6 @@
       <c r="C383" t="n">
         <v>91</v>
       </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -6572,11 +4657,6 @@
       <c r="C384" t="n">
         <v>73</v>
       </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -6588,11 +4668,6 @@
       <c r="C385" t="n">
         <v>92</v>
       </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -6604,11 +4679,6 @@
       <c r="C386" t="n">
         <v>55</v>
       </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -6620,11 +4690,6 @@
       <c r="C387" t="n">
         <v>12</v>
       </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -6636,11 +4701,6 @@
       <c r="C388" t="n">
         <v>104</v>
       </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -6652,11 +4712,6 @@
       <c r="C389" t="n">
         <v>26</v>
       </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -6668,11 +4723,6 @@
       <c r="C390" t="n">
         <v>121</v>
       </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -6684,11 +4734,6 @@
       <c r="C391" t="n">
         <v>110</v>
       </c>
-      <c r="D391" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -6700,11 +4745,6 @@
       <c r="C392" t="n">
         <v>181</v>
       </c>
-      <c r="D392" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -6716,11 +4756,6 @@
       <c r="C393" t="n">
         <v>137</v>
       </c>
-      <c r="D393" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -6732,11 +4767,6 @@
       <c r="C394" t="n">
         <v>107</v>
       </c>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -6748,11 +4778,6 @@
       <c r="C395" t="n">
         <v>82</v>
       </c>
-      <c r="D395" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -6764,11 +4789,6 @@
       <c r="C396" t="n">
         <v>11</v>
       </c>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -6780,11 +4800,6 @@
       <c r="C397" t="n">
         <v>57</v>
       </c>
-      <c r="D397" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -6796,11 +4811,6 @@
       <c r="C398" t="n">
         <v>41</v>
       </c>
-      <c r="D398" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -6812,11 +4822,6 @@
       <c r="C399" t="n">
         <v>45</v>
       </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -6828,11 +4833,6 @@
       <c r="C400" t="n">
         <v>99</v>
       </c>
-      <c r="D400" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -6844,11 +4844,6 @@
       <c r="C401" t="n">
         <v>57</v>
       </c>
-      <c r="D401" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -6860,11 +4855,6 @@
       <c r="C402" t="n">
         <v>181</v>
       </c>
-      <c r="D402" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -6876,11 +4866,6 @@
       <c r="C403" t="n">
         <v>18</v>
       </c>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -6892,11 +4877,6 @@
       <c r="C404" t="n">
         <v>52</v>
       </c>
-      <c r="D404" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -6908,11 +4888,6 @@
       <c r="C405" t="n">
         <v>18</v>
       </c>
-      <c r="D405" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -6924,11 +4899,6 @@
       <c r="C406" t="n">
         <v>44</v>
       </c>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -6940,11 +4910,6 @@
       <c r="C407" t="n">
         <v>10</v>
       </c>
-      <c r="D407" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -6956,11 +4921,6 @@
       <c r="C408" t="n">
         <v>74</v>
       </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -6972,11 +4932,6 @@
       <c r="C409" t="n">
         <v>53</v>
       </c>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -6988,11 +4943,6 @@
       <c r="C410" t="n">
         <v>24</v>
       </c>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -7004,11 +4954,6 @@
       <c r="C411" t="n">
         <v>46</v>
       </c>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -7020,11 +4965,6 @@
       <c r="C412" t="n">
         <v>55</v>
       </c>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -7036,11 +4976,6 @@
       <c r="C413" t="n">
         <v>75</v>
       </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -7052,11 +4987,6 @@
       <c r="C414" t="n">
         <v>53</v>
       </c>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -7068,11 +4998,6 @@
       <c r="C415" t="n">
         <v>46</v>
       </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -7084,11 +5009,6 @@
       <c r="C416" t="n">
         <v>28</v>
       </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -7100,11 +5020,6 @@
       <c r="C417" t="n">
         <v>100</v>
       </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -7116,11 +5031,6 @@
       <c r="C418" t="n">
         <v>106</v>
       </c>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -7132,11 +5042,6 @@
       <c r="C419" t="n">
         <v>134</v>
       </c>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -7148,11 +5053,6 @@
       <c r="C420" t="n">
         <v>6</v>
       </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -7164,11 +5064,6 @@
       <c r="C421" t="n">
         <v>126</v>
       </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -7180,11 +5075,6 @@
       <c r="C422" t="n">
         <v>36</v>
       </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -7196,11 +5086,6 @@
       <c r="C423" t="n">
         <v>34</v>
       </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -7212,11 +5097,6 @@
       <c r="C424" t="n">
         <v>111</v>
       </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -7228,11 +5108,6 @@
       <c r="C425" t="n">
         <v>115</v>
       </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -7244,11 +5119,6 @@
       <c r="C426" t="n">
         <v>70</v>
       </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -7260,11 +5130,6 @@
       <c r="C427" t="n">
         <v>125</v>
       </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -7276,11 +5141,6 @@
       <c r="C428" t="n">
         <v>96</v>
       </c>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -7292,11 +5152,6 @@
       <c r="C429" t="n">
         <v>48</v>
       </c>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -7308,11 +5163,6 @@
       <c r="C430" t="n">
         <v>55</v>
       </c>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -7324,11 +5174,6 @@
       <c r="C431" t="n">
         <v>84</v>
       </c>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -7340,11 +5185,6 @@
       <c r="C432" t="n">
         <v>29</v>
       </c>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -7356,11 +5196,6 @@
       <c r="C433" t="n">
         <v>128</v>
       </c>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -7372,11 +5207,6 @@
       <c r="C434" t="n">
         <v>78</v>
       </c>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -7388,11 +5218,6 @@
       <c r="C435" t="n">
         <v>139</v>
       </c>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -7404,11 +5229,6 @@
       <c r="C436" t="n">
         <v>158</v>
       </c>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -7420,11 +5240,6 @@
       <c r="C437" t="n">
         <v>73</v>
       </c>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -7436,11 +5251,6 @@
       <c r="C438" t="n">
         <v>151</v>
       </c>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -7452,11 +5262,6 @@
       <c r="C439" t="n">
         <v>206</v>
       </c>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -7468,11 +5273,6 @@
       <c r="C440" t="n">
         <v>182</v>
       </c>
-      <c r="D440" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -7484,11 +5284,6 @@
       <c r="C441" t="n">
         <v>104</v>
       </c>
-      <c r="D441" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -7500,11 +5295,6 @@
       <c r="C442" t="n">
         <v>30</v>
       </c>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -7516,11 +5306,6 @@
       <c r="C443" t="n">
         <v>48</v>
       </c>
-      <c r="D443" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -7532,11 +5317,6 @@
       <c r="C444" t="n">
         <v>64</v>
       </c>
-      <c r="D444" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -7548,11 +5328,6 @@
       <c r="C445" t="n">
         <v>128</v>
       </c>
-      <c r="D445" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -7564,11 +5339,6 @@
       <c r="C446" t="n">
         <v>124</v>
       </c>
-      <c r="D446" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -7580,11 +5350,6 @@
       <c r="C447" t="n">
         <v>196</v>
       </c>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -7596,11 +5361,6 @@
       <c r="C448" t="n">
         <v>159</v>
       </c>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -7612,11 +5372,6 @@
       <c r="C449" t="n">
         <v>188</v>
       </c>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -7628,11 +5383,6 @@
       <c r="C450" t="n">
         <v>5</v>
       </c>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -7644,11 +5394,6 @@
       <c r="C451" t="n">
         <v>3</v>
       </c>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -7660,11 +5405,6 @@
       <c r="C452" t="n">
         <v>7</v>
       </c>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -7676,11 +5416,6 @@
       <c r="C453" t="n">
         <v>125</v>
       </c>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -7692,11 +5427,6 @@
       <c r="C454" t="n">
         <v>61</v>
       </c>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -7708,11 +5438,6 @@
       <c r="C455" t="n">
         <v>81</v>
       </c>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -7724,11 +5449,6 @@
       <c r="C456" t="n">
         <v>88</v>
       </c>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -7740,11 +5460,6 @@
       <c r="C457" t="n">
         <v>63</v>
       </c>
-      <c r="D457" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -7756,11 +5471,6 @@
       <c r="C458" t="n">
         <v>3</v>
       </c>
-      <c r="D458" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -7772,11 +5482,6 @@
       <c r="C459" t="n">
         <v>49</v>
       </c>
-      <c r="D459" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -7788,11 +5493,6 @@
       <c r="C460" t="n">
         <v>7</v>
       </c>
-      <c r="D460" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -7804,11 +5504,6 @@
       <c r="C461" t="n">
         <v>45</v>
       </c>
-      <c r="D461" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -7820,11 +5515,6 @@
       <c r="C462" t="n">
         <v>77</v>
       </c>
-      <c r="D462" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -7836,11 +5526,6 @@
       <c r="C463" t="n">
         <v>75</v>
       </c>
-      <c r="D463" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -7852,11 +5537,6 @@
       <c r="C464" t="n">
         <v>12</v>
       </c>
-      <c r="D464" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -7868,11 +5548,6 @@
       <c r="C465" t="n">
         <v>33</v>
       </c>
-      <c r="D465" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -7884,11 +5559,6 @@
       <c r="C466" t="n">
         <v>32</v>
       </c>
-      <c r="D466" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -7900,11 +5570,6 @@
       <c r="C467" t="n">
         <v>28</v>
       </c>
-      <c r="D467" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -7916,11 +5581,6 @@
       <c r="C468" t="n">
         <v>79</v>
       </c>
-      <c r="D468" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -7932,11 +5592,6 @@
       <c r="C469" t="n">
         <v>216</v>
       </c>
-      <c r="D469" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -7948,11 +5603,6 @@
       <c r="C470" t="n">
         <v>23</v>
       </c>
-      <c r="D470" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -7964,11 +5614,6 @@
       <c r="C471" t="n">
         <v>67</v>
       </c>
-      <c r="D471" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -7980,11 +5625,6 @@
       <c r="C472" t="n">
         <v>39</v>
       </c>
-      <c r="D472" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -7996,11 +5636,6 @@
       <c r="C473" t="n">
         <v>56</v>
       </c>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -8012,11 +5647,6 @@
       <c r="C474" t="n">
         <v>63</v>
       </c>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -8028,11 +5658,6 @@
       <c r="C475" t="n">
         <v>24</v>
       </c>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -8044,11 +5669,6 @@
       <c r="C476" t="n">
         <v>77</v>
       </c>
-      <c r="D476" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -8060,11 +5680,6 @@
       <c r="C477" t="n">
         <v>61</v>
       </c>
-      <c r="D477" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -8076,11 +5691,6 @@
       <c r="C478" t="n">
         <v>15</v>
       </c>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -8092,11 +5702,6 @@
       <c r="C479" t="n">
         <v>37</v>
       </c>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -8108,11 +5713,6 @@
       <c r="C480" t="n">
         <v>10</v>
       </c>
-      <c r="D480" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -8124,11 +5724,6 @@
       <c r="C481" t="n">
         <v>26</v>
       </c>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -8140,11 +5735,6 @@
       <c r="C482" t="n">
         <v>85</v>
       </c>
-      <c r="D482" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -8156,11 +5746,6 @@
       <c r="C483" t="n">
         <v>99</v>
       </c>
-      <c r="D483" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -8172,11 +5757,6 @@
       <c r="C484" t="n">
         <v>75</v>
       </c>
-      <c r="D484" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -8188,11 +5768,6 @@
       <c r="C485" t="n">
         <v>38</v>
       </c>
-      <c r="D485" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -8204,11 +5779,6 @@
       <c r="C486" t="n">
         <v>15</v>
       </c>
-      <c r="D486" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -8220,11 +5790,6 @@
       <c r="C487" t="n">
         <v>38</v>
       </c>
-      <c r="D487" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -8236,11 +5801,6 @@
       <c r="C488" t="n">
         <v>209</v>
       </c>
-      <c r="D488" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -8252,11 +5812,6 @@
       <c r="C489" t="n">
         <v>158</v>
       </c>
-      <c r="D489" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -8268,11 +5823,6 @@
       <c r="C490" t="n">
         <v>5</v>
       </c>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -8284,11 +5834,6 @@
       <c r="C491" t="n">
         <v>65</v>
       </c>
-      <c r="D491" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -8300,11 +5845,6 @@
       <c r="C492" t="n">
         <v>45</v>
       </c>
-      <c r="D492" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -8316,11 +5856,6 @@
       <c r="C493" t="n">
         <v>61</v>
       </c>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -8332,11 +5867,6 @@
       <c r="C494" t="n">
         <v>57</v>
       </c>
-      <c r="D494" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -8348,11 +5878,6 @@
       <c r="C495" t="n">
         <v>45</v>
       </c>
-      <c r="D495" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -8364,11 +5889,6 @@
       <c r="C496" t="n">
         <v>58</v>
       </c>
-      <c r="D496" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -8380,11 +5900,6 @@
       <c r="C497" t="n">
         <v>15</v>
       </c>
-      <c r="D497" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -8396,11 +5911,6 @@
       <c r="C498" t="n">
         <v>50</v>
       </c>
-      <c r="D498" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -8412,11 +5922,6 @@
       <c r="C499" t="n">
         <v>57</v>
       </c>
-      <c r="D499" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -8428,11 +5933,6 @@
       <c r="C500" t="n">
         <v>181</v>
       </c>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -8444,11 +5944,6 @@
       <c r="C501" t="n">
         <v>49</v>
       </c>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -8460,11 +5955,6 @@
       <c r="C502" t="n">
         <v>120</v>
       </c>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -8476,11 +5966,6 @@
       <c r="C503" t="n">
         <v>53</v>
       </c>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -8492,11 +5977,6 @@
       <c r="C504" t="n">
         <v>159</v>
       </c>
-      <c r="D504" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -8508,11 +5988,6 @@
       <c r="C505" t="n">
         <v>42</v>
       </c>
-      <c r="D505" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -8524,11 +5999,6 @@
       <c r="C506" t="n">
         <v>61</v>
       </c>
-      <c r="D506" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -8540,11 +6010,6 @@
       <c r="C507" t="n">
         <v>73</v>
       </c>
-      <c r="D507" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -8556,11 +6021,6 @@
       <c r="C508" t="n">
         <v>23</v>
       </c>
-      <c r="D508" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -8572,11 +6032,6 @@
       <c r="C509" t="n">
         <v>54</v>
       </c>
-      <c r="D509" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -8588,11 +6043,6 @@
       <c r="C510" t="n">
         <v>162</v>
       </c>
-      <c r="D510" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -8604,11 +6054,6 @@
       <c r="C511" t="n">
         <v>148</v>
       </c>
-      <c r="D511" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -8620,11 +6065,6 @@
       <c r="C512" t="n">
         <v>199</v>
       </c>
-      <c r="D512" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -8636,11 +6076,6 @@
       <c r="C513" t="n">
         <v>66</v>
       </c>
-      <c r="D513" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -8652,11 +6087,6 @@
       <c r="C514" t="n">
         <v>107</v>
       </c>
-      <c r="D514" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -8668,11 +6098,6 @@
       <c r="C515" t="n">
         <v>68</v>
       </c>
-      <c r="D515" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -8684,11 +6109,6 @@
       <c r="C516" t="n">
         <v>41</v>
       </c>
-      <c r="D516" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -8700,11 +6120,6 @@
       <c r="C517" t="n">
         <v>4</v>
       </c>
-      <c r="D517" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -8716,11 +6131,6 @@
       <c r="C518" t="n">
         <v>77</v>
       </c>
-      <c r="D518" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -8732,11 +6142,6 @@
       <c r="C519" t="n">
         <v>42</v>
       </c>
-      <c r="D519" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -8748,11 +6153,6 @@
       <c r="C520" t="n">
         <v>67</v>
       </c>
-      <c r="D520" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -8764,11 +6164,6 @@
       <c r="C521" t="n">
         <v>51</v>
       </c>
-      <c r="D521" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -8780,11 +6175,6 @@
       <c r="C522" t="n">
         <v>96</v>
       </c>
-      <c r="D522" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -8796,11 +6186,6 @@
       <c r="C523" t="n">
         <v>41</v>
       </c>
-      <c r="D523" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -8812,11 +6197,6 @@
       <c r="C524" t="n">
         <v>36</v>
       </c>
-      <c r="D524" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -8828,11 +6208,6 @@
       <c r="C525" t="n">
         <v>41</v>
       </c>
-      <c r="D525" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -8844,11 +6219,6 @@
       <c r="C526" t="n">
         <v>40</v>
       </c>
-      <c r="D526" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -8860,11 +6230,6 @@
       <c r="C527" t="n">
         <v>181</v>
       </c>
-      <c r="D527" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -8876,11 +6241,6 @@
       <c r="C528" t="n">
         <v>113</v>
       </c>
-      <c r="D528" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -8892,11 +6252,6 @@
       <c r="C529" t="n">
         <v>42</v>
       </c>
-      <c r="D529" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -8908,11 +6263,6 @@
       <c r="C530" t="n">
         <v>131</v>
       </c>
-      <c r="D530" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -8924,11 +6274,6 @@
       <c r="C531" t="n">
         <v>29</v>
       </c>
-      <c r="D531" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -8940,11 +6285,6 @@
       <c r="C532" t="n">
         <v>114</v>
       </c>
-      <c r="D532" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -8956,11 +6296,6 @@
       <c r="C533" t="n">
         <v>71</v>
       </c>
-      <c r="D533" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -8972,11 +6307,6 @@
       <c r="C534" t="n">
         <v>17</v>
       </c>
-      <c r="D534" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -8988,11 +6318,6 @@
       <c r="C535" t="n">
         <v>48</v>
       </c>
-      <c r="D535" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -9004,11 +6329,6 @@
       <c r="C536" t="n">
         <v>43</v>
       </c>
-      <c r="D536" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -9020,11 +6340,6 @@
       <c r="C537" t="n">
         <v>167</v>
       </c>
-      <c r="D537" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -9036,11 +6351,6 @@
       <c r="C538" t="n">
         <v>110</v>
       </c>
-      <c r="D538" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -9052,11 +6362,6 @@
       <c r="C539" t="n">
         <v>12</v>
       </c>
-      <c r="D539" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -9068,11 +6373,6 @@
       <c r="C540" t="n">
         <v>86</v>
       </c>
-      <c r="D540" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -9084,11 +6384,6 @@
       <c r="C541" t="n">
         <v>83</v>
       </c>
-      <c r="D541" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
@@ -9100,11 +6395,6 @@
       <c r="C542" t="n">
         <v>43</v>
       </c>
-      <c r="D542" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
@@ -9116,11 +6406,6 @@
       <c r="C543" t="n">
         <v>93</v>
       </c>
-      <c r="D543" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
@@ -9132,11 +6417,6 @@
       <c r="C544" t="n">
         <v>172</v>
       </c>
-      <c r="D544" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
@@ -9148,11 +6428,6 @@
       <c r="C545" t="n">
         <v>155</v>
       </c>
-      <c r="D545" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
@@ -9164,11 +6439,6 @@
       <c r="C546" t="n">
         <v>246</v>
       </c>
-      <c r="D546" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="547">
       <c r="A547" t="n">
@@ -9180,11 +6450,6 @@
       <c r="C547" t="n">
         <v>146</v>
       </c>
-      <c r="D547" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
@@ -9196,11 +6461,6 @@
       <c r="C548" t="n">
         <v>14</v>
       </c>
-      <c r="D548" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
@@ -9212,11 +6472,6 @@
       <c r="C549" t="n">
         <v>21</v>
       </c>
-      <c r="D549" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
@@ -9228,11 +6483,6 @@
       <c r="C550" t="n">
         <v>104</v>
       </c>
-      <c r="D550" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
@@ -9244,11 +6494,6 @@
       <c r="C551" t="n">
         <v>143</v>
       </c>
-      <c r="D551" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
@@ -9260,11 +6505,6 @@
       <c r="C552" t="n">
         <v>79</v>
       </c>
-      <c r="D552" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
@@ -9276,11 +6516,6 @@
       <c r="C553" t="n">
         <v>33</v>
       </c>
-      <c r="D553" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
@@ -9292,11 +6527,6 @@
       <c r="C554" t="n">
         <v>122</v>
       </c>
-      <c r="D554" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
@@ -9308,11 +6538,6 @@
       <c r="C555" t="n">
         <v>25</v>
       </c>
-      <c r="D555" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
@@ -9324,11 +6549,6 @@
       <c r="C556" t="n">
         <v>29</v>
       </c>
-      <c r="D556" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
@@ -9340,11 +6560,6 @@
       <c r="C557" t="n">
         <v>55</v>
       </c>
-      <c r="D557" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
@@ -9356,11 +6571,6 @@
       <c r="C558" t="n">
         <v>65</v>
       </c>
-      <c r="D558" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
@@ -9372,11 +6582,6 @@
       <c r="C559" t="n">
         <v>31</v>
       </c>
-      <c r="D559" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="560">
       <c r="A560" t="n">
@@ -9388,11 +6593,6 @@
       <c r="C560" t="n">
         <v>45</v>
       </c>
-      <c r="D560" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="561">
       <c r="A561" t="n">
@@ -9404,11 +6604,6 @@
       <c r="C561" t="n">
         <v>26</v>
       </c>
-      <c r="D561" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
@@ -9420,11 +6615,6 @@
       <c r="C562" t="n">
         <v>55</v>
       </c>
-      <c r="D562" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
@@ -9436,11 +6626,6 @@
       <c r="C563" t="n">
         <v>124</v>
       </c>
-      <c r="D563" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
@@ -9452,11 +6637,6 @@
       <c r="C564" t="n">
         <v>19</v>
       </c>
-      <c r="D564" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
@@ -9468,11 +6648,6 @@
       <c r="C565" t="n">
         <v>41</v>
       </c>
-      <c r="D565" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
@@ -9484,11 +6659,6 @@
       <c r="C566" t="n">
         <v>32</v>
       </c>
-      <c r="D566" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
@@ -9500,11 +6670,6 @@
       <c r="C567" t="n">
         <v>57</v>
       </c>
-      <c r="D567" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
@@ -9516,11 +6681,6 @@
       <c r="C568" t="n">
         <v>4</v>
       </c>
-      <c r="D568" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
@@ -9532,11 +6692,6 @@
       <c r="C569" t="n">
         <v>89</v>
       </c>
-      <c r="D569" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
@@ -9548,11 +6703,6 @@
       <c r="C570" t="n">
         <v>67</v>
       </c>
-      <c r="D570" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
@@ -9564,11 +6714,6 @@
       <c r="C571" t="n">
         <v>73</v>
       </c>
-      <c r="D571" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
@@ -9580,11 +6725,6 @@
       <c r="C572" t="n">
         <v>158</v>
       </c>
-      <c r="D572" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
@@ -9596,11 +6736,6 @@
       <c r="C573" t="n">
         <v>79</v>
       </c>
-      <c r="D573" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
@@ -9612,11 +6747,6 @@
       <c r="C574" t="n">
         <v>29</v>
       </c>
-      <c r="D574" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
@@ -9628,11 +6758,6 @@
       <c r="C575" t="n">
         <v>60</v>
       </c>
-      <c r="D575" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
@@ -9644,11 +6769,6 @@
       <c r="C576" t="n">
         <v>100</v>
       </c>
-      <c r="D576" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="577">
       <c r="A577" t="n">
@@ -9660,11 +6780,6 @@
       <c r="C577" t="n">
         <v>48</v>
       </c>
-      <c r="D577" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="578">
       <c r="A578" t="n">
@@ -9676,11 +6791,6 @@
       <c r="C578" t="n">
         <v>47</v>
       </c>
-      <c r="D578" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="579">
       <c r="A579" t="n">
@@ -9692,11 +6802,6 @@
       <c r="C579" t="n">
         <v>37</v>
       </c>
-      <c r="D579" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
@@ -9708,11 +6813,6 @@
       <c r="C580" t="n">
         <v>45</v>
       </c>
-      <c r="D580" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="581">
       <c r="A581" t="n">
@@ -9724,11 +6824,6 @@
       <c r="C581" t="n">
         <v>155</v>
       </c>
-      <c r="D581" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="582">
       <c r="A582" t="n">
@@ -9740,11 +6835,6 @@
       <c r="C582" t="n">
         <v>32</v>
       </c>
-      <c r="D582" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="583">
       <c r="A583" t="n">
@@ -9756,11 +6846,6 @@
       <c r="C583" t="n">
         <v>166</v>
       </c>
-      <c r="D583" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="584">
       <c r="A584" t="n">
@@ -9772,11 +6857,6 @@
       <c r="C584" t="n">
         <v>10</v>
       </c>
-      <c r="D584" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="585">
       <c r="A585" t="n">
@@ -9788,11 +6868,6 @@
       <c r="C585" t="n">
         <v>39</v>
       </c>
-      <c r="D585" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="586">
       <c r="A586" t="n">
@@ -9804,11 +6879,6 @@
       <c r="C586" t="n">
         <v>46</v>
       </c>
-      <c r="D586" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
@@ -9820,11 +6890,6 @@
       <c r="C587" t="n">
         <v>62</v>
       </c>
-      <c r="D587" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="588">
       <c r="A588" t="n">
@@ -9836,11 +6901,6 @@
       <c r="C588" t="n">
         <v>43</v>
       </c>
-      <c r="D588" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="589">
       <c r="A589" t="n">
@@ -9852,11 +6912,6 @@
       <c r="C589" t="n">
         <v>66</v>
       </c>
-      <c r="D589" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
@@ -9868,11 +6923,6 @@
       <c r="C590" t="n">
         <v>22</v>
       </c>
-      <c r="D590" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="591">
       <c r="A591" t="n">
@@ -9884,11 +6934,6 @@
       <c r="C591" t="n">
         <v>116</v>
       </c>
-      <c r="D591" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="592">
       <c r="A592" t="n">
@@ -9900,11 +6945,6 @@
       <c r="C592" t="n">
         <v>105</v>
       </c>
-      <c r="D592" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="593">
       <c r="A593" t="n">
@@ -9916,11 +6956,6 @@
       <c r="C593" t="n">
         <v>75</v>
       </c>
-      <c r="D593" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="594">
       <c r="A594" t="n">
@@ -9932,11 +6967,6 @@
       <c r="C594" t="n">
         <v>142</v>
       </c>
-      <c r="D594" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="595">
       <c r="A595" t="n">
@@ -9948,11 +6978,6 @@
       <c r="C595" t="n">
         <v>96</v>
       </c>
-      <c r="D595" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="596">
       <c r="A596" t="n">
@@ -9964,11 +6989,6 @@
       <c r="C596" t="n">
         <v>68</v>
       </c>
-      <c r="D596" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="597">
       <c r="A597" t="n">
@@ -9980,11 +7000,6 @@
       <c r="C597" t="n">
         <v>51</v>
       </c>
-      <c r="D597" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="598">
       <c r="A598" t="n">
@@ -9996,11 +7011,6 @@
       <c r="C598" t="n">
         <v>110</v>
       </c>
-      <c r="D598" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="599">
       <c r="A599" t="n">
@@ -10012,11 +7022,6 @@
       <c r="C599" t="n">
         <v>97</v>
       </c>
-      <c r="D599" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="600">
       <c r="A600" t="n">
@@ -10028,11 +7033,6 @@
       <c r="C600" t="n">
         <v>40</v>
       </c>
-      <c r="D600" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="601">
       <c r="A601" t="n">
@@ -10044,11 +7044,6 @@
       <c r="C601" t="n">
         <v>136</v>
       </c>
-      <c r="D601" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="602">
       <c r="A602" t="n">
@@ -10060,11 +7055,6 @@
       <c r="C602" t="n">
         <v>187</v>
       </c>
-      <c r="D602" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="603">
       <c r="A603" t="n">
@@ -10076,11 +7066,6 @@
       <c r="C603" t="n">
         <v>66</v>
       </c>
-      <c r="D603" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="604">
       <c r="A604" t="n">
@@ -10092,11 +7077,6 @@
       <c r="C604" t="n">
         <v>66</v>
       </c>
-      <c r="D604" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="605">
       <c r="A605" t="n">
@@ -10108,11 +7088,6 @@
       <c r="C605" t="n">
         <v>119</v>
       </c>
-      <c r="D605" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="606">
       <c r="A606" t="n">
@@ -10124,11 +7099,6 @@
       <c r="C606" t="n">
         <v>61</v>
       </c>
-      <c r="D606" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="607">
       <c r="A607" t="n">
@@ -10140,11 +7110,6 @@
       <c r="C607" t="n">
         <v>95</v>
       </c>
-      <c r="D607" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="608">
       <c r="A608" t="n">
@@ -10156,11 +7121,6 @@
       <c r="C608" t="n">
         <v>150</v>
       </c>
-      <c r="D608" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="609">
       <c r="A609" t="n">
@@ -10172,11 +7132,6 @@
       <c r="C609" t="n">
         <v>40</v>
       </c>
-      <c r="D609" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="610">
       <c r="A610" t="n">
@@ -10188,11 +7143,6 @@
       <c r="C610" t="n">
         <v>110</v>
       </c>
-      <c r="D610" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="611">
       <c r="A611" t="n">
@@ -10204,11 +7154,6 @@
       <c r="C611" t="n">
         <v>269</v>
       </c>
-      <c r="D611" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="612">
       <c r="A612" t="n">
@@ -10220,11 +7165,6 @@
       <c r="C612" t="n">
         <v>75</v>
       </c>
-      <c r="D612" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
     </row>
     <row r="613">
       <c r="A613" t="n">
@@ -10236,11 +7176,6 @@
       <c r="C613" t="n">
         <v>90</v>
       </c>
-      <c r="D613" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="614">
       <c r="A614" t="n">
@@ -10252,11 +7187,6 @@
       <c r="C614" t="n">
         <v>31</v>
       </c>
-      <c r="D614" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="615">
       <c r="A615" t="n">
@@ -10268,11 +7198,6 @@
       <c r="C615" t="n">
         <v>305</v>
       </c>
-      <c r="D615" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="616">
       <c r="A616" t="n">
@@ -10284,11 +7209,6 @@
       <c r="C616" t="n">
         <v>56</v>
       </c>
-      <c r="D616" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="617">
       <c r="A617" t="n">
@@ -10300,11 +7220,6 @@
       <c r="C617" t="n">
         <v>46</v>
       </c>
-      <c r="D617" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="618">
       <c r="A618" t="n">
@@ -10316,11 +7231,6 @@
       <c r="C618" t="n">
         <v>39</v>
       </c>
-      <c r="D618" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="619">
       <c r="A619" t="n">
@@ -10332,11 +7242,6 @@
       <c r="C619" t="n">
         <v>54</v>
       </c>
-      <c r="D619" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="620">
       <c r="A620" t="n">
@@ -10348,11 +7253,6 @@
       <c r="C620" t="n">
         <v>66</v>
       </c>
-      <c r="D620" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="621">
       <c r="A621" t="n">
@@ -10364,11 +7264,6 @@
       <c r="C621" t="n">
         <v>72</v>
       </c>
-      <c r="D621" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="622">
       <c r="A622" t="n">
@@ -10380,11 +7275,6 @@
       <c r="C622" t="n">
         <v>63</v>
       </c>
-      <c r="D622" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="623">
       <c r="A623" t="n">
@@ -10396,11 +7286,6 @@
       <c r="C623" t="n">
         <v>29</v>
       </c>
-      <c r="D623" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="624">
       <c r="A624" t="n">
@@ -10412,11 +7297,6 @@
       <c r="C624" t="n">
         <v>22</v>
       </c>
-      <c r="D624" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="625">
       <c r="A625" t="n">
@@ -10428,11 +7308,6 @@
       <c r="C625" t="n">
         <v>53</v>
       </c>
-      <c r="D625" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="626">
       <c r="A626" t="n">
@@ -10444,11 +7319,6 @@
       <c r="C626" t="n">
         <v>71</v>
       </c>
-      <c r="D626" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="627">
       <c r="A627" t="n">
@@ -10460,11 +7330,6 @@
       <c r="C627" t="n">
         <v>81</v>
       </c>
-      <c r="D627" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="628">
       <c r="A628" t="n">
@@ -10476,11 +7341,6 @@
       <c r="C628" t="n">
         <v>104</v>
       </c>
-      <c r="D628" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="629">
       <c r="A629" t="n">
@@ -10492,11 +7352,6 @@
       <c r="C629" t="n">
         <v>46</v>
       </c>
-      <c r="D629" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="630">
       <c r="A630" t="n">
@@ -10508,11 +7363,6 @@
       <c r="C630" t="n">
         <v>79</v>
       </c>
-      <c r="D630" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="631">
       <c r="A631" t="n">
@@ -10524,11 +7374,6 @@
       <c r="C631" t="n">
         <v>74</v>
       </c>
-      <c r="D631" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="632">
       <c r="A632" t="n">
@@ -10540,11 +7385,6 @@
       <c r="C632" t="n">
         <v>137</v>
       </c>
-      <c r="D632" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="633">
       <c r="A633" t="n">
@@ -10556,11 +7396,6 @@
       <c r="C633" t="n">
         <v>25</v>
       </c>
-      <c r="D633" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="634">
       <c r="A634" t="n">
@@ -10572,11 +7407,6 @@
       <c r="C634" t="n">
         <v>80</v>
       </c>
-      <c r="D634" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="635">
       <c r="A635" t="n">
@@ -10588,11 +7418,6 @@
       <c r="C635" t="n">
         <v>65</v>
       </c>
-      <c r="D635" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
     </row>
     <row r="636">
       <c r="A636" t="n">
@@ -10604,11 +7429,6 @@
       <c r="C636" t="n">
         <v>95</v>
       </c>
-      <c r="D636" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="637">
       <c r="A637" t="n">
@@ -10620,11 +7440,6 @@
       <c r="C637" t="n">
         <v>47</v>
       </c>
-      <c r="D637" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="638">
       <c r="A638" t="n">
@@ -10636,11 +7451,6 @@
       <c r="C638" t="n">
         <v>56</v>
       </c>
-      <c r="D638" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="639">
       <c r="A639" t="n">
@@ -10652,11 +7462,6 @@
       <c r="C639" t="n">
         <v>41</v>
       </c>
-      <c r="D639" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="640">
       <c r="A640" t="n">
@@ -10668,11 +7473,6 @@
       <c r="C640" t="n">
         <v>96</v>
       </c>
-      <c r="D640" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="641">
       <c r="A641" t="n">
@@ -10684,11 +7484,6 @@
       <c r="C641" t="n">
         <v>23</v>
       </c>
-      <c r="D641" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="642">
       <c r="A642" t="n">
@@ -10700,11 +7495,6 @@
       <c r="C642" t="n">
         <v>349</v>
       </c>
-      <c r="D642" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="643">
       <c r="A643" t="n">
@@ -10716,11 +7506,6 @@
       <c r="C643" t="n">
         <v>109</v>
       </c>
-      <c r="D643" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="644">
       <c r="A644" t="n">
@@ -10732,11 +7517,6 @@
       <c r="C644" t="n">
         <v>292</v>
       </c>
-      <c r="D644" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="645">
       <c r="A645" t="n">
@@ -10748,11 +7528,6 @@
       <c r="C645" t="n">
         <v>275</v>
       </c>
-      <c r="D645" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="646">
       <c r="A646" t="n">
@@ -10764,11 +7539,6 @@
       <c r="C646" t="n">
         <v>355</v>
       </c>
-      <c r="D646" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="647">
       <c r="A647" t="n">
@@ -10780,11 +7550,6 @@
       <c r="C647" t="n">
         <v>7</v>
       </c>
-      <c r="D647" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
-      </c>
     </row>
     <row r="648">
       <c r="A648" t="n">
@@ -10796,11 +7561,6 @@
       <c r="C648" t="n">
         <v>252</v>
       </c>
-      <c r="D648" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
     </row>
     <row r="649">
       <c r="A649" t="n">
@@ -10812,11 +7572,6 @@
       <c r="C649" t="n">
         <v>24</v>
       </c>
-      <c r="D649" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="650">
       <c r="A650" t="n">
@@ -10828,11 +7583,6 @@
       <c r="C650" t="n">
         <v>102</v>
       </c>
-      <c r="D650" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="651">
       <c r="A651" t="n">
@@ -10844,11 +7594,6 @@
       <c r="C651" t="n">
         <v>61</v>
       </c>
-      <c r="D651" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="652">
       <c r="A652" t="n">
@@ -10860,11 +7605,6 @@
       <c r="C652" t="n">
         <v>174</v>
       </c>
-      <c r="D652" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="653">
       <c r="A653" t="n">
@@ -10876,11 +7616,6 @@
       <c r="C653" t="n">
         <v>118</v>
       </c>
-      <c r="D653" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="654">
       <c r="A654" t="n">
@@ -10892,11 +7627,6 @@
       <c r="C654" t="n">
         <v>437</v>
       </c>
-      <c r="D654" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="655">
       <c r="A655" t="n">
@@ -10908,11 +7638,6 @@
       <c r="C655" t="n">
         <v>50</v>
       </c>
-      <c r="D655" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
     </row>
     <row r="656">
       <c r="A656" t="n">
@@ -10924,11 +7649,6 @@
       <c r="C656" t="n">
         <v>159</v>
       </c>
-      <c r="D656" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="657">
       <c r="A657" t="n">
@@ -10940,11 +7660,6 @@
       <c r="C657" t="n">
         <v>298</v>
       </c>
-      <c r="D657" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="658">
       <c r="A658" t="n">
@@ -10956,11 +7671,6 @@
       <c r="C658" t="n">
         <v>45</v>
       </c>
-      <c r="D658" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="659">
       <c r="A659" t="n">
@@ -10972,11 +7682,6 @@
       <c r="C659" t="n">
         <v>136</v>
       </c>
-      <c r="D659" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
     </row>
     <row r="660">
       <c r="A660" t="n">
@@ -10987,11 +7692,6 @@
       </c>
       <c r="C660" t="n">
         <v>259</v>
-      </c>
-      <c r="D660" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/evolution/new_word_count_df.xlsx
+++ b/evolution/new_word_count_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C660"/>
+  <dimension ref="A1:D660"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>new_word_count</t>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Decade</t>
         </is>
       </c>
     </row>
@@ -455,6 +460,11 @@
       <c r="C2" t="n">
         <v>49</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -466,6 +476,11 @@
       <c r="C3" t="n">
         <v>41</v>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -477,6 +492,11 @@
       <c r="C4" t="n">
         <v>62</v>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -488,6 +508,11 @@
       <c r="C5" t="n">
         <v>50</v>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -499,6 +524,11 @@
       <c r="C6" t="n">
         <v>41</v>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -510,6 +540,11 @@
       <c r="C7" t="n">
         <v>66</v>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -521,6 +556,11 @@
       <c r="C8" t="n">
         <v>85</v>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -532,6 +572,11 @@
       <c r="C9" t="n">
         <v>25</v>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -543,6 +588,11 @@
       <c r="C10" t="n">
         <v>2</v>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -554,6 +604,11 @@
       <c r="C11" t="n">
         <v>58</v>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -565,6 +620,11 @@
       <c r="C12" t="n">
         <v>161</v>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -576,6 +636,11 @@
       <c r="C13" t="n">
         <v>75</v>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -587,6 +652,11 @@
       <c r="C14" t="n">
         <v>36</v>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -598,6 +668,11 @@
       <c r="C15" t="n">
         <v>74</v>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -609,6 +684,11 @@
       <c r="C16" t="n">
         <v>47</v>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -620,6 +700,11 @@
       <c r="C17" t="n">
         <v>50</v>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -631,6 +716,11 @@
       <c r="C18" t="n">
         <v>17</v>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -642,6 +732,11 @@
       <c r="C19" t="n">
         <v>28</v>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -653,6 +748,11 @@
       <c r="C20" t="n">
         <v>39</v>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -664,6 +764,11 @@
       <c r="C21" t="n">
         <v>39</v>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -675,6 +780,11 @@
       <c r="C22" t="n">
         <v>87</v>
       </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -686,6 +796,11 @@
       <c r="C23" t="n">
         <v>35</v>
       </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -697,6 +812,11 @@
       <c r="C24" t="n">
         <v>96</v>
       </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -708,6 +828,11 @@
       <c r="C25" t="n">
         <v>49</v>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -719,6 +844,11 @@
       <c r="C26" t="n">
         <v>67</v>
       </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -730,6 +860,11 @@
       <c r="C27" t="n">
         <v>13</v>
       </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -741,6 +876,11 @@
       <c r="C28" t="n">
         <v>125</v>
       </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -752,6 +892,11 @@
       <c r="C29" t="n">
         <v>134</v>
       </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -763,6 +908,11 @@
       <c r="C30" t="n">
         <v>139</v>
       </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -774,6 +924,11 @@
       <c r="C31" t="n">
         <v>204</v>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -785,6 +940,11 @@
       <c r="C32" t="n">
         <v>159</v>
       </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -796,6 +956,11 @@
       <c r="C33" t="n">
         <v>131</v>
       </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -807,6 +972,11 @@
       <c r="C34" t="n">
         <v>215</v>
       </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -818,6 +988,11 @@
       <c r="C35" t="n">
         <v>102</v>
       </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -829,6 +1004,11 @@
       <c r="C36" t="n">
         <v>145</v>
       </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -840,6 +1020,11 @@
       <c r="C37" t="n">
         <v>191</v>
       </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -851,6 +1036,11 @@
       <c r="C38" t="n">
         <v>165</v>
       </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -862,6 +1052,11 @@
       <c r="C39" t="n">
         <v>170</v>
       </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -873,6 +1068,11 @@
       <c r="C40" t="n">
         <v>218</v>
       </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -884,6 +1084,11 @@
       <c r="C41" t="n">
         <v>171</v>
       </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -895,6 +1100,11 @@
       <c r="C42" t="n">
         <v>194</v>
       </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -906,6 +1116,11 @@
       <c r="C43" t="n">
         <v>382</v>
       </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -917,6 +1132,11 @@
       <c r="C44" t="n">
         <v>91</v>
       </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -928,6 +1148,11 @@
       <c r="C45" t="n">
         <v>49</v>
       </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -939,6 +1164,11 @@
       <c r="C46" t="n">
         <v>180</v>
       </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -950,6 +1180,11 @@
       <c r="C47" t="n">
         <v>47</v>
       </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -961,6 +1196,11 @@
       <c r="C48" t="n">
         <v>26</v>
       </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -972,6 +1212,11 @@
       <c r="C49" t="n">
         <v>18</v>
       </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -983,6 +1228,11 @@
       <c r="C50" t="n">
         <v>132</v>
       </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -994,6 +1244,11 @@
       <c r="C51" t="n">
         <v>47</v>
       </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1005,6 +1260,11 @@
       <c r="C52" t="n">
         <v>111</v>
       </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1016,6 +1276,11 @@
       <c r="C53" t="n">
         <v>76</v>
       </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1027,6 +1292,11 @@
       <c r="C54" t="n">
         <v>31</v>
       </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1038,6 +1308,11 @@
       <c r="C55" t="n">
         <v>99</v>
       </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1049,6 +1324,11 @@
       <c r="C56" t="n">
         <v>68</v>
       </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1060,6 +1340,11 @@
       <c r="C57" t="n">
         <v>36</v>
       </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1071,6 +1356,11 @@
       <c r="C58" t="n">
         <v>123</v>
       </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1082,6 +1372,11 @@
       <c r="C59" t="n">
         <v>130</v>
       </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1093,6 +1388,11 @@
       <c r="C60" t="n">
         <v>192</v>
       </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1104,6 +1404,11 @@
       <c r="C61" t="n">
         <v>123</v>
       </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1115,6 +1420,11 @@
       <c r="C62" t="n">
         <v>152</v>
       </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1126,6 +1436,11 @@
       <c r="C63" t="n">
         <v>217</v>
       </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1137,6 +1452,11 @@
       <c r="C64" t="n">
         <v>167</v>
       </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1148,6 +1468,11 @@
       <c r="C65" t="n">
         <v>190</v>
       </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1159,6 +1484,11 @@
       <c r="C66" t="n">
         <v>175</v>
       </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1170,6 +1500,11 @@
       <c r="C67" t="n">
         <v>234</v>
       </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1181,6 +1516,11 @@
       <c r="C68" t="n">
         <v>550</v>
       </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1192,6 +1532,11 @@
       <c r="C69" t="n">
         <v>419</v>
       </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1203,6 +1548,11 @@
       <c r="C70" t="n">
         <v>420</v>
       </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1214,6 +1564,11 @@
       <c r="C71" t="n">
         <v>636</v>
       </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1225,6 +1580,11 @@
       <c r="C72" t="n">
         <v>702</v>
       </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1236,6 +1596,11 @@
       <c r="C73" t="n">
         <v>5</v>
       </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1247,6 +1612,11 @@
       <c r="C74" t="n">
         <v>6</v>
       </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1258,6 +1628,11 @@
       <c r="C75" t="n">
         <v>147</v>
       </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -1269,6 +1644,11 @@
       <c r="C76" t="n">
         <v>44</v>
       </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1280,6 +1660,11 @@
       <c r="C77" t="n">
         <v>117</v>
       </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1291,6 +1676,11 @@
       <c r="C78" t="n">
         <v>148</v>
       </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -1302,6 +1692,11 @@
       <c r="C79" t="n">
         <v>40</v>
       </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -1313,6 +1708,11 @@
       <c r="C80" t="n">
         <v>36</v>
       </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -1324,6 +1724,11 @@
       <c r="C81" t="n">
         <v>72</v>
       </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -1335,6 +1740,11 @@
       <c r="C82" t="n">
         <v>53</v>
       </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -1346,6 +1756,11 @@
       <c r="C83" t="n">
         <v>25</v>
       </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -1357,6 +1772,11 @@
       <c r="C84" t="n">
         <v>47</v>
       </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -1368,6 +1788,11 @@
       <c r="C85" t="n">
         <v>71</v>
       </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -1379,6 +1804,11 @@
       <c r="C86" t="n">
         <v>128</v>
       </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -1390,6 +1820,11 @@
       <c r="C87" t="n">
         <v>112</v>
       </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -1401,6 +1836,11 @@
       <c r="C88" t="n">
         <v>61</v>
       </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -1412,6 +1852,11 @@
       <c r="C89" t="n">
         <v>55</v>
       </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -1423,6 +1868,11 @@
       <c r="C90" t="n">
         <v>139</v>
       </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -1434,6 +1884,11 @@
       <c r="C91" t="n">
         <v>115</v>
       </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -1445,6 +1900,11 @@
       <c r="C92" t="n">
         <v>121</v>
       </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -1456,6 +1916,11 @@
       <c r="C93" t="n">
         <v>110</v>
       </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -1467,6 +1932,11 @@
       <c r="C94" t="n">
         <v>97</v>
       </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -1478,6 +1948,11 @@
       <c r="C95" t="n">
         <v>41</v>
       </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -1489,6 +1964,11 @@
       <c r="C96" t="n">
         <v>18</v>
       </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -1500,6 +1980,11 @@
       <c r="C97" t="n">
         <v>74</v>
       </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -1511,6 +1996,11 @@
       <c r="C98" t="n">
         <v>9</v>
       </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -1522,6 +2012,11 @@
       <c r="C99" t="n">
         <v>94</v>
       </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -1533,6 +2028,11 @@
       <c r="C100" t="n">
         <v>125</v>
       </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -1544,6 +2044,11 @@
       <c r="C101" t="n">
         <v>69</v>
       </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -1555,6 +2060,11 @@
       <c r="C102" t="n">
         <v>78</v>
       </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -1566,6 +2076,11 @@
       <c r="C103" t="n">
         <v>209</v>
       </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -1577,6 +2092,11 @@
       <c r="C104" t="n">
         <v>92</v>
       </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -1588,6 +2108,11 @@
       <c r="C105" t="n">
         <v>197</v>
       </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -1599,6 +2124,11 @@
       <c r="C106" t="n">
         <v>81</v>
       </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -1610,6 +2140,11 @@
       <c r="C107" t="n">
         <v>122</v>
       </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -1621,6 +2156,11 @@
       <c r="C108" t="n">
         <v>141</v>
       </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -1632,6 +2172,11 @@
       <c r="C109" t="n">
         <v>82</v>
       </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -1643,6 +2188,11 @@
       <c r="C110" t="n">
         <v>204</v>
       </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -1654,6 +2204,11 @@
       <c r="C111" t="n">
         <v>109</v>
       </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -1665,6 +2220,11 @@
       <c r="C112" t="n">
         <v>171</v>
       </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -1676,6 +2236,11 @@
       <c r="C113" t="n">
         <v>60</v>
       </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -1687,6 +2252,11 @@
       <c r="C114" t="n">
         <v>72</v>
       </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -1698,6 +2268,11 @@
       <c r="C115" t="n">
         <v>151</v>
       </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -1709,6 +2284,11 @@
       <c r="C116" t="n">
         <v>143</v>
       </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -1720,6 +2300,11 @@
       <c r="C117" t="n">
         <v>6</v>
       </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -1731,6 +2316,11 @@
       <c r="C118" t="n">
         <v>54</v>
       </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -1742,6 +2332,11 @@
       <c r="C119" t="n">
         <v>52</v>
       </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -1753,6 +2348,11 @@
       <c r="C120" t="n">
         <v>10</v>
       </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -1764,6 +2364,11 @@
       <c r="C121" t="n">
         <v>52</v>
       </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -1775,6 +2380,11 @@
       <c r="C122" t="n">
         <v>52</v>
       </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -1786,6 +2396,11 @@
       <c r="C123" t="n">
         <v>22</v>
       </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -1797,6 +2412,11 @@
       <c r="C124" t="n">
         <v>92</v>
       </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -1808,6 +2428,11 @@
       <c r="C125" t="n">
         <v>86</v>
       </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -1819,6 +2444,11 @@
       <c r="C126" t="n">
         <v>77</v>
       </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -1830,6 +2460,11 @@
       <c r="C127" t="n">
         <v>70</v>
       </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -1841,6 +2476,11 @@
       <c r="C128" t="n">
         <v>130</v>
       </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -1852,6 +2492,11 @@
       <c r="C129" t="n">
         <v>80</v>
       </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -1863,6 +2508,11 @@
       <c r="C130" t="n">
         <v>113</v>
       </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -1874,6 +2524,11 @@
       <c r="C131" t="n">
         <v>140</v>
       </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -1885,6 +2540,11 @@
       <c r="C132" t="n">
         <v>142</v>
       </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -1896,6 +2556,11 @@
       <c r="C133" t="n">
         <v>86</v>
       </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -1907,6 +2572,11 @@
       <c r="C134" t="n">
         <v>109</v>
       </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -1918,6 +2588,11 @@
       <c r="C135" t="n">
         <v>80</v>
       </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -1929,6 +2604,11 @@
       <c r="C136" t="n">
         <v>62</v>
       </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -1940,6 +2620,11 @@
       <c r="C137" t="n">
         <v>41</v>
       </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -1951,6 +2636,11 @@
       <c r="C138" t="n">
         <v>139</v>
       </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -1962,6 +2652,11 @@
       <c r="C139" t="n">
         <v>147</v>
       </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -1973,6 +2668,11 @@
       <c r="C140" t="n">
         <v>135</v>
       </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -1984,6 +2684,11 @@
       <c r="C141" t="n">
         <v>131</v>
       </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -1995,6 +2700,11 @@
       <c r="C142" t="n">
         <v>81</v>
       </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -2006,6 +2716,11 @@
       <c r="C143" t="n">
         <v>166</v>
       </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -2017,6 +2732,11 @@
       <c r="C144" t="n">
         <v>156</v>
       </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -2028,6 +2748,11 @@
       <c r="C145" t="n">
         <v>155</v>
       </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -2039,6 +2764,11 @@
       <c r="C146" t="n">
         <v>179</v>
       </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -2050,6 +2780,11 @@
       <c r="C147" t="n">
         <v>78</v>
       </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -2061,6 +2796,11 @@
       <c r="C148" t="n">
         <v>176</v>
       </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -2072,6 +2812,11 @@
       <c r="C149" t="n">
         <v>333</v>
       </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -2083,6 +2828,11 @@
       <c r="C150" t="n">
         <v>60</v>
       </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -2094,6 +2844,11 @@
       <c r="C151" t="n">
         <v>101</v>
       </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -2105,6 +2860,11 @@
       <c r="C152" t="n">
         <v>67</v>
       </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -2116,6 +2876,11 @@
       <c r="C153" t="n">
         <v>32</v>
       </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -2127,6 +2892,11 @@
       <c r="C154" t="n">
         <v>26</v>
       </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -2138,6 +2908,11 @@
       <c r="C155" t="n">
         <v>121</v>
       </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -2149,6 +2924,11 @@
       <c r="C156" t="n">
         <v>35</v>
       </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -2160,6 +2940,11 @@
       <c r="C157" t="n">
         <v>28</v>
       </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -2171,6 +2956,11 @@
       <c r="C158" t="n">
         <v>32</v>
       </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -2182,6 +2972,11 @@
       <c r="C159" t="n">
         <v>30</v>
       </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -2193,6 +2988,11 @@
       <c r="C160" t="n">
         <v>106</v>
       </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -2204,6 +3004,11 @@
       <c r="C161" t="n">
         <v>48</v>
       </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -2215,6 +3020,11 @@
       <c r="C162" t="n">
         <v>40</v>
       </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -2226,6 +3036,11 @@
       <c r="C163" t="n">
         <v>86</v>
       </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -2237,6 +3052,11 @@
       <c r="C164" t="n">
         <v>36</v>
       </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -2248,6 +3068,11 @@
       <c r="C165" t="n">
         <v>45</v>
       </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -2259,6 +3084,11 @@
       <c r="C166" t="n">
         <v>184</v>
       </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -2270,6 +3100,11 @@
       <c r="C167" t="n">
         <v>44</v>
       </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -2281,6 +3116,11 @@
       <c r="C168" t="n">
         <v>117</v>
       </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -2292,6 +3132,11 @@
       <c r="C169" t="n">
         <v>208</v>
       </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -2303,6 +3148,11 @@
       <c r="C170" t="n">
         <v>58</v>
       </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -2314,6 +3164,11 @@
       <c r="C171" t="n">
         <v>305</v>
       </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -2325,6 +3180,11 @@
       <c r="C172" t="n">
         <v>295</v>
       </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -2336,6 +3196,11 @@
       <c r="C173" t="n">
         <v>102</v>
       </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -2347,6 +3212,11 @@
       <c r="C174" t="n">
         <v>326</v>
       </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -2358,6 +3228,11 @@
       <c r="C175" t="n">
         <v>286</v>
       </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -2369,6 +3244,11 @@
       <c r="C176" t="n">
         <v>191</v>
       </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -2380,6 +3260,11 @@
       <c r="C177" t="n">
         <v>295</v>
       </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -2391,6 +3276,11 @@
       <c r="C178" t="n">
         <v>353</v>
       </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -2402,6 +3292,11 @@
       <c r="C179" t="n">
         <v>349</v>
       </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -2413,6 +3308,11 @@
       <c r="C180" t="n">
         <v>518</v>
       </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -2424,6 +3324,11 @@
       <c r="C181" t="n">
         <v>459</v>
       </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -2435,6 +3340,11 @@
       <c r="C182" t="n">
         <v>445</v>
       </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -2446,6 +3356,11 @@
       <c r="C183" t="n">
         <v>11</v>
       </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -2457,6 +3372,11 @@
       <c r="C184" t="n">
         <v>11</v>
       </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -2468,6 +3388,11 @@
       <c r="C185" t="n">
         <v>108</v>
       </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -2479,6 +3404,11 @@
       <c r="C186" t="n">
         <v>72</v>
       </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -2490,6 +3420,11 @@
       <c r="C187" t="n">
         <v>47</v>
       </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -2501,6 +3436,11 @@
       <c r="C188" t="n">
         <v>54</v>
       </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -2512,6 +3452,11 @@
       <c r="C189" t="n">
         <v>46</v>
       </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -2523,6 +3468,11 @@
       <c r="C190" t="n">
         <v>104</v>
       </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -2534,6 +3484,11 @@
       <c r="C191" t="n">
         <v>55</v>
       </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -2545,6 +3500,11 @@
       <c r="C192" t="n">
         <v>76</v>
       </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -2556,6 +3516,11 @@
       <c r="C193" t="n">
         <v>51</v>
       </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -2567,6 +3532,11 @@
       <c r="C194" t="n">
         <v>63</v>
       </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -2578,6 +3548,11 @@
       <c r="C195" t="n">
         <v>107</v>
       </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -2589,6 +3564,11 @@
       <c r="C196" t="n">
         <v>35</v>
       </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -2600,6 +3580,11 @@
       <c r="C197" t="n">
         <v>95</v>
       </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -2611,6 +3596,11 @@
       <c r="C198" t="n">
         <v>25</v>
       </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -2622,6 +3612,11 @@
       <c r="C199" t="n">
         <v>61</v>
       </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -2633,6 +3628,11 @@
       <c r="C200" t="n">
         <v>56</v>
       </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -2644,6 +3644,11 @@
       <c r="C201" t="n">
         <v>87</v>
       </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -2655,6 +3660,11 @@
       <c r="C202" t="n">
         <v>66</v>
       </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -2666,6 +3676,11 @@
       <c r="C203" t="n">
         <v>127</v>
       </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -2677,6 +3692,11 @@
       <c r="C204" t="n">
         <v>211</v>
       </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -2688,6 +3708,11 @@
       <c r="C205" t="n">
         <v>89</v>
       </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -2699,6 +3724,11 @@
       <c r="C206" t="n">
         <v>106</v>
       </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -2710,6 +3740,11 @@
       <c r="C207" t="n">
         <v>74</v>
       </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -2721,6 +3756,11 @@
       <c r="C208" t="n">
         <v>127</v>
       </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -2732,6 +3772,11 @@
       <c r="C209" t="n">
         <v>88</v>
       </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -2743,6 +3788,11 @@
       <c r="C210" t="n">
         <v>104</v>
       </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -2754,6 +3804,11 @@
       <c r="C211" t="n">
         <v>159</v>
       </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -2765,6 +3820,11 @@
       <c r="C212" t="n">
         <v>115</v>
       </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -2776,6 +3836,11 @@
       <c r="C213" t="n">
         <v>162</v>
       </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -2787,6 +3852,11 @@
       <c r="C214" t="n">
         <v>228</v>
       </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -2798,6 +3868,11 @@
       <c r="C215" t="n">
         <v>348</v>
       </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -2809,6 +3884,11 @@
       <c r="C216" t="n">
         <v>7</v>
       </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -2820,6 +3900,11 @@
       <c r="C217" t="n">
         <v>54</v>
       </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -2831,6 +3916,11 @@
       <c r="C218" t="n">
         <v>2</v>
       </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -2842,6 +3932,11 @@
       <c r="C219" t="n">
         <v>10</v>
       </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -2853,6 +3948,11 @@
       <c r="C220" t="n">
         <v>10</v>
       </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -2864,6 +3964,11 @@
       <c r="C221" t="n">
         <v>6</v>
       </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -2875,6 +3980,11 @@
       <c r="C222" t="n">
         <v>65</v>
       </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -2886,6 +3996,11 @@
       <c r="C223" t="n">
         <v>162</v>
       </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -2897,6 +4012,11 @@
       <c r="C224" t="n">
         <v>81</v>
       </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -2908,6 +4028,11 @@
       <c r="C225" t="n">
         <v>91</v>
       </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -2919,6 +4044,11 @@
       <c r="C226" t="n">
         <v>52</v>
       </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -2930,6 +4060,11 @@
       <c r="C227" t="n">
         <v>141</v>
       </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -2941,6 +4076,11 @@
       <c r="C228" t="n">
         <v>15</v>
       </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -2952,6 +4092,11 @@
       <c r="C229" t="n">
         <v>113</v>
       </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -2963,6 +4108,11 @@
       <c r="C230" t="n">
         <v>49</v>
       </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -2974,6 +4124,11 @@
       <c r="C231" t="n">
         <v>49</v>
       </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -2985,6 +4140,11 @@
       <c r="C232" t="n">
         <v>29</v>
       </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -2996,6 +4156,11 @@
       <c r="C233" t="n">
         <v>23</v>
       </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -3007,6 +4172,11 @@
       <c r="C234" t="n">
         <v>20</v>
       </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -3018,6 +4188,11 @@
       <c r="C235" t="n">
         <v>108</v>
       </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -3029,6 +4204,11 @@
       <c r="C236" t="n">
         <v>176</v>
       </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -3040,6 +4220,11 @@
       <c r="C237" t="n">
         <v>191</v>
       </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -3051,6 +4236,11 @@
       <c r="C238" t="n">
         <v>141</v>
       </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -3062,6 +4252,11 @@
       <c r="C239" t="n">
         <v>249</v>
       </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -3073,6 +4268,11 @@
       <c r="C240" t="n">
         <v>106</v>
       </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -3084,6 +4284,11 @@
       <c r="C241" t="n">
         <v>153</v>
       </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -3095,6 +4300,11 @@
       <c r="C242" t="n">
         <v>99</v>
       </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -3106,6 +4316,11 @@
       <c r="C243" t="n">
         <v>183</v>
       </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -3117,6 +4332,11 @@
       <c r="C244" t="n">
         <v>121</v>
       </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -3128,6 +4348,11 @@
       <c r="C245" t="n">
         <v>95</v>
       </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -3139,6 +4364,11 @@
       <c r="C246" t="n">
         <v>259</v>
       </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -3150,6 +4380,11 @@
       <c r="C247" t="n">
         <v>75</v>
       </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -3161,6 +4396,11 @@
       <c r="C248" t="n">
         <v>294</v>
       </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -3172,6 +4412,11 @@
       <c r="C249" t="n">
         <v>194</v>
       </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -3183,6 +4428,11 @@
       <c r="C250" t="n">
         <v>65</v>
       </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -3194,6 +4444,11 @@
       <c r="C251" t="n">
         <v>45</v>
       </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -3205,6 +4460,11 @@
       <c r="C252" t="n">
         <v>81</v>
       </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -3216,6 +4476,11 @@
       <c r="C253" t="n">
         <v>45</v>
       </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -3227,6 +4492,11 @@
       <c r="C254" t="n">
         <v>75</v>
       </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -3238,6 +4508,11 @@
       <c r="C255" t="n">
         <v>96</v>
       </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -3249,6 +4524,11 @@
       <c r="C256" t="n">
         <v>30</v>
       </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -3260,6 +4540,11 @@
       <c r="C257" t="n">
         <v>34</v>
       </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -3271,6 +4556,11 @@
       <c r="C258" t="n">
         <v>55</v>
       </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -3282,6 +4572,11 @@
       <c r="C259" t="n">
         <v>247</v>
       </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -3293,6 +4588,11 @@
       <c r="C260" t="n">
         <v>24</v>
       </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -3304,6 +4604,11 @@
       <c r="C261" t="n">
         <v>271</v>
       </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -3315,6 +4620,11 @@
       <c r="C262" t="n">
         <v>78</v>
       </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -3326,6 +4636,11 @@
       <c r="C263" t="n">
         <v>114</v>
       </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -3337,6 +4652,11 @@
       <c r="C264" t="n">
         <v>146</v>
       </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -3348,6 +4668,11 @@
       <c r="C265" t="n">
         <v>134</v>
       </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -3359,6 +4684,11 @@
       <c r="C266" t="n">
         <v>94</v>
       </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -3370,6 +4700,11 @@
       <c r="C267" t="n">
         <v>43</v>
       </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -3381,6 +4716,11 @@
       <c r="C268" t="n">
         <v>26</v>
       </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -3392,6 +4732,11 @@
       <c r="C269" t="n">
         <v>184</v>
       </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -3403,6 +4748,11 @@
       <c r="C270" t="n">
         <v>68</v>
       </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -3414,6 +4764,11 @@
       <c r="C271" t="n">
         <v>97</v>
       </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -3425,6 +4780,11 @@
       <c r="C272" t="n">
         <v>29</v>
       </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -3436,6 +4796,11 @@
       <c r="C273" t="n">
         <v>53</v>
       </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -3447,6 +4812,11 @@
       <c r="C274" t="n">
         <v>98</v>
       </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -3458,6 +4828,11 @@
       <c r="C275" t="n">
         <v>210</v>
       </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -3469,6 +4844,11 @@
       <c r="C276" t="n">
         <v>118</v>
       </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -3480,6 +4860,11 @@
       <c r="C277" t="n">
         <v>120</v>
       </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -3491,6 +4876,11 @@
       <c r="C278" t="n">
         <v>65</v>
       </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -3502,6 +4892,11 @@
       <c r="C279" t="n">
         <v>105</v>
       </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -3513,6 +4908,11 @@
       <c r="C280" t="n">
         <v>119</v>
       </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -3524,6 +4924,11 @@
       <c r="C281" t="n">
         <v>236</v>
       </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -3535,6 +4940,11 @@
       <c r="C282" t="n">
         <v>283</v>
       </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -3546,6 +4956,11 @@
       <c r="C283" t="n">
         <v>183</v>
       </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -3557,6 +4972,11 @@
       <c r="C284" t="n">
         <v>117</v>
       </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -3568,6 +4988,11 @@
       <c r="C285" t="n">
         <v>407</v>
       </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -3579,6 +5004,11 @@
       <c r="C286" t="n">
         <v>211</v>
       </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -3590,6 +5020,11 @@
       <c r="C287" t="n">
         <v>72</v>
       </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -3601,6 +5036,11 @@
       <c r="C288" t="n">
         <v>54</v>
       </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -3612,6 +5052,11 @@
       <c r="C289" t="n">
         <v>136</v>
       </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -3623,6 +5068,11 @@
       <c r="C290" t="n">
         <v>203</v>
       </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -3634,6 +5084,11 @@
       <c r="C291" t="n">
         <v>19</v>
       </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -3645,6 +5100,11 @@
       <c r="C292" t="n">
         <v>59</v>
       </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -3656,6 +5116,11 @@
       <c r="C293" t="n">
         <v>70</v>
       </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -3667,6 +5132,11 @@
       <c r="C294" t="n">
         <v>20</v>
       </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -3678,6 +5148,11 @@
       <c r="C295" t="n">
         <v>71</v>
       </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -3689,6 +5164,11 @@
       <c r="C296" t="n">
         <v>5</v>
       </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -3700,6 +5180,11 @@
       <c r="C297" t="n">
         <v>18</v>
       </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -3711,6 +5196,11 @@
       <c r="C298" t="n">
         <v>31</v>
       </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -3722,6 +5212,11 @@
       <c r="C299" t="n">
         <v>50</v>
       </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -3733,6 +5228,11 @@
       <c r="C300" t="n">
         <v>68</v>
       </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -3744,6 +5244,11 @@
       <c r="C301" t="n">
         <v>109</v>
       </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -3755,6 +5260,11 @@
       <c r="C302" t="n">
         <v>184</v>
       </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -3766,6 +5276,11 @@
       <c r="C303" t="n">
         <v>108</v>
       </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -3777,6 +5292,11 @@
       <c r="C304" t="n">
         <v>130</v>
       </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -3788,6 +5308,11 @@
       <c r="C305" t="n">
         <v>42</v>
       </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -3799,6 +5324,11 @@
       <c r="C306" t="n">
         <v>191</v>
       </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -3810,6 +5340,11 @@
       <c r="C307" t="n">
         <v>122</v>
       </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -3821,6 +5356,11 @@
       <c r="C308" t="n">
         <v>115</v>
       </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -3832,6 +5372,11 @@
       <c r="C309" t="n">
         <v>137</v>
       </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -3843,6 +5388,11 @@
       <c r="C310" t="n">
         <v>137</v>
       </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -3854,6 +5404,11 @@
       <c r="C311" t="n">
         <v>112</v>
       </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -3865,6 +5420,11 @@
       <c r="C312" t="n">
         <v>132</v>
       </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -3876,6 +5436,11 @@
       <c r="C313" t="n">
         <v>225</v>
       </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -3887,6 +5452,11 @@
       <c r="C314" t="n">
         <v>62</v>
       </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -3898,6 +5468,11 @@
       <c r="C315" t="n">
         <v>39</v>
       </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -3909,6 +5484,11 @@
       <c r="C316" t="n">
         <v>98</v>
       </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -3920,6 +5500,11 @@
       <c r="C317" t="n">
         <v>53</v>
       </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -3931,6 +5516,11 @@
       <c r="C318" t="n">
         <v>37</v>
       </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -3942,6 +5532,11 @@
       <c r="C319" t="n">
         <v>56</v>
       </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -3953,6 +5548,11 @@
       <c r="C320" t="n">
         <v>71</v>
       </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -3964,6 +5564,11 @@
       <c r="C321" t="n">
         <v>29</v>
       </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -3975,6 +5580,11 @@
       <c r="C322" t="n">
         <v>25</v>
       </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -3986,6 +5596,11 @@
       <c r="C323" t="n">
         <v>39</v>
       </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -3997,6 +5612,11 @@
       <c r="C324" t="n">
         <v>75</v>
       </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -4008,6 +5628,11 @@
       <c r="C325" t="n">
         <v>119</v>
       </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -4019,6 +5644,11 @@
       <c r="C326" t="n">
         <v>198</v>
       </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -4030,6 +5660,11 @@
       <c r="C327" t="n">
         <v>92</v>
       </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -4041,6 +5676,11 @@
       <c r="C328" t="n">
         <v>66</v>
       </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -4052,6 +5692,11 @@
       <c r="C329" t="n">
         <v>131</v>
       </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -4063,6 +5708,11 @@
       <c r="C330" t="n">
         <v>158</v>
       </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -4074,6 +5724,11 @@
       <c r="C331" t="n">
         <v>78</v>
       </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -4085,6 +5740,11 @@
       <c r="C332" t="n">
         <v>210</v>
       </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -4096,6 +5756,11 @@
       <c r="C333" t="n">
         <v>69</v>
       </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -4107,6 +5772,11 @@
       <c r="C334" t="n">
         <v>330</v>
       </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -4118,6 +5788,11 @@
       <c r="C335" t="n">
         <v>12</v>
       </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -4129,6 +5804,11 @@
       <c r="C336" t="n">
         <v>3</v>
       </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -4140,6 +5820,11 @@
       <c r="C337" t="n">
         <v>6</v>
       </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -4151,6 +5836,11 @@
       <c r="C338" t="n">
         <v>5</v>
       </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -4162,6 +5852,11 @@
       <c r="C339" t="n">
         <v>42</v>
       </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -4173,6 +5868,11 @@
       <c r="C340" t="n">
         <v>2</v>
       </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -4184,6 +5884,11 @@
       <c r="C341" t="n">
         <v>13</v>
       </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -4195,6 +5900,11 @@
       <c r="C342" t="n">
         <v>35</v>
       </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -4206,6 +5916,11 @@
       <c r="C343" t="n">
         <v>126</v>
       </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -4217,6 +5932,11 @@
       <c r="C344" t="n">
         <v>19</v>
       </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -4228,6 +5948,11 @@
       <c r="C345" t="n">
         <v>97</v>
       </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -4239,6 +5964,11 @@
       <c r="C346" t="n">
         <v>53</v>
       </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -4250,6 +5980,11 @@
       <c r="C347" t="n">
         <v>16</v>
       </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -4261,6 +5996,11 @@
       <c r="C348" t="n">
         <v>94</v>
       </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -4272,6 +6012,11 @@
       <c r="C349" t="n">
         <v>53</v>
       </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -4283,6 +6028,11 @@
       <c r="C350" t="n">
         <v>34</v>
       </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -4294,6 +6044,11 @@
       <c r="C351" t="n">
         <v>43</v>
       </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -4305,6 +6060,11 @@
       <c r="C352" t="n">
         <v>53</v>
       </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -4316,6 +6076,11 @@
       <c r="C353" t="n">
         <v>50</v>
       </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -4327,6 +6092,11 @@
       <c r="C354" t="n">
         <v>82</v>
       </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -4338,6 +6108,11 @@
       <c r="C355" t="n">
         <v>99</v>
       </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -4349,6 +6124,11 @@
       <c r="C356" t="n">
         <v>65</v>
       </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -4360,6 +6140,11 @@
       <c r="C357" t="n">
         <v>168</v>
       </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -4371,6 +6156,11 @@
       <c r="C358" t="n">
         <v>234</v>
       </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -4382,6 +6172,11 @@
       <c r="C359" t="n">
         <v>197</v>
       </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -4393,6 +6188,11 @@
       <c r="C360" t="n">
         <v>201</v>
       </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -4404,6 +6204,11 @@
       <c r="C361" t="n">
         <v>153</v>
       </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -4415,6 +6220,11 @@
       <c r="C362" t="n">
         <v>50</v>
       </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -4426,6 +6236,11 @@
       <c r="C363" t="n">
         <v>232</v>
       </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -4437,6 +6252,11 @@
       <c r="C364" t="n">
         <v>26</v>
       </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -4448,6 +6268,11 @@
       <c r="C365" t="n">
         <v>164</v>
       </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -4459,6 +6284,11 @@
       <c r="C366" t="n">
         <v>51</v>
       </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -4470,6 +6300,11 @@
       <c r="C367" t="n">
         <v>41</v>
       </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -4481,6 +6316,11 @@
       <c r="C368" t="n">
         <v>136</v>
       </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -4492,6 +6332,11 @@
       <c r="C369" t="n">
         <v>7</v>
       </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -4503,6 +6348,11 @@
       <c r="C370" t="n">
         <v>78</v>
       </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -4514,6 +6364,11 @@
       <c r="C371" t="n">
         <v>69</v>
       </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -4525,6 +6380,11 @@
       <c r="C372" t="n">
         <v>24</v>
       </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -4536,6 +6396,11 @@
       <c r="C373" t="n">
         <v>45</v>
       </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -4547,6 +6412,11 @@
       <c r="C374" t="n">
         <v>120</v>
       </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -4558,6 +6428,11 @@
       <c r="C375" t="n">
         <v>45</v>
       </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -4569,6 +6444,11 @@
       <c r="C376" t="n">
         <v>15</v>
       </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -4580,6 +6460,11 @@
       <c r="C377" t="n">
         <v>29</v>
       </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -4591,6 +6476,11 @@
       <c r="C378" t="n">
         <v>51</v>
       </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -4602,6 +6492,11 @@
       <c r="C379" t="n">
         <v>41</v>
       </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -4613,6 +6508,11 @@
       <c r="C380" t="n">
         <v>54</v>
       </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -4624,6 +6524,11 @@
       <c r="C381" t="n">
         <v>103</v>
       </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -4635,6 +6540,11 @@
       <c r="C382" t="n">
         <v>53</v>
       </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -4646,6 +6556,11 @@
       <c r="C383" t="n">
         <v>91</v>
       </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -4657,6 +6572,11 @@
       <c r="C384" t="n">
         <v>73</v>
       </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -4668,6 +6588,11 @@
       <c r="C385" t="n">
         <v>92</v>
       </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -4679,6 +6604,11 @@
       <c r="C386" t="n">
         <v>55</v>
       </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -4690,6 +6620,11 @@
       <c r="C387" t="n">
         <v>12</v>
       </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -4701,6 +6636,11 @@
       <c r="C388" t="n">
         <v>104</v>
       </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -4712,6 +6652,11 @@
       <c r="C389" t="n">
         <v>26</v>
       </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -4723,6 +6668,11 @@
       <c r="C390" t="n">
         <v>121</v>
       </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -4734,6 +6684,11 @@
       <c r="C391" t="n">
         <v>110</v>
       </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -4745,6 +6700,11 @@
       <c r="C392" t="n">
         <v>181</v>
       </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -4756,6 +6716,11 @@
       <c r="C393" t="n">
         <v>137</v>
       </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -4767,6 +6732,11 @@
       <c r="C394" t="n">
         <v>107</v>
       </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -4778,6 +6748,11 @@
       <c r="C395" t="n">
         <v>82</v>
       </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -4789,6 +6764,11 @@
       <c r="C396" t="n">
         <v>11</v>
       </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -4800,6 +6780,11 @@
       <c r="C397" t="n">
         <v>57</v>
       </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -4811,6 +6796,11 @@
       <c r="C398" t="n">
         <v>41</v>
       </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -4822,6 +6812,11 @@
       <c r="C399" t="n">
         <v>45</v>
       </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -4833,6 +6828,11 @@
       <c r="C400" t="n">
         <v>99</v>
       </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -4844,6 +6844,11 @@
       <c r="C401" t="n">
         <v>57</v>
       </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -4855,6 +6860,11 @@
       <c r="C402" t="n">
         <v>181</v>
       </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -4866,6 +6876,11 @@
       <c r="C403" t="n">
         <v>18</v>
       </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -4877,6 +6892,11 @@
       <c r="C404" t="n">
         <v>52</v>
       </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -4888,6 +6908,11 @@
       <c r="C405" t="n">
         <v>18</v>
       </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -4899,6 +6924,11 @@
       <c r="C406" t="n">
         <v>44</v>
       </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -4910,6 +6940,11 @@
       <c r="C407" t="n">
         <v>10</v>
       </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -4921,6 +6956,11 @@
       <c r="C408" t="n">
         <v>74</v>
       </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -4932,6 +6972,11 @@
       <c r="C409" t="n">
         <v>53</v>
       </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -4943,6 +6988,11 @@
       <c r="C410" t="n">
         <v>24</v>
       </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -4954,6 +7004,11 @@
       <c r="C411" t="n">
         <v>46</v>
       </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -4965,6 +7020,11 @@
       <c r="C412" t="n">
         <v>55</v>
       </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -4976,6 +7036,11 @@
       <c r="C413" t="n">
         <v>75</v>
       </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -4987,6 +7052,11 @@
       <c r="C414" t="n">
         <v>53</v>
       </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -4998,6 +7068,11 @@
       <c r="C415" t="n">
         <v>46</v>
       </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -5009,6 +7084,11 @@
       <c r="C416" t="n">
         <v>28</v>
       </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -5020,6 +7100,11 @@
       <c r="C417" t="n">
         <v>100</v>
       </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -5031,6 +7116,11 @@
       <c r="C418" t="n">
         <v>106</v>
       </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -5042,6 +7132,11 @@
       <c r="C419" t="n">
         <v>134</v>
       </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -5053,6 +7148,11 @@
       <c r="C420" t="n">
         <v>6</v>
       </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -5064,6 +7164,11 @@
       <c r="C421" t="n">
         <v>126</v>
       </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -5075,6 +7180,11 @@
       <c r="C422" t="n">
         <v>36</v>
       </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -5086,6 +7196,11 @@
       <c r="C423" t="n">
         <v>34</v>
       </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -5097,6 +7212,11 @@
       <c r="C424" t="n">
         <v>111</v>
       </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -5108,6 +7228,11 @@
       <c r="C425" t="n">
         <v>115</v>
       </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -5119,6 +7244,11 @@
       <c r="C426" t="n">
         <v>70</v>
       </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -5130,6 +7260,11 @@
       <c r="C427" t="n">
         <v>125</v>
       </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -5141,6 +7276,11 @@
       <c r="C428" t="n">
         <v>96</v>
       </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -5152,6 +7292,11 @@
       <c r="C429" t="n">
         <v>48</v>
       </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -5163,6 +7308,11 @@
       <c r="C430" t="n">
         <v>55</v>
       </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -5174,6 +7324,11 @@
       <c r="C431" t="n">
         <v>84</v>
       </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -5185,6 +7340,11 @@
       <c r="C432" t="n">
         <v>29</v>
       </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -5196,6 +7356,11 @@
       <c r="C433" t="n">
         <v>128</v>
       </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -5207,6 +7372,11 @@
       <c r="C434" t="n">
         <v>78</v>
       </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -5218,6 +7388,11 @@
       <c r="C435" t="n">
         <v>139</v>
       </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -5229,6 +7404,11 @@
       <c r="C436" t="n">
         <v>158</v>
       </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -5240,6 +7420,11 @@
       <c r="C437" t="n">
         <v>73</v>
       </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -5251,6 +7436,11 @@
       <c r="C438" t="n">
         <v>151</v>
       </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -5262,6 +7452,11 @@
       <c r="C439" t="n">
         <v>206</v>
       </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -5273,6 +7468,11 @@
       <c r="C440" t="n">
         <v>182</v>
       </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -5284,6 +7484,11 @@
       <c r="C441" t="n">
         <v>104</v>
       </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -5295,6 +7500,11 @@
       <c r="C442" t="n">
         <v>30</v>
       </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -5306,6 +7516,11 @@
       <c r="C443" t="n">
         <v>48</v>
       </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -5317,6 +7532,11 @@
       <c r="C444" t="n">
         <v>64</v>
       </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -5328,6 +7548,11 @@
       <c r="C445" t="n">
         <v>128</v>
       </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -5339,6 +7564,11 @@
       <c r="C446" t="n">
         <v>124</v>
       </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -5350,6 +7580,11 @@
       <c r="C447" t="n">
         <v>196</v>
       </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -5361,6 +7596,11 @@
       <c r="C448" t="n">
         <v>159</v>
       </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -5372,6 +7612,11 @@
       <c r="C449" t="n">
         <v>188</v>
       </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -5383,6 +7628,11 @@
       <c r="C450" t="n">
         <v>5</v>
       </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -5394,6 +7644,11 @@
       <c r="C451" t="n">
         <v>3</v>
       </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -5405,6 +7660,11 @@
       <c r="C452" t="n">
         <v>7</v>
       </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -5416,6 +7676,11 @@
       <c r="C453" t="n">
         <v>125</v>
       </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -5427,6 +7692,11 @@
       <c r="C454" t="n">
         <v>61</v>
       </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -5438,6 +7708,11 @@
       <c r="C455" t="n">
         <v>81</v>
       </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -5449,6 +7724,11 @@
       <c r="C456" t="n">
         <v>88</v>
       </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -5460,6 +7740,11 @@
       <c r="C457" t="n">
         <v>63</v>
       </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -5471,6 +7756,11 @@
       <c r="C458" t="n">
         <v>3</v>
       </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -5482,6 +7772,11 @@
       <c r="C459" t="n">
         <v>49</v>
       </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -5493,6 +7788,11 @@
       <c r="C460" t="n">
         <v>7</v>
       </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -5504,6 +7804,11 @@
       <c r="C461" t="n">
         <v>45</v>
       </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -5515,6 +7820,11 @@
       <c r="C462" t="n">
         <v>77</v>
       </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -5526,6 +7836,11 @@
       <c r="C463" t="n">
         <v>75</v>
       </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -5537,6 +7852,11 @@
       <c r="C464" t="n">
         <v>12</v>
       </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -5548,6 +7868,11 @@
       <c r="C465" t="n">
         <v>33</v>
       </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -5559,6 +7884,11 @@
       <c r="C466" t="n">
         <v>32</v>
       </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -5570,6 +7900,11 @@
       <c r="C467" t="n">
         <v>28</v>
       </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -5581,6 +7916,11 @@
       <c r="C468" t="n">
         <v>79</v>
       </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -5592,6 +7932,11 @@
       <c r="C469" t="n">
         <v>216</v>
       </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -5603,6 +7948,11 @@
       <c r="C470" t="n">
         <v>23</v>
       </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -5614,6 +7964,11 @@
       <c r="C471" t="n">
         <v>67</v>
       </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -5625,6 +7980,11 @@
       <c r="C472" t="n">
         <v>39</v>
       </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -5636,6 +7996,11 @@
       <c r="C473" t="n">
         <v>56</v>
       </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -5647,6 +8012,11 @@
       <c r="C474" t="n">
         <v>63</v>
       </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -5658,6 +8028,11 @@
       <c r="C475" t="n">
         <v>24</v>
       </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -5669,6 +8044,11 @@
       <c r="C476" t="n">
         <v>77</v>
       </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -5680,6 +8060,11 @@
       <c r="C477" t="n">
         <v>61</v>
       </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -5691,6 +8076,11 @@
       <c r="C478" t="n">
         <v>15</v>
       </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -5702,6 +8092,11 @@
       <c r="C479" t="n">
         <v>37</v>
       </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -5713,6 +8108,11 @@
       <c r="C480" t="n">
         <v>10</v>
       </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -5724,6 +8124,11 @@
       <c r="C481" t="n">
         <v>26</v>
       </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -5735,6 +8140,11 @@
       <c r="C482" t="n">
         <v>85</v>
       </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -5746,6 +8156,11 @@
       <c r="C483" t="n">
         <v>99</v>
       </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -5757,6 +8172,11 @@
       <c r="C484" t="n">
         <v>75</v>
       </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -5768,6 +8188,11 @@
       <c r="C485" t="n">
         <v>38</v>
       </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -5779,6 +8204,11 @@
       <c r="C486" t="n">
         <v>15</v>
       </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -5790,6 +8220,11 @@
       <c r="C487" t="n">
         <v>38</v>
       </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -5801,6 +8236,11 @@
       <c r="C488" t="n">
         <v>209</v>
       </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -5812,6 +8252,11 @@
       <c r="C489" t="n">
         <v>158</v>
       </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -5823,6 +8268,11 @@
       <c r="C490" t="n">
         <v>5</v>
       </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -5834,6 +8284,11 @@
       <c r="C491" t="n">
         <v>65</v>
       </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -5845,6 +8300,11 @@
       <c r="C492" t="n">
         <v>45</v>
       </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -5856,6 +8316,11 @@
       <c r="C493" t="n">
         <v>61</v>
       </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -5867,6 +8332,11 @@
       <c r="C494" t="n">
         <v>57</v>
       </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -5878,6 +8348,11 @@
       <c r="C495" t="n">
         <v>45</v>
       </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -5889,6 +8364,11 @@
       <c r="C496" t="n">
         <v>58</v>
       </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -5900,6 +8380,11 @@
       <c r="C497" t="n">
         <v>15</v>
       </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -5911,6 +8396,11 @@
       <c r="C498" t="n">
         <v>50</v>
       </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -5922,6 +8412,11 @@
       <c r="C499" t="n">
         <v>57</v>
       </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -5933,6 +8428,11 @@
       <c r="C500" t="n">
         <v>181</v>
       </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -5944,6 +8444,11 @@
       <c r="C501" t="n">
         <v>49</v>
       </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -5955,6 +8460,11 @@
       <c r="C502" t="n">
         <v>120</v>
       </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -5966,6 +8476,11 @@
       <c r="C503" t="n">
         <v>53</v>
       </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -5977,6 +8492,11 @@
       <c r="C504" t="n">
         <v>159</v>
       </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -5988,6 +8508,11 @@
       <c r="C505" t="n">
         <v>42</v>
       </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -5999,6 +8524,11 @@
       <c r="C506" t="n">
         <v>61</v>
       </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -6010,6 +8540,11 @@
       <c r="C507" t="n">
         <v>73</v>
       </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -6021,6 +8556,11 @@
       <c r="C508" t="n">
         <v>23</v>
       </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -6032,6 +8572,11 @@
       <c r="C509" t="n">
         <v>54</v>
       </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -6043,6 +8588,11 @@
       <c r="C510" t="n">
         <v>162</v>
       </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -6054,6 +8604,11 @@
       <c r="C511" t="n">
         <v>148</v>
       </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -6065,6 +8620,11 @@
       <c r="C512" t="n">
         <v>199</v>
       </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -6076,6 +8636,11 @@
       <c r="C513" t="n">
         <v>66</v>
       </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -6087,6 +8652,11 @@
       <c r="C514" t="n">
         <v>107</v>
       </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -6098,6 +8668,11 @@
       <c r="C515" t="n">
         <v>68</v>
       </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -6109,6 +8684,11 @@
       <c r="C516" t="n">
         <v>41</v>
       </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -6120,6 +8700,11 @@
       <c r="C517" t="n">
         <v>4</v>
       </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -6131,6 +8716,11 @@
       <c r="C518" t="n">
         <v>77</v>
       </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -6142,6 +8732,11 @@
       <c r="C519" t="n">
         <v>42</v>
       </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -6153,6 +8748,11 @@
       <c r="C520" t="n">
         <v>67</v>
       </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -6164,6 +8764,11 @@
       <c r="C521" t="n">
         <v>51</v>
       </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -6175,6 +8780,11 @@
       <c r="C522" t="n">
         <v>96</v>
       </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -6186,6 +8796,11 @@
       <c r="C523" t="n">
         <v>41</v>
       </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -6197,6 +8812,11 @@
       <c r="C524" t="n">
         <v>36</v>
       </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -6208,6 +8828,11 @@
       <c r="C525" t="n">
         <v>41</v>
       </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -6219,6 +8844,11 @@
       <c r="C526" t="n">
         <v>40</v>
       </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -6230,6 +8860,11 @@
       <c r="C527" t="n">
         <v>181</v>
       </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -6241,6 +8876,11 @@
       <c r="C528" t="n">
         <v>113</v>
       </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -6252,6 +8892,11 @@
       <c r="C529" t="n">
         <v>42</v>
       </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -6263,6 +8908,11 @@
       <c r="C530" t="n">
         <v>131</v>
       </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -6274,6 +8924,11 @@
       <c r="C531" t="n">
         <v>29</v>
       </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -6285,6 +8940,11 @@
       <c r="C532" t="n">
         <v>114</v>
       </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -6296,6 +8956,11 @@
       <c r="C533" t="n">
         <v>71</v>
       </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -6307,6 +8972,11 @@
       <c r="C534" t="n">
         <v>17</v>
       </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -6318,6 +8988,11 @@
       <c r="C535" t="n">
         <v>48</v>
       </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -6329,6 +9004,11 @@
       <c r="C536" t="n">
         <v>43</v>
       </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -6340,6 +9020,11 @@
       <c r="C537" t="n">
         <v>167</v>
       </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -6351,6 +9036,11 @@
       <c r="C538" t="n">
         <v>110</v>
       </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -6362,6 +9052,11 @@
       <c r="C539" t="n">
         <v>12</v>
       </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -6373,6 +9068,11 @@
       <c r="C540" t="n">
         <v>86</v>
       </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -6384,6 +9084,11 @@
       <c r="C541" t="n">
         <v>83</v>
       </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
@@ -6395,6 +9100,11 @@
       <c r="C542" t="n">
         <v>43</v>
       </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
@@ -6406,6 +9116,11 @@
       <c r="C543" t="n">
         <v>93</v>
       </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
@@ -6417,6 +9132,11 @@
       <c r="C544" t="n">
         <v>172</v>
       </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
@@ -6428,6 +9148,11 @@
       <c r="C545" t="n">
         <v>155</v>
       </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
@@ -6439,6 +9164,11 @@
       <c r="C546" t="n">
         <v>246</v>
       </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="n">
@@ -6450,6 +9180,11 @@
       <c r="C547" t="n">
         <v>146</v>
       </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
@@ -6461,6 +9196,11 @@
       <c r="C548" t="n">
         <v>14</v>
       </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
@@ -6472,6 +9212,11 @@
       <c r="C549" t="n">
         <v>21</v>
       </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
@@ -6483,6 +9228,11 @@
       <c r="C550" t="n">
         <v>104</v>
       </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
@@ -6494,6 +9244,11 @@
       <c r="C551" t="n">
         <v>143</v>
       </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
@@ -6505,6 +9260,11 @@
       <c r="C552" t="n">
         <v>79</v>
       </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
@@ -6516,6 +9276,11 @@
       <c r="C553" t="n">
         <v>33</v>
       </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
@@ -6527,6 +9292,11 @@
       <c r="C554" t="n">
         <v>122</v>
       </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
@@ -6538,6 +9308,11 @@
       <c r="C555" t="n">
         <v>25</v>
       </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
@@ -6549,6 +9324,11 @@
       <c r="C556" t="n">
         <v>29</v>
       </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
@@ -6560,6 +9340,11 @@
       <c r="C557" t="n">
         <v>55</v>
       </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
@@ -6571,6 +9356,11 @@
       <c r="C558" t="n">
         <v>65</v>
       </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
@@ -6582,6 +9372,11 @@
       <c r="C559" t="n">
         <v>31</v>
       </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="n">
@@ -6593,6 +9388,11 @@
       <c r="C560" t="n">
         <v>45</v>
       </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="n">
@@ -6604,6 +9404,11 @@
       <c r="C561" t="n">
         <v>26</v>
       </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
@@ -6615,6 +9420,11 @@
       <c r="C562" t="n">
         <v>55</v>
       </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
@@ -6626,6 +9436,11 @@
       <c r="C563" t="n">
         <v>124</v>
       </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
@@ -6637,6 +9452,11 @@
       <c r="C564" t="n">
         <v>19</v>
       </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
@@ -6648,6 +9468,11 @@
       <c r="C565" t="n">
         <v>41</v>
       </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
@@ -6659,6 +9484,11 @@
       <c r="C566" t="n">
         <v>32</v>
       </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
@@ -6670,6 +9500,11 @@
       <c r="C567" t="n">
         <v>57</v>
       </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
@@ -6681,6 +9516,11 @@
       <c r="C568" t="n">
         <v>4</v>
       </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
@@ -6692,6 +9532,11 @@
       <c r="C569" t="n">
         <v>89</v>
       </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
@@ -6703,6 +9548,11 @@
       <c r="C570" t="n">
         <v>67</v>
       </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
@@ -6714,6 +9564,11 @@
       <c r="C571" t="n">
         <v>73</v>
       </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
@@ -6725,6 +9580,11 @@
       <c r="C572" t="n">
         <v>158</v>
       </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
@@ -6736,6 +9596,11 @@
       <c r="C573" t="n">
         <v>79</v>
       </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
@@ -6747,6 +9612,11 @@
       <c r="C574" t="n">
         <v>29</v>
       </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
@@ -6758,6 +9628,11 @@
       <c r="C575" t="n">
         <v>60</v>
       </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
@@ -6769,6 +9644,11 @@
       <c r="C576" t="n">
         <v>100</v>
       </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="n">
@@ -6780,6 +9660,11 @@
       <c r="C577" t="n">
         <v>48</v>
       </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="n">
@@ -6791,6 +9676,11 @@
       <c r="C578" t="n">
         <v>47</v>
       </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="n">
@@ -6802,6 +9692,11 @@
       <c r="C579" t="n">
         <v>37</v>
       </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
@@ -6813,6 +9708,11 @@
       <c r="C580" t="n">
         <v>45</v>
       </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="n">
@@ -6824,6 +9724,11 @@
       <c r="C581" t="n">
         <v>155</v>
       </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="n">
@@ -6835,6 +9740,11 @@
       <c r="C582" t="n">
         <v>32</v>
       </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="n">
@@ -6846,6 +9756,11 @@
       <c r="C583" t="n">
         <v>166</v>
       </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="n">
@@ -6857,6 +9772,11 @@
       <c r="C584" t="n">
         <v>10</v>
       </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="n">
@@ -6868,6 +9788,11 @@
       <c r="C585" t="n">
         <v>39</v>
       </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="n">
@@ -6879,6 +9804,11 @@
       <c r="C586" t="n">
         <v>46</v>
       </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
@@ -6890,6 +9820,11 @@
       <c r="C587" t="n">
         <v>62</v>
       </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="n">
@@ -6901,6 +9836,11 @@
       <c r="C588" t="n">
         <v>43</v>
       </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="n">
@@ -6912,6 +9852,11 @@
       <c r="C589" t="n">
         <v>66</v>
       </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
@@ -6923,6 +9868,11 @@
       <c r="C590" t="n">
         <v>22</v>
       </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="n">
@@ -6934,6 +9884,11 @@
       <c r="C591" t="n">
         <v>116</v>
       </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="n">
@@ -6945,6 +9900,11 @@
       <c r="C592" t="n">
         <v>105</v>
       </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="n">
@@ -6956,6 +9916,11 @@
       <c r="C593" t="n">
         <v>75</v>
       </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="n">
@@ -6967,6 +9932,11 @@
       <c r="C594" t="n">
         <v>142</v>
       </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="n">
@@ -6978,6 +9948,11 @@
       <c r="C595" t="n">
         <v>96</v>
       </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="n">
@@ -6989,6 +9964,11 @@
       <c r="C596" t="n">
         <v>68</v>
       </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="n">
@@ -7000,6 +9980,11 @@
       <c r="C597" t="n">
         <v>51</v>
       </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="n">
@@ -7011,6 +9996,11 @@
       <c r="C598" t="n">
         <v>110</v>
       </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="n">
@@ -7022,6 +10012,11 @@
       <c r="C599" t="n">
         <v>97</v>
       </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="n">
@@ -7033,6 +10028,11 @@
       <c r="C600" t="n">
         <v>40</v>
       </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="n">
@@ -7044,6 +10044,11 @@
       <c r="C601" t="n">
         <v>136</v>
       </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="n">
@@ -7055,6 +10060,11 @@
       <c r="C602" t="n">
         <v>187</v>
       </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="n">
@@ -7066,6 +10076,11 @@
       <c r="C603" t="n">
         <v>66</v>
       </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="n">
@@ -7077,6 +10092,11 @@
       <c r="C604" t="n">
         <v>66</v>
       </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="n">
@@ -7088,6 +10108,11 @@
       <c r="C605" t="n">
         <v>119</v>
       </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="n">
@@ -7099,6 +10124,11 @@
       <c r="C606" t="n">
         <v>61</v>
       </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="n">
@@ -7110,6 +10140,11 @@
       <c r="C607" t="n">
         <v>95</v>
       </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="n">
@@ -7121,6 +10156,11 @@
       <c r="C608" t="n">
         <v>150</v>
       </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="n">
@@ -7132,6 +10172,11 @@
       <c r="C609" t="n">
         <v>40</v>
       </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="n">
@@ -7143,6 +10188,11 @@
       <c r="C610" t="n">
         <v>110</v>
       </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="n">
@@ -7154,6 +10204,11 @@
       <c r="C611" t="n">
         <v>269</v>
       </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="n">
@@ -7165,6 +10220,11 @@
       <c r="C612" t="n">
         <v>75</v>
       </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>1980s</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="n">
@@ -7176,6 +10236,11 @@
       <c r="C613" t="n">
         <v>90</v>
       </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="n">
@@ -7187,6 +10252,11 @@
       <c r="C614" t="n">
         <v>31</v>
       </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="n">
@@ -7198,6 +10268,11 @@
       <c r="C615" t="n">
         <v>305</v>
       </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="n">
@@ -7209,6 +10284,11 @@
       <c r="C616" t="n">
         <v>56</v>
       </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="n">
@@ -7220,6 +10300,11 @@
       <c r="C617" t="n">
         <v>46</v>
       </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="n">
@@ -7231,6 +10316,11 @@
       <c r="C618" t="n">
         <v>39</v>
       </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="n">
@@ -7242,6 +10332,11 @@
       <c r="C619" t="n">
         <v>54</v>
       </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="n">
@@ -7253,6 +10348,11 @@
       <c r="C620" t="n">
         <v>66</v>
       </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="n">
@@ -7264,6 +10364,11 @@
       <c r="C621" t="n">
         <v>72</v>
       </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="n">
@@ -7275,6 +10380,11 @@
       <c r="C622" t="n">
         <v>63</v>
       </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="n">
@@ -7286,6 +10396,11 @@
       <c r="C623" t="n">
         <v>29</v>
       </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="n">
@@ -7297,6 +10412,11 @@
       <c r="C624" t="n">
         <v>22</v>
       </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="n">
@@ -7308,6 +10428,11 @@
       <c r="C625" t="n">
         <v>53</v>
       </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="n">
@@ -7319,6 +10444,11 @@
       <c r="C626" t="n">
         <v>71</v>
       </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="n">
@@ -7330,6 +10460,11 @@
       <c r="C627" t="n">
         <v>81</v>
       </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="n">
@@ -7341,6 +10476,11 @@
       <c r="C628" t="n">
         <v>104</v>
       </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="n">
@@ -7352,6 +10492,11 @@
       <c r="C629" t="n">
         <v>46</v>
       </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="n">
@@ -7363,6 +10508,11 @@
       <c r="C630" t="n">
         <v>79</v>
       </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="n">
@@ -7374,6 +10524,11 @@
       <c r="C631" t="n">
         <v>74</v>
       </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="n">
@@ -7385,6 +10540,11 @@
       <c r="C632" t="n">
         <v>137</v>
       </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="n">
@@ -7396,6 +10556,11 @@
       <c r="C633" t="n">
         <v>25</v>
       </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="n">
@@ -7407,6 +10572,11 @@
       <c r="C634" t="n">
         <v>80</v>
       </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="n">
@@ -7418,6 +10588,11 @@
       <c r="C635" t="n">
         <v>65</v>
       </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>1990s</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="n">
@@ -7429,6 +10604,11 @@
       <c r="C636" t="n">
         <v>95</v>
       </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="n">
@@ -7440,6 +10620,11 @@
       <c r="C637" t="n">
         <v>47</v>
       </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="n">
@@ -7451,6 +10636,11 @@
       <c r="C638" t="n">
         <v>56</v>
       </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="n">
@@ -7462,6 +10652,11 @@
       <c r="C639" t="n">
         <v>41</v>
       </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="n">
@@ -7473,6 +10668,11 @@
       <c r="C640" t="n">
         <v>96</v>
       </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="n">
@@ -7484,6 +10684,11 @@
       <c r="C641" t="n">
         <v>23</v>
       </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="n">
@@ -7495,6 +10700,11 @@
       <c r="C642" t="n">
         <v>349</v>
       </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="n">
@@ -7506,6 +10716,11 @@
       <c r="C643" t="n">
         <v>109</v>
       </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="n">
@@ -7517,6 +10732,11 @@
       <c r="C644" t="n">
         <v>292</v>
       </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="n">
@@ -7528,6 +10748,11 @@
       <c r="C645" t="n">
         <v>275</v>
       </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="n">
@@ -7539,6 +10764,11 @@
       <c r="C646" t="n">
         <v>355</v>
       </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="n">
@@ -7550,6 +10780,11 @@
       <c r="C647" t="n">
         <v>7</v>
       </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>1970s</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="n">
@@ -7561,6 +10796,11 @@
       <c r="C648" t="n">
         <v>252</v>
       </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="n">
@@ -7572,6 +10812,11 @@
       <c r="C649" t="n">
         <v>24</v>
       </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="n">
@@ -7583,6 +10828,11 @@
       <c r="C650" t="n">
         <v>102</v>
       </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="n">
@@ -7594,6 +10844,11 @@
       <c r="C651" t="n">
         <v>61</v>
       </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="n">
@@ -7605,6 +10860,11 @@
       <c r="C652" t="n">
         <v>174</v>
       </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="n">
@@ -7616,6 +10876,11 @@
       <c r="C653" t="n">
         <v>118</v>
       </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="n">
@@ -7627,6 +10892,11 @@
       <c r="C654" t="n">
         <v>437</v>
       </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="n">
@@ -7638,6 +10908,11 @@
       <c r="C655" t="n">
         <v>50</v>
       </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="n">
@@ -7649,6 +10924,11 @@
       <c r="C656" t="n">
         <v>159</v>
       </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="n">
@@ -7660,6 +10940,11 @@
       <c r="C657" t="n">
         <v>298</v>
       </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="n">
@@ -7671,6 +10956,11 @@
       <c r="C658" t="n">
         <v>45</v>
       </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="n">
@@ -7682,6 +10972,11 @@
       <c r="C659" t="n">
         <v>136</v>
       </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="n">
@@ -7692,6 +10987,11 @@
       </c>
       <c r="C660" t="n">
         <v>259</v>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/evolution/new_word_count_df.xlsx
+++ b/evolution/new_word_count_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D536"/>
+  <dimension ref="A1:D506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1847,10 +1847,10 @@
         <v>3</v>
       </c>
       <c r="B89" t="n">
-        <v>1979</v>
+        <v>1972</v>
       </c>
       <c r="C89" t="n">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -1863,14 +1863,14 @@
         <v>3</v>
       </c>
       <c r="B90" t="n">
-        <v>1980</v>
+        <v>1974</v>
       </c>
       <c r="C90" t="n">
-        <v>182</v>
+        <v>3</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
@@ -1879,14 +1879,14 @@
         <v>3</v>
       </c>
       <c r="B91" t="n">
-        <v>1985</v>
+        <v>1975</v>
       </c>
       <c r="C91" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
@@ -1895,14 +1895,14 @@
         <v>3</v>
       </c>
       <c r="B92" t="n">
-        <v>1988</v>
+        <v>1977</v>
       </c>
       <c r="C92" t="n">
-        <v>44</v>
+        <v>174</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
@@ -1911,14 +1911,14 @@
         <v>3</v>
       </c>
       <c r="B93" t="n">
-        <v>1989</v>
+        <v>1978</v>
       </c>
       <c r="C93" t="n">
-        <v>132</v>
+        <v>58</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
@@ -1927,14 +1927,14 @@
         <v>3</v>
       </c>
       <c r="B94" t="n">
-        <v>1990</v>
+        <v>1979</v>
       </c>
       <c r="C94" t="n">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
@@ -1943,14 +1943,14 @@
         <v>3</v>
       </c>
       <c r="B95" t="n">
-        <v>1991</v>
+        <v>1980</v>
       </c>
       <c r="C95" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -1959,14 +1959,14 @@
         <v>3</v>
       </c>
       <c r="B96" t="n">
-        <v>1992</v>
+        <v>1985</v>
       </c>
       <c r="C96" t="n">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -1975,14 +1975,14 @@
         <v>3</v>
       </c>
       <c r="B97" t="n">
-        <v>1994</v>
+        <v>1987</v>
       </c>
       <c r="C97" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -1991,14 +1991,14 @@
         <v>3</v>
       </c>
       <c r="B98" t="n">
-        <v>1996</v>
+        <v>1989</v>
       </c>
       <c r="C98" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -2007,10 +2007,10 @@
         <v>3</v>
       </c>
       <c r="B99" t="n">
-        <v>1997</v>
+        <v>1990</v>
       </c>
       <c r="C99" t="n">
-        <v>268</v>
+        <v>51</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -2023,10 +2023,10 @@
         <v>3</v>
       </c>
       <c r="B100" t="n">
-        <v>1998</v>
+        <v>1991</v>
       </c>
       <c r="C100" t="n">
-        <v>247</v>
+        <v>6</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -2039,10 +2039,10 @@
         <v>3</v>
       </c>
       <c r="B101" t="n">
-        <v>1999</v>
+        <v>1992</v>
       </c>
       <c r="C101" t="n">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -2055,14 +2055,14 @@
         <v>3</v>
       </c>
       <c r="B102" t="n">
-        <v>2000</v>
+        <v>1993</v>
       </c>
       <c r="C102" t="n">
-        <v>103</v>
+        <v>233</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -2071,14 +2071,14 @@
         <v>3</v>
       </c>
       <c r="B103" t="n">
-        <v>2001</v>
+        <v>1994</v>
       </c>
       <c r="C103" t="n">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -2087,14 +2087,14 @@
         <v>3</v>
       </c>
       <c r="B104" t="n">
-        <v>2002</v>
+        <v>1995</v>
       </c>
       <c r="C104" t="n">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -2103,14 +2103,14 @@
         <v>3</v>
       </c>
       <c r="B105" t="n">
-        <v>2003</v>
+        <v>1996</v>
       </c>
       <c r="C105" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -2119,14 +2119,14 @@
         <v>3</v>
       </c>
       <c r="B106" t="n">
-        <v>2004</v>
+        <v>1998</v>
       </c>
       <c r="C106" t="n">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -2135,14 +2135,14 @@
         <v>3</v>
       </c>
       <c r="B107" t="n">
-        <v>2005</v>
+        <v>1999</v>
       </c>
       <c r="C107" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -2151,10 +2151,10 @@
         <v>3</v>
       </c>
       <c r="B108" t="n">
-        <v>2006</v>
+        <v>2000</v>
       </c>
       <c r="C108" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -2167,10 +2167,10 @@
         <v>3</v>
       </c>
       <c r="B109" t="n">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="C109" t="n">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -2183,10 +2183,10 @@
         <v>3</v>
       </c>
       <c r="B110" t="n">
-        <v>2008</v>
+        <v>2002</v>
       </c>
       <c r="C110" t="n">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -2199,10 +2199,10 @@
         <v>3</v>
       </c>
       <c r="B111" t="n">
-        <v>2009</v>
+        <v>2003</v>
       </c>
       <c r="C111" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -2215,14 +2215,14 @@
         <v>3</v>
       </c>
       <c r="B112" t="n">
-        <v>2010</v>
+        <v>2004</v>
       </c>
       <c r="C112" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -2231,14 +2231,14 @@
         <v>3</v>
       </c>
       <c r="B113" t="n">
-        <v>2011</v>
+        <v>2005</v>
       </c>
       <c r="C113" t="n">
-        <v>146</v>
+        <v>55</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -2247,14 +2247,14 @@
         <v>3</v>
       </c>
       <c r="B114" t="n">
-        <v>2012</v>
+        <v>2007</v>
       </c>
       <c r="C114" t="n">
-        <v>142</v>
+        <v>65</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -2263,14 +2263,14 @@
         <v>3</v>
       </c>
       <c r="B115" t="n">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="C115" t="n">
-        <v>289</v>
+        <v>22</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -2279,14 +2279,14 @@
         <v>3</v>
       </c>
       <c r="B116" t="n">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="C116" t="n">
-        <v>248</v>
+        <v>84</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -2295,10 +2295,10 @@
         <v>3</v>
       </c>
       <c r="B117" t="n">
-        <v>2015</v>
+        <v>2010</v>
       </c>
       <c r="C117" t="n">
-        <v>223</v>
+        <v>34</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -2311,10 +2311,10 @@
         <v>3</v>
       </c>
       <c r="B118" t="n">
-        <v>2016</v>
+        <v>2011</v>
       </c>
       <c r="C118" t="n">
-        <v>211</v>
+        <v>133</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -2327,10 +2327,10 @@
         <v>3</v>
       </c>
       <c r="B119" t="n">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="C119" t="n">
-        <v>102</v>
+        <v>166</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -2343,10 +2343,10 @@
         <v>3</v>
       </c>
       <c r="B120" t="n">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="C120" t="n">
-        <v>204</v>
+        <v>159</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -2359,10 +2359,10 @@
         <v>3</v>
       </c>
       <c r="B121" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="C121" t="n">
-        <v>188</v>
+        <v>92</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -2375,14 +2375,14 @@
         <v>3</v>
       </c>
       <c r="B122" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="C122" t="n">
-        <v>251</v>
+        <v>185</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -2391,14 +2391,14 @@
         <v>3</v>
       </c>
       <c r="B123" t="n">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="C123" t="n">
-        <v>238</v>
+        <v>153</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -2407,14 +2407,14 @@
         <v>3</v>
       </c>
       <c r="B124" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C124" t="n">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -2423,14 +2423,14 @@
         <v>3</v>
       </c>
       <c r="B125" t="n">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="C125" t="n">
-        <v>470</v>
+        <v>256</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -2439,94 +2439,94 @@
         <v>3</v>
       </c>
       <c r="B126" t="n">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="C126" t="n">
-        <v>360</v>
+        <v>270</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B127" t="n">
-        <v>1972</v>
+        <v>2020</v>
       </c>
       <c r="C127" t="n">
-        <v>6</v>
+        <v>140</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B128" t="n">
-        <v>1985</v>
+        <v>2021</v>
       </c>
       <c r="C128" t="n">
-        <v>54</v>
+        <v>204</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B129" t="n">
-        <v>1987</v>
+        <v>2022</v>
       </c>
       <c r="C129" t="n">
-        <v>52</v>
+        <v>263</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B130" t="n">
-        <v>1991</v>
+        <v>2023</v>
       </c>
       <c r="C130" t="n">
-        <v>10</v>
+        <v>278</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B131" t="n">
-        <v>1992</v>
+        <v>2024</v>
       </c>
       <c r="C131" t="n">
-        <v>52</v>
+        <v>380</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -2535,14 +2535,14 @@
         <v>4</v>
       </c>
       <c r="B132" t="n">
-        <v>1993</v>
+        <v>1979</v>
       </c>
       <c r="C132" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
@@ -2551,14 +2551,14 @@
         <v>4</v>
       </c>
       <c r="B133" t="n">
-        <v>1994</v>
+        <v>1980</v>
       </c>
       <c r="C133" t="n">
-        <v>22</v>
+        <v>182</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -2567,14 +2567,14 @@
         <v>4</v>
       </c>
       <c r="B134" t="n">
-        <v>1995</v>
+        <v>1985</v>
       </c>
       <c r="C134" t="n">
-        <v>119</v>
+        <v>60</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -2583,14 +2583,14 @@
         <v>4</v>
       </c>
       <c r="B135" t="n">
-        <v>1996</v>
+        <v>1988</v>
       </c>
       <c r="C135" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -2599,14 +2599,14 @@
         <v>4</v>
       </c>
       <c r="B136" t="n">
-        <v>1997</v>
+        <v>1989</v>
       </c>
       <c r="C136" t="n">
-        <v>27</v>
+        <v>132</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -2615,10 +2615,10 @@
         <v>4</v>
       </c>
       <c r="B137" t="n">
-        <v>1998</v>
+        <v>1990</v>
       </c>
       <c r="C137" t="n">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -2631,10 +2631,10 @@
         <v>4</v>
       </c>
       <c r="B138" t="n">
-        <v>1999</v>
+        <v>1991</v>
       </c>
       <c r="C138" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -2647,14 +2647,14 @@
         <v>4</v>
       </c>
       <c r="B139" t="n">
-        <v>2001</v>
+        <v>1992</v>
       </c>
       <c r="C139" t="n">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -2663,14 +2663,14 @@
         <v>4</v>
       </c>
       <c r="B140" t="n">
-        <v>2002</v>
+        <v>1994</v>
       </c>
       <c r="C140" t="n">
-        <v>181</v>
+        <v>32</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -2679,14 +2679,14 @@
         <v>4</v>
       </c>
       <c r="B141" t="n">
-        <v>2003</v>
+        <v>1996</v>
       </c>
       <c r="C141" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -2695,14 +2695,14 @@
         <v>4</v>
       </c>
       <c r="B142" t="n">
-        <v>2004</v>
+        <v>1997</v>
       </c>
       <c r="C142" t="n">
-        <v>166</v>
+        <v>268</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -2711,14 +2711,14 @@
         <v>4</v>
       </c>
       <c r="B143" t="n">
-        <v>2006</v>
+        <v>1998</v>
       </c>
       <c r="C143" t="n">
-        <v>130</v>
+        <v>247</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -2727,14 +2727,14 @@
         <v>4</v>
       </c>
       <c r="B144" t="n">
-        <v>2007</v>
+        <v>1999</v>
       </c>
       <c r="C144" t="n">
-        <v>85</v>
+        <v>179</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -2743,10 +2743,10 @@
         <v>4</v>
       </c>
       <c r="B145" t="n">
-        <v>2008</v>
+        <v>2000</v>
       </c>
       <c r="C145" t="n">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -2759,10 +2759,10 @@
         <v>4</v>
       </c>
       <c r="B146" t="n">
-        <v>2009</v>
+        <v>2001</v>
       </c>
       <c r="C146" t="n">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -2775,14 +2775,14 @@
         <v>4</v>
       </c>
       <c r="B147" t="n">
-        <v>2010</v>
+        <v>2002</v>
       </c>
       <c r="C147" t="n">
-        <v>96</v>
+        <v>154</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -2791,14 +2791,14 @@
         <v>4</v>
       </c>
       <c r="B148" t="n">
-        <v>2011</v>
+        <v>2003</v>
       </c>
       <c r="C148" t="n">
-        <v>56</v>
+        <v>160</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -2807,14 +2807,14 @@
         <v>4</v>
       </c>
       <c r="B149" t="n">
-        <v>2012</v>
+        <v>2004</v>
       </c>
       <c r="C149" t="n">
         <v>39</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -2823,14 +2823,14 @@
         <v>4</v>
       </c>
       <c r="B150" t="n">
-        <v>2013</v>
+        <v>2005</v>
       </c>
       <c r="C150" t="n">
-        <v>127</v>
+        <v>44</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -2839,14 +2839,14 @@
         <v>4</v>
       </c>
       <c r="B151" t="n">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="C151" t="n">
-        <v>167</v>
+        <v>61</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -2855,14 +2855,14 @@
         <v>4</v>
       </c>
       <c r="B152" t="n">
-        <v>2015</v>
+        <v>2007</v>
       </c>
       <c r="C152" t="n">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -2871,14 +2871,14 @@
         <v>4</v>
       </c>
       <c r="B153" t="n">
-        <v>2016</v>
+        <v>2008</v>
       </c>
       <c r="C153" t="n">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -2887,14 +2887,14 @@
         <v>4</v>
       </c>
       <c r="B154" t="n">
-        <v>2017</v>
+        <v>2009</v>
       </c>
       <c r="C154" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -2903,10 +2903,10 @@
         <v>4</v>
       </c>
       <c r="B155" t="n">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="C155" t="n">
-        <v>143</v>
+        <v>88</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -2919,10 +2919,10 @@
         <v>4</v>
       </c>
       <c r="B156" t="n">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="C156" t="n">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -2935,14 +2935,14 @@
         <v>4</v>
       </c>
       <c r="B157" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="C157" t="n">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -2951,14 +2951,14 @@
         <v>4</v>
       </c>
       <c r="B158" t="n">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="C158" t="n">
-        <v>198</v>
+        <v>289</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -2967,14 +2967,14 @@
         <v>4</v>
       </c>
       <c r="B159" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C159" t="n">
-        <v>135</v>
+        <v>248</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -2983,14 +2983,14 @@
         <v>4</v>
       </c>
       <c r="B160" t="n">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="C160" t="n">
-        <v>168</v>
+        <v>223</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -2999,142 +2999,142 @@
         <v>4</v>
       </c>
       <c r="B161" t="n">
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="C161" t="n">
-        <v>322</v>
+        <v>211</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B162" t="n">
-        <v>1976</v>
+        <v>2017</v>
       </c>
       <c r="C162" t="n">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B163" t="n">
-        <v>1978</v>
+        <v>2018</v>
       </c>
       <c r="C163" t="n">
-        <v>101</v>
+        <v>204</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B164" t="n">
-        <v>1981</v>
+        <v>2019</v>
       </c>
       <c r="C164" t="n">
-        <v>67</v>
+        <v>188</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B165" t="n">
-        <v>1992</v>
+        <v>2020</v>
       </c>
       <c r="C165" t="n">
-        <v>27</v>
+        <v>251</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B166" t="n">
-        <v>1993</v>
+        <v>2021</v>
       </c>
       <c r="C166" t="n">
-        <v>123</v>
+        <v>238</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B167" t="n">
-        <v>1994</v>
+        <v>2022</v>
       </c>
       <c r="C167" t="n">
-        <v>36</v>
+        <v>161</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B168" t="n">
-        <v>1996</v>
+        <v>2023</v>
       </c>
       <c r="C168" t="n">
-        <v>29</v>
+        <v>470</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B169" t="n">
-        <v>1998</v>
+        <v>2024</v>
       </c>
       <c r="C169" t="n">
-        <v>34</v>
+        <v>360</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -3143,14 +3143,14 @@
         <v>5</v>
       </c>
       <c r="B170" t="n">
-        <v>2000</v>
+        <v>1972</v>
       </c>
       <c r="C170" t="n">
-        <v>103</v>
+        <v>6</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
@@ -3159,14 +3159,14 @@
         <v>5</v>
       </c>
       <c r="B171" t="n">
-        <v>2002</v>
+        <v>1985</v>
       </c>
       <c r="C171" t="n">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -3175,14 +3175,14 @@
         <v>5</v>
       </c>
       <c r="B172" t="n">
-        <v>2003</v>
+        <v>1987</v>
       </c>
       <c r="C172" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -3191,14 +3191,14 @@
         <v>5</v>
       </c>
       <c r="B173" t="n">
-        <v>2004</v>
+        <v>1991</v>
       </c>
       <c r="C173" t="n">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -3207,14 +3207,14 @@
         <v>5</v>
       </c>
       <c r="B174" t="n">
-        <v>2005</v>
+        <v>1992</v>
       </c>
       <c r="C174" t="n">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -3223,14 +3223,14 @@
         <v>5</v>
       </c>
       <c r="B175" t="n">
-        <v>2006</v>
+        <v>1993</v>
       </c>
       <c r="C175" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -3239,14 +3239,14 @@
         <v>5</v>
       </c>
       <c r="B176" t="n">
-        <v>2007</v>
+        <v>1994</v>
       </c>
       <c r="C176" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -3255,14 +3255,14 @@
         <v>5</v>
       </c>
       <c r="B177" t="n">
-        <v>2008</v>
+        <v>1995</v>
       </c>
       <c r="C177" t="n">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -3271,14 +3271,14 @@
         <v>5</v>
       </c>
       <c r="B178" t="n">
-        <v>2009</v>
+        <v>1996</v>
       </c>
       <c r="C178" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -3287,14 +3287,14 @@
         <v>5</v>
       </c>
       <c r="B179" t="n">
-        <v>2010</v>
+        <v>1997</v>
       </c>
       <c r="C179" t="n">
-        <v>157</v>
+        <v>27</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -3303,14 +3303,14 @@
         <v>5</v>
       </c>
       <c r="B180" t="n">
-        <v>2011</v>
+        <v>1998</v>
       </c>
       <c r="C180" t="n">
-        <v>269</v>
+        <v>51</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -3319,14 +3319,14 @@
         <v>5</v>
       </c>
       <c r="B181" t="n">
-        <v>2012</v>
+        <v>1999</v>
       </c>
       <c r="C181" t="n">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -3335,14 +3335,14 @@
         <v>5</v>
       </c>
       <c r="B182" t="n">
-        <v>2013</v>
+        <v>2001</v>
       </c>
       <c r="C182" t="n">
-        <v>294</v>
+        <v>31</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3351,14 +3351,14 @@
         <v>5</v>
       </c>
       <c r="B183" t="n">
-        <v>2014</v>
+        <v>2002</v>
       </c>
       <c r="C183" t="n">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3367,14 +3367,14 @@
         <v>5</v>
       </c>
       <c r="B184" t="n">
-        <v>2015</v>
+        <v>2003</v>
       </c>
       <c r="C184" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3383,14 +3383,14 @@
         <v>5</v>
       </c>
       <c r="B185" t="n">
-        <v>2016</v>
+        <v>2004</v>
       </c>
       <c r="C185" t="n">
-        <v>304</v>
+        <v>166</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3399,14 +3399,14 @@
         <v>5</v>
       </c>
       <c r="B186" t="n">
-        <v>2017</v>
+        <v>2006</v>
       </c>
       <c r="C186" t="n">
-        <v>339</v>
+        <v>130</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3415,14 +3415,14 @@
         <v>5</v>
       </c>
       <c r="B187" t="n">
-        <v>2018</v>
+        <v>2007</v>
       </c>
       <c r="C187" t="n">
-        <v>201</v>
+        <v>85</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3431,14 +3431,14 @@
         <v>5</v>
       </c>
       <c r="B188" t="n">
-        <v>2019</v>
+        <v>2008</v>
       </c>
       <c r="C188" t="n">
-        <v>325</v>
+        <v>135</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3447,14 +3447,14 @@
         <v>5</v>
       </c>
       <c r="B189" t="n">
-        <v>2020</v>
+        <v>2009</v>
       </c>
       <c r="C189" t="n">
-        <v>346</v>
+        <v>101</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3463,14 +3463,14 @@
         <v>5</v>
       </c>
       <c r="B190" t="n">
-        <v>2021</v>
+        <v>2010</v>
       </c>
       <c r="C190" t="n">
-        <v>389</v>
+        <v>96</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -3479,14 +3479,14 @@
         <v>5</v>
       </c>
       <c r="B191" t="n">
-        <v>2022</v>
+        <v>2011</v>
       </c>
       <c r="C191" t="n">
-        <v>555</v>
+        <v>56</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -3495,14 +3495,14 @@
         <v>5</v>
       </c>
       <c r="B192" t="n">
-        <v>2023</v>
+        <v>2012</v>
       </c>
       <c r="C192" t="n">
-        <v>449</v>
+        <v>39</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -3511,190 +3511,190 @@
         <v>5</v>
       </c>
       <c r="B193" t="n">
-        <v>2024</v>
+        <v>2013</v>
       </c>
       <c r="C193" t="n">
-        <v>587</v>
+        <v>127</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B194" t="n">
-        <v>1981</v>
+        <v>2014</v>
       </c>
       <c r="C194" t="n">
-        <v>11</v>
+        <v>167</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B195" t="n">
-        <v>1991</v>
+        <v>2015</v>
       </c>
       <c r="C195" t="n">
-        <v>11</v>
+        <v>145</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B196" t="n">
-        <v>1992</v>
+        <v>2016</v>
       </c>
       <c r="C196" t="n">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B197" t="n">
-        <v>1993</v>
+        <v>2017</v>
       </c>
       <c r="C197" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B198" t="n">
-        <v>1995</v>
+        <v>2018</v>
       </c>
       <c r="C198" t="n">
-        <v>47</v>
+        <v>143</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B199" t="n">
-        <v>1996</v>
+        <v>2019</v>
       </c>
       <c r="C199" t="n">
-        <v>54</v>
+        <v>178</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B200" t="n">
-        <v>1997</v>
+        <v>2020</v>
       </c>
       <c r="C200" t="n">
-        <v>46</v>
+        <v>188</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B201" t="n">
-        <v>1998</v>
+        <v>2021</v>
       </c>
       <c r="C201" t="n">
-        <v>97</v>
+        <v>198</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B202" t="n">
-        <v>2000</v>
+        <v>2022</v>
       </c>
       <c r="C202" t="n">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B203" t="n">
-        <v>2001</v>
+        <v>2023</v>
       </c>
       <c r="C203" t="n">
-        <v>76</v>
+        <v>168</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B204" t="n">
-        <v>2002</v>
+        <v>2024</v>
       </c>
       <c r="C204" t="n">
-        <v>69</v>
+        <v>322</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -3703,14 +3703,14 @@
         <v>6</v>
       </c>
       <c r="B205" t="n">
-        <v>2003</v>
+        <v>1976</v>
       </c>
       <c r="C205" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
@@ -3719,14 +3719,14 @@
         <v>6</v>
       </c>
       <c r="B206" t="n">
-        <v>2004</v>
+        <v>1978</v>
       </c>
       <c r="C206" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
@@ -3735,14 +3735,14 @@
         <v>6</v>
       </c>
       <c r="B207" t="n">
-        <v>2005</v>
+        <v>1981</v>
       </c>
       <c r="C207" t="n">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -3751,14 +3751,14 @@
         <v>6</v>
       </c>
       <c r="B208" t="n">
-        <v>2006</v>
+        <v>1992</v>
       </c>
       <c r="C208" t="n">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -3767,14 +3767,14 @@
         <v>6</v>
       </c>
       <c r="B209" t="n">
-        <v>2007</v>
+        <v>1993</v>
       </c>
       <c r="C209" t="n">
-        <v>25</v>
+        <v>123</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -3783,14 +3783,14 @@
         <v>6</v>
       </c>
       <c r="B210" t="n">
-        <v>2008</v>
+        <v>1994</v>
       </c>
       <c r="C210" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -3799,14 +3799,14 @@
         <v>6</v>
       </c>
       <c r="B211" t="n">
-        <v>2009</v>
+        <v>1996</v>
       </c>
       <c r="C211" t="n">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -3815,14 +3815,14 @@
         <v>6</v>
       </c>
       <c r="B212" t="n">
-        <v>2010</v>
+        <v>1998</v>
       </c>
       <c r="C212" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -3831,14 +3831,14 @@
         <v>6</v>
       </c>
       <c r="B213" t="n">
-        <v>2011</v>
+        <v>2000</v>
       </c>
       <c r="C213" t="n">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3847,14 +3847,14 @@
         <v>6</v>
       </c>
       <c r="B214" t="n">
-        <v>2012</v>
+        <v>2002</v>
       </c>
       <c r="C214" t="n">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3863,14 +3863,14 @@
         <v>6</v>
       </c>
       <c r="B215" t="n">
-        <v>2013</v>
+        <v>2003</v>
       </c>
       <c r="C215" t="n">
-        <v>220</v>
+        <v>47</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3879,14 +3879,14 @@
         <v>6</v>
       </c>
       <c r="B216" t="n">
-        <v>2014</v>
+        <v>2004</v>
       </c>
       <c r="C216" t="n">
-        <v>95</v>
+        <v>158</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3895,14 +3895,14 @@
         <v>6</v>
       </c>
       <c r="B217" t="n">
-        <v>2015</v>
+        <v>2005</v>
       </c>
       <c r="C217" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3911,14 +3911,14 @@
         <v>6</v>
       </c>
       <c r="B218" t="n">
-        <v>2016</v>
+        <v>2006</v>
       </c>
       <c r="C218" t="n">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3927,14 +3927,14 @@
         <v>6</v>
       </c>
       <c r="B219" t="n">
-        <v>2017</v>
+        <v>2007</v>
       </c>
       <c r="C219" t="n">
-        <v>138</v>
+        <v>41</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3943,14 +3943,14 @@
         <v>6</v>
       </c>
       <c r="B220" t="n">
-        <v>2018</v>
+        <v>2008</v>
       </c>
       <c r="C220" t="n">
         <v>85</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3959,14 +3959,14 @@
         <v>6</v>
       </c>
       <c r="B221" t="n">
-        <v>2019</v>
+        <v>2009</v>
       </c>
       <c r="C221" t="n">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3975,14 +3975,14 @@
         <v>6</v>
       </c>
       <c r="B222" t="n">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="C222" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -3991,14 +3991,14 @@
         <v>6</v>
       </c>
       <c r="B223" t="n">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="C223" t="n">
-        <v>102</v>
+        <v>269</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -4007,14 +4007,14 @@
         <v>6</v>
       </c>
       <c r="B224" t="n">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="C224" t="n">
-        <v>209</v>
+        <v>9</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -4023,14 +4023,14 @@
         <v>6</v>
       </c>
       <c r="B225" t="n">
-        <v>2023</v>
+        <v>2013</v>
       </c>
       <c r="C225" t="n">
-        <v>222</v>
+        <v>294</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -4039,174 +4039,174 @@
         <v>6</v>
       </c>
       <c r="B226" t="n">
-        <v>2024</v>
+        <v>2014</v>
       </c>
       <c r="C226" t="n">
-        <v>381</v>
+        <v>219</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B227" t="n">
-        <v>1972</v>
+        <v>2015</v>
       </c>
       <c r="C227" t="n">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B228" t="n">
-        <v>1977</v>
+        <v>2016</v>
       </c>
       <c r="C228" t="n">
-        <v>54</v>
+        <v>304</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B229" t="n">
-        <v>1979</v>
+        <v>2017</v>
       </c>
       <c r="C229" t="n">
-        <v>2</v>
+        <v>339</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B230" t="n">
-        <v>1980</v>
+        <v>2018</v>
       </c>
       <c r="C230" t="n">
-        <v>4</v>
+        <v>201</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B231" t="n">
-        <v>1989</v>
+        <v>2019</v>
       </c>
       <c r="C231" t="n">
-        <v>6</v>
+        <v>325</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B232" t="n">
-        <v>1990</v>
+        <v>2020</v>
       </c>
       <c r="C232" t="n">
-        <v>66</v>
+        <v>346</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B233" t="n">
-        <v>1992</v>
+        <v>2021</v>
       </c>
       <c r="C233" t="n">
-        <v>163</v>
+        <v>389</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B234" t="n">
-        <v>1993</v>
+        <v>2022</v>
       </c>
       <c r="C234" t="n">
-        <v>81</v>
+        <v>555</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B235" t="n">
-        <v>1994</v>
+        <v>2023</v>
       </c>
       <c r="C235" t="n">
-        <v>92</v>
+        <v>449</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B236" t="n">
-        <v>1996</v>
+        <v>2024</v>
       </c>
       <c r="C236" t="n">
-        <v>52</v>
+        <v>587</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -4215,14 +4215,14 @@
         <v>7</v>
       </c>
       <c r="B237" t="n">
-        <v>1998</v>
+        <v>1976</v>
       </c>
       <c r="C237" t="n">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
@@ -4231,14 +4231,14 @@
         <v>7</v>
       </c>
       <c r="B238" t="n">
-        <v>2000</v>
+        <v>1979</v>
       </c>
       <c r="C238" t="n">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
@@ -4247,14 +4247,14 @@
         <v>7</v>
       </c>
       <c r="B239" t="n">
-        <v>2001</v>
+        <v>1980</v>
       </c>
       <c r="C239" t="n">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -4263,14 +4263,14 @@
         <v>7</v>
       </c>
       <c r="B240" t="n">
-        <v>2003</v>
+        <v>1986</v>
       </c>
       <c r="C240" t="n">
-        <v>108</v>
+        <v>41</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -4279,14 +4279,14 @@
         <v>7</v>
       </c>
       <c r="B241" t="n">
-        <v>2004</v>
+        <v>1991</v>
       </c>
       <c r="C241" t="n">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -4295,14 +4295,14 @@
         <v>7</v>
       </c>
       <c r="B242" t="n">
-        <v>2007</v>
+        <v>1992</v>
       </c>
       <c r="C242" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -4311,14 +4311,14 @@
         <v>7</v>
       </c>
       <c r="B243" t="n">
-        <v>2008</v>
+        <v>1993</v>
       </c>
       <c r="C243" t="n">
-        <v>28</v>
+        <v>113</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -4327,14 +4327,14 @@
         <v>7</v>
       </c>
       <c r="B244" t="n">
-        <v>2009</v>
+        <v>1994</v>
       </c>
       <c r="C244" t="n">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -4343,14 +4343,14 @@
         <v>7</v>
       </c>
       <c r="B245" t="n">
-        <v>2010</v>
+        <v>1995</v>
       </c>
       <c r="C245" t="n">
-        <v>20</v>
+        <v>123</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -4359,14 +4359,14 @@
         <v>7</v>
       </c>
       <c r="B246" t="n">
-        <v>2011</v>
+        <v>1996</v>
       </c>
       <c r="C246" t="n">
-        <v>104</v>
+        <v>41</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -4375,14 +4375,14 @@
         <v>7</v>
       </c>
       <c r="B247" t="n">
-        <v>2012</v>
+        <v>1997</v>
       </c>
       <c r="C247" t="n">
-        <v>215</v>
+        <v>18</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -4391,14 +4391,14 @@
         <v>7</v>
       </c>
       <c r="B248" t="n">
-        <v>2013</v>
+        <v>1998</v>
       </c>
       <c r="C248" t="n">
-        <v>178</v>
+        <v>151</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -4407,14 +4407,14 @@
         <v>7</v>
       </c>
       <c r="B249" t="n">
-        <v>2014</v>
+        <v>1999</v>
       </c>
       <c r="C249" t="n">
-        <v>134</v>
+        <v>15</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -4423,14 +4423,14 @@
         <v>7</v>
       </c>
       <c r="B250" t="n">
-        <v>2015</v>
+        <v>2000</v>
       </c>
       <c r="C250" t="n">
-        <v>226</v>
+        <v>92</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -4439,14 +4439,14 @@
         <v>7</v>
       </c>
       <c r="B251" t="n">
-        <v>2016</v>
+        <v>2002</v>
       </c>
       <c r="C251" t="n">
-        <v>155</v>
+        <v>46</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -4455,14 +4455,14 @@
         <v>7</v>
       </c>
       <c r="B252" t="n">
-        <v>2017</v>
+        <v>2003</v>
       </c>
       <c r="C252" t="n">
-        <v>181</v>
+        <v>10</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -4471,14 +4471,14 @@
         <v>7</v>
       </c>
       <c r="B253" t="n">
-        <v>2018</v>
+        <v>2005</v>
       </c>
       <c r="C253" t="n">
-        <v>254</v>
+        <v>61</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -4487,14 +4487,14 @@
         <v>7</v>
       </c>
       <c r="B254" t="n">
-        <v>2019</v>
+        <v>2006</v>
       </c>
       <c r="C254" t="n">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -4503,14 +4503,14 @@
         <v>7</v>
       </c>
       <c r="B255" t="n">
-        <v>2020</v>
+        <v>2007</v>
       </c>
       <c r="C255" t="n">
-        <v>116</v>
+        <v>58</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -4519,14 +4519,14 @@
         <v>7</v>
       </c>
       <c r="B256" t="n">
-        <v>2021</v>
+        <v>2008</v>
       </c>
       <c r="C256" t="n">
-        <v>117</v>
+        <v>58</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -4535,14 +4535,14 @@
         <v>7</v>
       </c>
       <c r="B257" t="n">
-        <v>2022</v>
+        <v>2009</v>
       </c>
       <c r="C257" t="n">
-        <v>264</v>
+        <v>82</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -4551,14 +4551,14 @@
         <v>7</v>
       </c>
       <c r="B258" t="n">
-        <v>2023</v>
+        <v>2010</v>
       </c>
       <c r="C258" t="n">
-        <v>106</v>
+        <v>149</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -4567,222 +4567,222 @@
         <v>7</v>
       </c>
       <c r="B259" t="n">
-        <v>2024</v>
+        <v>2011</v>
       </c>
       <c r="C259" t="n">
-        <v>290</v>
+        <v>36</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B260" t="n">
-        <v>1976</v>
+        <v>2012</v>
       </c>
       <c r="C260" t="n">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B261" t="n">
-        <v>1979</v>
+        <v>2013</v>
       </c>
       <c r="C261" t="n">
-        <v>110</v>
+        <v>43</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B262" t="n">
-        <v>1980</v>
+        <v>2014</v>
       </c>
       <c r="C262" t="n">
-        <v>78</v>
+        <v>158</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B263" t="n">
-        <v>1986</v>
+        <v>2015</v>
       </c>
       <c r="C263" t="n">
-        <v>41</v>
+        <v>124</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B264" t="n">
-        <v>1991</v>
+        <v>2016</v>
       </c>
       <c r="C264" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B265" t="n">
-        <v>1992</v>
+        <v>2017</v>
       </c>
       <c r="C265" t="n">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B266" t="n">
-        <v>1993</v>
+        <v>2018</v>
       </c>
       <c r="C266" t="n">
-        <v>113</v>
+        <v>167</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B267" t="n">
-        <v>1994</v>
+        <v>2019</v>
       </c>
       <c r="C267" t="n">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B268" t="n">
-        <v>1995</v>
+        <v>2020</v>
       </c>
       <c r="C268" t="n">
-        <v>123</v>
+        <v>201</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B269" t="n">
-        <v>1996</v>
+        <v>2021</v>
       </c>
       <c r="C269" t="n">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B270" t="n">
-        <v>1997</v>
+        <v>2022</v>
       </c>
       <c r="C270" t="n">
-        <v>18</v>
+        <v>161</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B271" t="n">
-        <v>1998</v>
+        <v>2023</v>
       </c>
       <c r="C271" t="n">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B272" t="n">
-        <v>1999</v>
+        <v>2024</v>
       </c>
       <c r="C272" t="n">
-        <v>15</v>
+        <v>171</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -4791,14 +4791,14 @@
         <v>8</v>
       </c>
       <c r="B273" t="n">
-        <v>2000</v>
+        <v>1981</v>
       </c>
       <c r="C273" t="n">
-        <v>92</v>
+        <v>11</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -4807,14 +4807,14 @@
         <v>8</v>
       </c>
       <c r="B274" t="n">
-        <v>2002</v>
+        <v>1991</v>
       </c>
       <c r="C274" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -4823,14 +4823,14 @@
         <v>8</v>
       </c>
       <c r="B275" t="n">
-        <v>2003</v>
+        <v>1992</v>
       </c>
       <c r="C275" t="n">
-        <v>10</v>
+        <v>108</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -4839,14 +4839,14 @@
         <v>8</v>
       </c>
       <c r="B276" t="n">
-        <v>2005</v>
+        <v>1993</v>
       </c>
       <c r="C276" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -4855,14 +4855,14 @@
         <v>8</v>
       </c>
       <c r="B277" t="n">
-        <v>2006</v>
+        <v>1995</v>
       </c>
       <c r="C277" t="n">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -4871,14 +4871,14 @@
         <v>8</v>
       </c>
       <c r="B278" t="n">
-        <v>2007</v>
+        <v>1996</v>
       </c>
       <c r="C278" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -4887,14 +4887,14 @@
         <v>8</v>
       </c>
       <c r="B279" t="n">
-        <v>2008</v>
+        <v>1997</v>
       </c>
       <c r="C279" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -4903,14 +4903,14 @@
         <v>8</v>
       </c>
       <c r="B280" t="n">
-        <v>2009</v>
+        <v>1998</v>
       </c>
       <c r="C280" t="n">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -4919,14 +4919,14 @@
         <v>8</v>
       </c>
       <c r="B281" t="n">
-        <v>2010</v>
+        <v>2000</v>
       </c>
       <c r="C281" t="n">
-        <v>149</v>
+        <v>76</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -4935,14 +4935,14 @@
         <v>8</v>
       </c>
       <c r="B282" t="n">
-        <v>2011</v>
+        <v>2001</v>
       </c>
       <c r="C282" t="n">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -4951,14 +4951,14 @@
         <v>8</v>
       </c>
       <c r="B283" t="n">
-        <v>2012</v>
+        <v>2002</v>
       </c>
       <c r="C283" t="n">
-        <v>116</v>
+        <v>69</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -4967,14 +4967,14 @@
         <v>8</v>
       </c>
       <c r="B284" t="n">
-        <v>2013</v>
+        <v>2003</v>
       </c>
       <c r="C284" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -4983,14 +4983,14 @@
         <v>8</v>
       </c>
       <c r="B285" t="n">
-        <v>2014</v>
+        <v>2004</v>
       </c>
       <c r="C285" t="n">
-        <v>158</v>
+        <v>107</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -4999,14 +4999,14 @@
         <v>8</v>
       </c>
       <c r="B286" t="n">
-        <v>2015</v>
+        <v>2005</v>
       </c>
       <c r="C286" t="n">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -5015,14 +5015,14 @@
         <v>8</v>
       </c>
       <c r="B287" t="n">
-        <v>2016</v>
+        <v>2006</v>
       </c>
       <c r="C287" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -5031,14 +5031,14 @@
         <v>8</v>
       </c>
       <c r="B288" t="n">
-        <v>2017</v>
+        <v>2007</v>
       </c>
       <c r="C288" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -5047,14 +5047,14 @@
         <v>8</v>
       </c>
       <c r="B289" t="n">
-        <v>2018</v>
+        <v>2008</v>
       </c>
       <c r="C289" t="n">
-        <v>167</v>
+        <v>24</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -5063,14 +5063,14 @@
         <v>8</v>
       </c>
       <c r="B290" t="n">
-        <v>2019</v>
+        <v>2009</v>
       </c>
       <c r="C290" t="n">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -5079,14 +5079,14 @@
         <v>8</v>
       </c>
       <c r="B291" t="n">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="C291" t="n">
-        <v>201</v>
+        <v>62</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -5095,14 +5095,14 @@
         <v>8</v>
       </c>
       <c r="B292" t="n">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="C292" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -5111,14 +5111,14 @@
         <v>8</v>
       </c>
       <c r="B293" t="n">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="C293" t="n">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -5127,14 +5127,14 @@
         <v>8</v>
       </c>
       <c r="B294" t="n">
-        <v>2023</v>
+        <v>2013</v>
       </c>
       <c r="C294" t="n">
-        <v>169</v>
+        <v>220</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -5143,174 +5143,174 @@
         <v>8</v>
       </c>
       <c r="B295" t="n">
-        <v>2024</v>
+        <v>2014</v>
       </c>
       <c r="C295" t="n">
-        <v>171</v>
+        <v>95</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B296" t="n">
-        <v>1984</v>
+        <v>2015</v>
       </c>
       <c r="C296" t="n">
-        <v>15</v>
+        <v>114</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B297" t="n">
-        <v>1994</v>
+        <v>2016</v>
       </c>
       <c r="C297" t="n">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B298" t="n">
-        <v>1995</v>
+        <v>2017</v>
       </c>
       <c r="C298" t="n">
-        <v>38</v>
+        <v>138</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B299" t="n">
-        <v>1999</v>
+        <v>2018</v>
       </c>
       <c r="C299" t="n">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B300" t="n">
-        <v>2000</v>
+        <v>2019</v>
       </c>
       <c r="C300" t="n">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B301" t="n">
-        <v>2001</v>
+        <v>2020</v>
       </c>
       <c r="C301" t="n">
-        <v>38</v>
+        <v>159</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B302" t="n">
-        <v>2002</v>
+        <v>2021</v>
       </c>
       <c r="C302" t="n">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B303" t="n">
-        <v>2005</v>
+        <v>2022</v>
       </c>
       <c r="C303" t="n">
-        <v>50</v>
+        <v>209</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B304" t="n">
-        <v>2006</v>
+        <v>2023</v>
       </c>
       <c r="C304" t="n">
-        <v>38</v>
+        <v>222</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B305" t="n">
-        <v>2007</v>
+        <v>2024</v>
       </c>
       <c r="C305" t="n">
-        <v>55</v>
+        <v>381</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -5319,14 +5319,14 @@
         <v>9</v>
       </c>
       <c r="B306" t="n">
-        <v>2008</v>
+        <v>1989</v>
       </c>
       <c r="C306" t="n">
-        <v>167</v>
+        <v>8</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -5335,14 +5335,14 @@
         <v>9</v>
       </c>
       <c r="B307" t="n">
-        <v>2009</v>
+        <v>1993</v>
       </c>
       <c r="C307" t="n">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -5351,14 +5351,14 @@
         <v>9</v>
       </c>
       <c r="B308" t="n">
-        <v>2010</v>
+        <v>1997</v>
       </c>
       <c r="C308" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -5367,14 +5367,14 @@
         <v>9</v>
       </c>
       <c r="B309" t="n">
-        <v>2011</v>
+        <v>1999</v>
       </c>
       <c r="C309" t="n">
-        <v>118</v>
+        <v>174</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -5383,14 +5383,14 @@
         <v>9</v>
       </c>
       <c r="B310" t="n">
-        <v>2012</v>
+        <v>2000</v>
       </c>
       <c r="C310" t="n">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -5399,14 +5399,14 @@
         <v>9</v>
       </c>
       <c r="B311" t="n">
-        <v>2013</v>
+        <v>2001</v>
       </c>
       <c r="C311" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -5415,14 +5415,14 @@
         <v>9</v>
       </c>
       <c r="B312" t="n">
-        <v>2014</v>
+        <v>2002</v>
       </c>
       <c r="C312" t="n">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -5431,14 +5431,14 @@
         <v>9</v>
       </c>
       <c r="B313" t="n">
-        <v>2015</v>
+        <v>2006</v>
       </c>
       <c r="C313" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -5447,14 +5447,14 @@
         <v>9</v>
       </c>
       <c r="B314" t="n">
-        <v>2016</v>
+        <v>2007</v>
       </c>
       <c r="C314" t="n">
-        <v>226</v>
+        <v>29</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -5463,14 +5463,14 @@
         <v>9</v>
       </c>
       <c r="B315" t="n">
-        <v>2017</v>
+        <v>2008</v>
       </c>
       <c r="C315" t="n">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -5479,10 +5479,10 @@
         <v>9</v>
       </c>
       <c r="B316" t="n">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="C316" t="n">
-        <v>216</v>
+        <v>164</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -5495,10 +5495,10 @@
         <v>9</v>
       </c>
       <c r="B317" t="n">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="C317" t="n">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -5511,14 +5511,14 @@
         <v>9</v>
       </c>
       <c r="B318" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="C318" t="n">
-        <v>269</v>
+        <v>221</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -5527,14 +5527,14 @@
         <v>9</v>
       </c>
       <c r="B319" t="n">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="C319" t="n">
-        <v>285</v>
+        <v>73</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -5543,14 +5543,14 @@
         <v>9</v>
       </c>
       <c r="B320" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C320" t="n">
-        <v>209</v>
+        <v>176</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -5559,14 +5559,14 @@
         <v>9</v>
       </c>
       <c r="B321" t="n">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="C321" t="n">
-        <v>149</v>
+        <v>253</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -5575,142 +5575,142 @@
         <v>9</v>
       </c>
       <c r="B322" t="n">
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="C322" t="n">
-        <v>444</v>
+        <v>96</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B323" t="n">
-        <v>1992</v>
+        <v>2017</v>
       </c>
       <c r="C323" t="n">
-        <v>54</v>
+        <v>279</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B324" t="n">
-        <v>1993</v>
+        <v>2018</v>
       </c>
       <c r="C324" t="n">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B325" t="n">
-        <v>2005</v>
+        <v>2019</v>
       </c>
       <c r="C325" t="n">
-        <v>53</v>
+        <v>342</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B326" t="n">
-        <v>2006</v>
+        <v>2020</v>
       </c>
       <c r="C326" t="n">
-        <v>38</v>
+        <v>333</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B327" t="n">
-        <v>2010</v>
+        <v>2021</v>
       </c>
       <c r="C327" t="n">
-        <v>61</v>
+        <v>242</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B328" t="n">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="C328" t="n">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B329" t="n">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="C329" t="n">
-        <v>119</v>
+        <v>403</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B330" t="n">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="C330" t="n">
-        <v>29</v>
+        <v>662</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -5719,14 +5719,14 @@
         <v>10</v>
       </c>
       <c r="B331" t="n">
-        <v>2015</v>
+        <v>1984</v>
       </c>
       <c r="C331" t="n">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -5735,14 +5735,14 @@
         <v>10</v>
       </c>
       <c r="B332" t="n">
-        <v>2016</v>
+        <v>1994</v>
       </c>
       <c r="C332" t="n">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -5751,14 +5751,14 @@
         <v>10</v>
       </c>
       <c r="B333" t="n">
-        <v>2017</v>
+        <v>1995</v>
       </c>
       <c r="C333" t="n">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -5767,14 +5767,14 @@
         <v>10</v>
       </c>
       <c r="B334" t="n">
-        <v>2018</v>
+        <v>1999</v>
       </c>
       <c r="C334" t="n">
-        <v>92</v>
+        <v>41</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -5783,14 +5783,14 @@
         <v>10</v>
       </c>
       <c r="B335" t="n">
-        <v>2019</v>
+        <v>2000</v>
       </c>
       <c r="C335" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -5799,14 +5799,14 @@
         <v>10</v>
       </c>
       <c r="B336" t="n">
-        <v>2020</v>
+        <v>2001</v>
       </c>
       <c r="C336" t="n">
-        <v>498</v>
+        <v>38</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -5815,14 +5815,14 @@
         <v>10</v>
       </c>
       <c r="B337" t="n">
-        <v>2021</v>
+        <v>2002</v>
       </c>
       <c r="C337" t="n">
-        <v>403</v>
+        <v>46</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -5831,14 +5831,14 @@
         <v>10</v>
       </c>
       <c r="B338" t="n">
-        <v>2022</v>
+        <v>2005</v>
       </c>
       <c r="C338" t="n">
-        <v>280</v>
+        <v>50</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -5847,14 +5847,14 @@
         <v>10</v>
       </c>
       <c r="B339" t="n">
-        <v>2023</v>
+        <v>2006</v>
       </c>
       <c r="C339" t="n">
-        <v>493</v>
+        <v>38</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -5863,186 +5863,186 @@
         <v>10</v>
       </c>
       <c r="B340" t="n">
-        <v>2024</v>
+        <v>2007</v>
       </c>
       <c r="C340" t="n">
-        <v>208</v>
+        <v>55</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B341" t="n">
-        <v>1989</v>
+        <v>2008</v>
       </c>
       <c r="C341" t="n">
-        <v>8</v>
+        <v>167</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B342" t="n">
-        <v>1993</v>
+        <v>2009</v>
       </c>
       <c r="C342" t="n">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B343" t="n">
-        <v>1997</v>
+        <v>2010</v>
       </c>
       <c r="C343" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B344" t="n">
-        <v>1999</v>
+        <v>2011</v>
       </c>
       <c r="C344" t="n">
-        <v>174</v>
+        <v>118</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B345" t="n">
-        <v>2000</v>
+        <v>2012</v>
       </c>
       <c r="C345" t="n">
-        <v>54</v>
+        <v>118</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B346" t="n">
-        <v>2001</v>
+        <v>2013</v>
       </c>
       <c r="C346" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B347" t="n">
-        <v>2002</v>
+        <v>2014</v>
       </c>
       <c r="C347" t="n">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B348" t="n">
-        <v>2006</v>
+        <v>2015</v>
       </c>
       <c r="C348" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B349" t="n">
-        <v>2007</v>
+        <v>2016</v>
       </c>
       <c r="C349" t="n">
-        <v>29</v>
+        <v>226</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B350" t="n">
-        <v>2008</v>
+        <v>2017</v>
       </c>
       <c r="C350" t="n">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B351" t="n">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="C351" t="n">
-        <v>164</v>
+        <v>216</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -6052,13 +6052,13 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B352" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="C352" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -6068,81 +6068,81 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B353" t="n">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C353" t="n">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B354" t="n">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="C354" t="n">
-        <v>73</v>
+        <v>285</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B355" t="n">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="C355" t="n">
-        <v>176</v>
+        <v>209</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B356" t="n">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="C356" t="n">
-        <v>253</v>
+        <v>149</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B357" t="n">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="C357" t="n">
-        <v>96</v>
+        <v>444</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -6151,14 +6151,14 @@
         <v>11</v>
       </c>
       <c r="B358" t="n">
-        <v>2017</v>
+        <v>1972</v>
       </c>
       <c r="C358" t="n">
-        <v>279</v>
+        <v>12</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
@@ -6167,14 +6167,14 @@
         <v>11</v>
       </c>
       <c r="B359" t="n">
-        <v>2018</v>
+        <v>1973</v>
       </c>
       <c r="C359" t="n">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
@@ -6183,14 +6183,14 @@
         <v>11</v>
       </c>
       <c r="B360" t="n">
-        <v>2019</v>
+        <v>1974</v>
       </c>
       <c r="C360" t="n">
-        <v>342</v>
+        <v>6</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
@@ -6199,14 +6199,14 @@
         <v>11</v>
       </c>
       <c r="B361" t="n">
-        <v>2020</v>
+        <v>1977</v>
       </c>
       <c r="C361" t="n">
-        <v>333</v>
+        <v>5</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
@@ -6215,14 +6215,14 @@
         <v>11</v>
       </c>
       <c r="B362" t="n">
-        <v>2021</v>
+        <v>1981</v>
       </c>
       <c r="C362" t="n">
-        <v>242</v>
+        <v>2</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -6231,14 +6231,14 @@
         <v>11</v>
       </c>
       <c r="B363" t="n">
-        <v>2022</v>
+        <v>1983</v>
       </c>
       <c r="C363" t="n">
-        <v>295</v>
+        <v>13</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -6247,14 +6247,14 @@
         <v>11</v>
       </c>
       <c r="B364" t="n">
-        <v>2023</v>
+        <v>1994</v>
       </c>
       <c r="C364" t="n">
-        <v>403</v>
+        <v>38</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -6263,298 +6263,298 @@
         <v>11</v>
       </c>
       <c r="B365" t="n">
-        <v>2024</v>
+        <v>1995</v>
       </c>
       <c r="C365" t="n">
-        <v>662</v>
+        <v>53</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B366" t="n">
-        <v>1972</v>
+        <v>1998</v>
       </c>
       <c r="C366" t="n">
-        <v>12</v>
+        <v>126</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B367" t="n">
-        <v>1973</v>
+        <v>1999</v>
       </c>
       <c r="C367" t="n">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B368" t="n">
-        <v>1974</v>
+        <v>2000</v>
       </c>
       <c r="C368" t="n">
-        <v>6</v>
+        <v>91</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B369" t="n">
-        <v>1977</v>
+        <v>2001</v>
       </c>
       <c r="C369" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B370" t="n">
-        <v>1981</v>
+        <v>2002</v>
       </c>
       <c r="C370" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B371" t="n">
-        <v>1983</v>
+        <v>2004</v>
       </c>
       <c r="C371" t="n">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B372" t="n">
-        <v>1994</v>
+        <v>2005</v>
       </c>
       <c r="C372" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B373" t="n">
-        <v>1995</v>
+        <v>2006</v>
       </c>
       <c r="C373" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B374" t="n">
-        <v>1998</v>
+        <v>2009</v>
       </c>
       <c r="C374" t="n">
-        <v>126</v>
+        <v>23</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B375" t="n">
-        <v>1999</v>
+        <v>2010</v>
       </c>
       <c r="C375" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B376" t="n">
-        <v>2000</v>
+        <v>2011</v>
       </c>
       <c r="C376" t="n">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B377" t="n">
-        <v>2001</v>
+        <v>2012</v>
       </c>
       <c r="C377" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B378" t="n">
-        <v>2002</v>
+        <v>2013</v>
       </c>
       <c r="C378" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B379" t="n">
-        <v>2004</v>
+        <v>2014</v>
       </c>
       <c r="C379" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B380" t="n">
-        <v>2005</v>
+        <v>2015</v>
       </c>
       <c r="C380" t="n">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B381" t="n">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C381" t="n">
-        <v>34</v>
+        <v>172</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B382" t="n">
-        <v>2009</v>
+        <v>2017</v>
       </c>
       <c r="C382" t="n">
-        <v>23</v>
+        <v>209</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B383" t="n">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="C383" t="n">
-        <v>55</v>
+        <v>233</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -6564,13 +6564,13 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B384" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="C384" t="n">
-        <v>128</v>
+        <v>171</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -6580,81 +6580,81 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B385" t="n">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C385" t="n">
-        <v>26</v>
+        <v>174</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B386" t="n">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="C386" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B387" t="n">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="C387" t="n">
-        <v>96</v>
+        <v>217</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B388" t="n">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="C388" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B389" t="n">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="C389" t="n">
         <v>172</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -6663,14 +6663,14 @@
         <v>12</v>
       </c>
       <c r="B390" t="n">
-        <v>2017</v>
+        <v>1992</v>
       </c>
       <c r="C390" t="n">
-        <v>209</v>
+        <v>54</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -6679,14 +6679,14 @@
         <v>12</v>
       </c>
       <c r="B391" t="n">
-        <v>2018</v>
+        <v>1993</v>
       </c>
       <c r="C391" t="n">
-        <v>233</v>
+        <v>68</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -6695,14 +6695,14 @@
         <v>12</v>
       </c>
       <c r="B392" t="n">
-        <v>2019</v>
+        <v>2005</v>
       </c>
       <c r="C392" t="n">
-        <v>171</v>
+        <v>53</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -6711,14 +6711,14 @@
         <v>12</v>
       </c>
       <c r="B393" t="n">
-        <v>2020</v>
+        <v>2006</v>
       </c>
       <c r="C393" t="n">
-        <v>174</v>
+        <v>38</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -6727,14 +6727,14 @@
         <v>12</v>
       </c>
       <c r="B394" t="n">
-        <v>2021</v>
+        <v>2010</v>
       </c>
       <c r="C394" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -6743,14 +6743,14 @@
         <v>12</v>
       </c>
       <c r="B395" t="n">
-        <v>2022</v>
+        <v>2011</v>
       </c>
       <c r="C395" t="n">
-        <v>217</v>
+        <v>67</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -6759,14 +6759,14 @@
         <v>12</v>
       </c>
       <c r="B396" t="n">
-        <v>2023</v>
+        <v>2013</v>
       </c>
       <c r="C396" t="n">
-        <v>72</v>
+        <v>119</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -6775,174 +6775,174 @@
         <v>12</v>
       </c>
       <c r="B397" t="n">
-        <v>2024</v>
+        <v>2014</v>
       </c>
       <c r="C397" t="n">
-        <v>172</v>
+        <v>29</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B398" t="n">
-        <v>1972</v>
+        <v>2015</v>
       </c>
       <c r="C398" t="n">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B399" t="n">
-        <v>1974</v>
+        <v>2016</v>
       </c>
       <c r="C399" t="n">
-        <v>3</v>
+        <v>112</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B400" t="n">
-        <v>1975</v>
+        <v>2017</v>
       </c>
       <c r="C400" t="n">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B401" t="n">
-        <v>1977</v>
+        <v>2018</v>
       </c>
       <c r="C401" t="n">
-        <v>125</v>
+        <v>92</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B402" t="n">
-        <v>1978</v>
+        <v>2019</v>
       </c>
       <c r="C402" t="n">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B403" t="n">
-        <v>1979</v>
+        <v>2020</v>
       </c>
       <c r="C403" t="n">
-        <v>81</v>
+        <v>498</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B404" t="n">
-        <v>1980</v>
+        <v>2021</v>
       </c>
       <c r="C404" t="n">
-        <v>95</v>
+        <v>403</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B405" t="n">
-        <v>1985</v>
+        <v>2022</v>
       </c>
       <c r="C405" t="n">
-        <v>62</v>
+        <v>280</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B406" t="n">
-        <v>1987</v>
+        <v>2023</v>
       </c>
       <c r="C406" t="n">
-        <v>3</v>
+        <v>493</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B407" t="n">
-        <v>1989</v>
+        <v>2024</v>
       </c>
       <c r="C407" t="n">
-        <v>49</v>
+        <v>208</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -6951,14 +6951,14 @@
         <v>13</v>
       </c>
       <c r="B408" t="n">
-        <v>1991</v>
+        <v>1971</v>
       </c>
       <c r="C408" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
@@ -6967,14 +6967,14 @@
         <v>13</v>
       </c>
       <c r="B409" t="n">
-        <v>1992</v>
+        <v>1976</v>
       </c>
       <c r="C409" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
@@ -6983,14 +6983,14 @@
         <v>13</v>
       </c>
       <c r="B410" t="n">
-        <v>1993</v>
+        <v>1978</v>
       </c>
       <c r="C410" t="n">
-        <v>191</v>
+        <v>37</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
@@ -6999,14 +6999,14 @@
         <v>13</v>
       </c>
       <c r="B411" t="n">
-        <v>1994</v>
+        <v>1986</v>
       </c>
       <c r="C411" t="n">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -7015,14 +7015,14 @@
         <v>13</v>
       </c>
       <c r="B412" t="n">
-        <v>1995</v>
+        <v>1987</v>
       </c>
       <c r="C412" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -7031,10 +7031,10 @@
         <v>13</v>
       </c>
       <c r="B413" t="n">
-        <v>1996</v>
+        <v>1991</v>
       </c>
       <c r="C413" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -7047,10 +7047,10 @@
         <v>13</v>
       </c>
       <c r="B414" t="n">
-        <v>1998</v>
+        <v>1992</v>
       </c>
       <c r="C414" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -7063,10 +7063,10 @@
         <v>13</v>
       </c>
       <c r="B415" t="n">
-        <v>1999</v>
+        <v>1993</v>
       </c>
       <c r="C415" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -7079,10 +7079,10 @@
         <v>13</v>
       </c>
       <c r="B416" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="C416" t="n">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -7095,10 +7095,10 @@
         <v>13</v>
       </c>
       <c r="B417" t="n">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="C417" t="n">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -7111,10 +7111,10 @@
         <v>13</v>
       </c>
       <c r="B418" t="n">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="C418" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -7127,10 +7127,10 @@
         <v>13</v>
       </c>
       <c r="B419" t="n">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="C419" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -7143,10 +7143,10 @@
         <v>13</v>
       </c>
       <c r="B420" t="n">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="C420" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -7159,10 +7159,10 @@
         <v>13</v>
       </c>
       <c r="B421" t="n">
-        <v>2005</v>
+        <v>2008</v>
       </c>
       <c r="C421" t="n">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         <v>2009</v>
       </c>
       <c r="C422" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>2010</v>
       </c>
       <c r="C423" t="n">
-        <v>37</v>
+        <v>182</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>2011</v>
       </c>
       <c r="C424" t="n">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
         <v>2012</v>
       </c>
       <c r="C425" t="n">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>2013</v>
       </c>
       <c r="C426" t="n">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>2014</v>
       </c>
       <c r="C427" t="n">
-        <v>19</v>
+        <v>158</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>2015</v>
       </c>
       <c r="C428" t="n">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>2016</v>
       </c>
       <c r="C429" t="n">
-        <v>44</v>
+        <v>123</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>2017</v>
       </c>
       <c r="C430" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>2018</v>
       </c>
       <c r="C431" t="n">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>2019</v>
       </c>
       <c r="C432" t="n">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>2020</v>
       </c>
       <c r="C433" t="n">
-        <v>69</v>
+        <v>154</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>2021</v>
       </c>
       <c r="C434" t="n">
-        <v>164</v>
+        <v>233</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>2022</v>
       </c>
       <c r="C435" t="n">
-        <v>90</v>
+        <v>174</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>2023</v>
       </c>
       <c r="C436" t="n">
-        <v>297</v>
+        <v>49</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>2024</v>
       </c>
       <c r="C437" t="n">
-        <v>256</v>
+        <v>94</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -7431,14 +7431,14 @@
         <v>14</v>
       </c>
       <c r="B438" t="n">
-        <v>1971</v>
+        <v>1980</v>
       </c>
       <c r="C438" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -7447,14 +7447,14 @@
         <v>14</v>
       </c>
       <c r="B439" t="n">
-        <v>1976</v>
+        <v>1982</v>
       </c>
       <c r="C439" t="n">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -7463,14 +7463,14 @@
         <v>14</v>
       </c>
       <c r="B440" t="n">
-        <v>1978</v>
+        <v>1986</v>
       </c>
       <c r="C440" t="n">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -7479,10 +7479,10 @@
         <v>14</v>
       </c>
       <c r="B441" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="C441" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -7495,14 +7495,14 @@
         <v>14</v>
       </c>
       <c r="B442" t="n">
-        <v>1987</v>
+        <v>1991</v>
       </c>
       <c r="C442" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -7511,10 +7511,10 @@
         <v>14</v>
       </c>
       <c r="B443" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="C443" t="n">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -7527,10 +7527,10 @@
         <v>14</v>
       </c>
       <c r="B444" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="C444" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -7543,10 +7543,10 @@
         <v>14</v>
       </c>
       <c r="B445" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="C445" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -7559,14 +7559,14 @@
         <v>14</v>
       </c>
       <c r="B446" t="n">
-        <v>2001</v>
+        <v>1995</v>
       </c>
       <c r="C446" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -7575,14 +7575,14 @@
         <v>14</v>
       </c>
       <c r="B447" t="n">
-        <v>2003</v>
+        <v>1996</v>
       </c>
       <c r="C447" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -7591,14 +7591,14 @@
         <v>14</v>
       </c>
       <c r="B448" t="n">
-        <v>2004</v>
+        <v>1999</v>
       </c>
       <c r="C448" t="n">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -7607,10 +7607,10 @@
         <v>14</v>
       </c>
       <c r="B449" t="n">
-        <v>2005</v>
+        <v>2000</v>
       </c>
       <c r="C449" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -7623,10 +7623,10 @@
         <v>14</v>
       </c>
       <c r="B450" t="n">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="C450" t="n">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -7639,10 +7639,10 @@
         <v>14</v>
       </c>
       <c r="B451" t="n">
-        <v>2008</v>
+        <v>2002</v>
       </c>
       <c r="C451" t="n">
-        <v>31</v>
+        <v>174</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -7655,10 +7655,10 @@
         <v>14</v>
       </c>
       <c r="B452" t="n">
-        <v>2009</v>
+        <v>2003</v>
       </c>
       <c r="C452" t="n">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -7671,14 +7671,14 @@
         <v>14</v>
       </c>
       <c r="B453" t="n">
-        <v>2010</v>
+        <v>2004</v>
       </c>
       <c r="C453" t="n">
-        <v>182</v>
+        <v>43</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -7687,14 +7687,14 @@
         <v>14</v>
       </c>
       <c r="B454" t="n">
-        <v>2011</v>
+        <v>2005</v>
       </c>
       <c r="C454" t="n">
-        <v>40</v>
+        <v>211</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -7703,14 +7703,14 @@
         <v>14</v>
       </c>
       <c r="B455" t="n">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="C455" t="n">
-        <v>122</v>
+        <v>29</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -7719,14 +7719,14 @@
         <v>14</v>
       </c>
       <c r="B456" t="n">
-        <v>2013</v>
+        <v>2007</v>
       </c>
       <c r="C456" t="n">
-        <v>83</v>
+        <v>242</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -7735,14 +7735,14 @@
         <v>14</v>
       </c>
       <c r="B457" t="n">
-        <v>2014</v>
+        <v>2008</v>
       </c>
       <c r="C457" t="n">
-        <v>158</v>
+        <v>109</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -7751,14 +7751,14 @@
         <v>14</v>
       </c>
       <c r="B458" t="n">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="C458" t="n">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -7767,10 +7767,10 @@
         <v>14</v>
       </c>
       <c r="B459" t="n">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="C459" t="n">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -7783,10 +7783,10 @@
         <v>14</v>
       </c>
       <c r="B460" t="n">
-        <v>2017</v>
+        <v>2011</v>
       </c>
       <c r="C460" t="n">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -7799,10 +7799,10 @@
         <v>14</v>
       </c>
       <c r="B461" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="C461" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -7815,10 +7815,10 @@
         <v>14</v>
       </c>
       <c r="B462" t="n">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="C462" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -7831,14 +7831,14 @@
         <v>14</v>
       </c>
       <c r="B463" t="n">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="C463" t="n">
-        <v>154</v>
+        <v>40</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -7847,14 +7847,14 @@
         <v>14</v>
       </c>
       <c r="B464" t="n">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="C464" t="n">
-        <v>233</v>
+        <v>139</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -7863,14 +7863,14 @@
         <v>14</v>
       </c>
       <c r="B465" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C465" t="n">
-        <v>174</v>
+        <v>99</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -7879,14 +7879,14 @@
         <v>14</v>
       </c>
       <c r="B466" t="n">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="C466" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -7895,110 +7895,110 @@
         <v>14</v>
       </c>
       <c r="B467" t="n">
-        <v>2024</v>
+        <v>2018</v>
       </c>
       <c r="C467" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B468" t="n">
-        <v>1980</v>
+        <v>2019</v>
       </c>
       <c r="C468" t="n">
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B469" t="n">
-        <v>1982</v>
+        <v>2020</v>
       </c>
       <c r="C469" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B470" t="n">
-        <v>1986</v>
+        <v>2021</v>
       </c>
       <c r="C470" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B471" t="n">
-        <v>1987</v>
+        <v>2022</v>
       </c>
       <c r="C471" t="n">
-        <v>45</v>
+        <v>144</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B472" t="n">
-        <v>1991</v>
+        <v>2023</v>
       </c>
       <c r="C472" t="n">
-        <v>59</v>
+        <v>190</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B473" t="n">
-        <v>1992</v>
+        <v>2024</v>
       </c>
       <c r="C473" t="n">
-        <v>104</v>
+        <v>227</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -8007,14 +8007,14 @@
         <v>15</v>
       </c>
       <c r="B474" t="n">
-        <v>1993</v>
+        <v>1980</v>
       </c>
       <c r="C474" t="n">
-        <v>43</v>
+        <v>146</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -8023,14 +8023,14 @@
         <v>15</v>
       </c>
       <c r="B475" t="n">
-        <v>1994</v>
+        <v>1982</v>
       </c>
       <c r="C475" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -8039,14 +8039,14 @@
         <v>15</v>
       </c>
       <c r="B476" t="n">
-        <v>1995</v>
+        <v>1985</v>
       </c>
       <c r="C476" t="n">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -8055,14 +8055,14 @@
         <v>15</v>
       </c>
       <c r="B477" t="n">
-        <v>1996</v>
+        <v>1987</v>
       </c>
       <c r="C477" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -8071,10 +8071,10 @@
         <v>15</v>
       </c>
       <c r="B478" t="n">
-        <v>1999</v>
+        <v>1991</v>
       </c>
       <c r="C478" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -8087,14 +8087,14 @@
         <v>15</v>
       </c>
       <c r="B479" t="n">
-        <v>2000</v>
+        <v>1992</v>
       </c>
       <c r="C479" t="n">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -8103,14 +8103,14 @@
         <v>15</v>
       </c>
       <c r="B480" t="n">
-        <v>2001</v>
+        <v>1994</v>
       </c>
       <c r="C480" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -8119,14 +8119,14 @@
         <v>15</v>
       </c>
       <c r="B481" t="n">
-        <v>2002</v>
+        <v>1995</v>
       </c>
       <c r="C481" t="n">
-        <v>174</v>
+        <v>33</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -8135,14 +8135,14 @@
         <v>15</v>
       </c>
       <c r="B482" t="n">
-        <v>2003</v>
+        <v>1996</v>
       </c>
       <c r="C482" t="n">
-        <v>110</v>
+        <v>29</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -8151,14 +8151,14 @@
         <v>15</v>
       </c>
       <c r="B483" t="n">
-        <v>2004</v>
+        <v>1997</v>
       </c>
       <c r="C483" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -8167,14 +8167,14 @@
         <v>15</v>
       </c>
       <c r="B484" t="n">
-        <v>2005</v>
+        <v>1998</v>
       </c>
       <c r="C484" t="n">
-        <v>211</v>
+        <v>114</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -8183,14 +8183,14 @@
         <v>15</v>
       </c>
       <c r="B485" t="n">
-        <v>2006</v>
+        <v>1999</v>
       </c>
       <c r="C485" t="n">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -8199,10 +8199,10 @@
         <v>15</v>
       </c>
       <c r="B486" t="n">
-        <v>2007</v>
+        <v>2000</v>
       </c>
       <c r="C486" t="n">
-        <v>242</v>
+        <v>54</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -8215,10 +8215,10 @@
         <v>15</v>
       </c>
       <c r="B487" t="n">
-        <v>2008</v>
+        <v>2002</v>
       </c>
       <c r="C487" t="n">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -8231,10 +8231,10 @@
         <v>15</v>
       </c>
       <c r="B488" t="n">
-        <v>2009</v>
+        <v>2004</v>
       </c>
       <c r="C488" t="n">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -8247,14 +8247,14 @@
         <v>15</v>
       </c>
       <c r="B489" t="n">
-        <v>2010</v>
+        <v>2005</v>
       </c>
       <c r="C489" t="n">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -8263,14 +8263,14 @@
         <v>15</v>
       </c>
       <c r="B490" t="n">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="C490" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -8279,14 +8279,14 @@
         <v>15</v>
       </c>
       <c r="B491" t="n">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="C491" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -8295,14 +8295,14 @@
         <v>15</v>
       </c>
       <c r="B492" t="n">
-        <v>2013</v>
+        <v>2009</v>
       </c>
       <c r="C492" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -8311,10 +8311,10 @@
         <v>15</v>
       </c>
       <c r="B493" t="n">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C493" t="n">
-        <v>40</v>
+        <v>118</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -8327,10 +8327,10 @@
         <v>15</v>
       </c>
       <c r="B494" t="n">
-        <v>2015</v>
+        <v>2011</v>
       </c>
       <c r="C494" t="n">
-        <v>139</v>
+        <v>46</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -8343,10 +8343,10 @@
         <v>15</v>
       </c>
       <c r="B495" t="n">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C495" t="n">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -8359,10 +8359,10 @@
         <v>15</v>
       </c>
       <c r="B496" t="n">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="C496" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -8375,10 +8375,10 @@
         <v>15</v>
       </c>
       <c r="B497" t="n">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="C497" t="n">
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -8391,10 +8391,10 @@
         <v>15</v>
       </c>
       <c r="B498" t="n">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="C498" t="n">
-        <v>113</v>
+        <v>49</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -8407,14 +8407,14 @@
         <v>15</v>
       </c>
       <c r="B499" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C499" t="n">
-        <v>40</v>
+        <v>128</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -8423,14 +8423,14 @@
         <v>15</v>
       </c>
       <c r="B500" t="n">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="C500" t="n">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -8439,14 +8439,14 @@
         <v>15</v>
       </c>
       <c r="B501" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C501" t="n">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -8455,10 +8455,10 @@
         <v>15</v>
       </c>
       <c r="B502" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="C502" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -8471,10 +8471,10 @@
         <v>15</v>
       </c>
       <c r="B503" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="C503" t="n">
-        <v>227</v>
+        <v>88</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -8484,527 +8484,47 @@
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B504" t="n">
-        <v>1980</v>
+        <v>2022</v>
       </c>
       <c r="C504" t="n">
-        <v>146</v>
+        <v>68</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B505" t="n">
-        <v>1982</v>
+        <v>2023</v>
       </c>
       <c r="C505" t="n">
-        <v>14</v>
+        <v>130</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B506" t="n">
-        <v>1985</v>
+        <v>2024</v>
       </c>
       <c r="C506" t="n">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="D506" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
-    </row>
-    <row r="507">
-      <c r="A507" t="n">
-        <v>16</v>
-      </c>
-      <c r="B507" t="n">
-        <v>1987</v>
-      </c>
-      <c r="C507" t="n">
-        <v>54</v>
-      </c>
-      <c r="D507" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
-      </c>
-    </row>
-    <row r="508">
-      <c r="A508" t="n">
-        <v>16</v>
-      </c>
-      <c r="B508" t="n">
-        <v>1991</v>
-      </c>
-      <c r="C508" t="n">
-        <v>62</v>
-      </c>
-      <c r="D508" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509" t="n">
-        <v>16</v>
-      </c>
-      <c r="B509" t="n">
-        <v>1992</v>
-      </c>
-      <c r="C509" t="n">
-        <v>97</v>
-      </c>
-      <c r="D509" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
-    </row>
-    <row r="510">
-      <c r="A510" t="n">
-        <v>16</v>
-      </c>
-      <c r="B510" t="n">
-        <v>1994</v>
-      </c>
-      <c r="C510" t="n">
-        <v>78</v>
-      </c>
-      <c r="D510" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511" t="n">
-        <v>16</v>
-      </c>
-      <c r="B511" t="n">
-        <v>1995</v>
-      </c>
-      <c r="C511" t="n">
-        <v>33</v>
-      </c>
-      <c r="D511" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
-    </row>
-    <row r="512">
-      <c r="A512" t="n">
-        <v>16</v>
-      </c>
-      <c r="B512" t="n">
-        <v>1996</v>
-      </c>
-      <c r="C512" t="n">
-        <v>29</v>
-      </c>
-      <c r="D512" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
-    </row>
-    <row r="513">
-      <c r="A513" t="n">
-        <v>16</v>
-      </c>
-      <c r="B513" t="n">
-        <v>1997</v>
-      </c>
-      <c r="C513" t="n">
-        <v>26</v>
-      </c>
-      <c r="D513" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
-    </row>
-    <row r="514">
-      <c r="A514" t="n">
-        <v>16</v>
-      </c>
-      <c r="B514" t="n">
-        <v>1998</v>
-      </c>
-      <c r="C514" t="n">
-        <v>114</v>
-      </c>
-      <c r="D514" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
-    </row>
-    <row r="515">
-      <c r="A515" t="n">
-        <v>16</v>
-      </c>
-      <c r="B515" t="n">
-        <v>1999</v>
-      </c>
-      <c r="C515" t="n">
-        <v>75</v>
-      </c>
-      <c r="D515" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
-      </c>
-    </row>
-    <row r="516">
-      <c r="A516" t="n">
-        <v>16</v>
-      </c>
-      <c r="B516" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C516" t="n">
-        <v>54</v>
-      </c>
-      <c r="D516" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517" t="n">
-        <v>16</v>
-      </c>
-      <c r="B517" t="n">
-        <v>2002</v>
-      </c>
-      <c r="C517" t="n">
-        <v>77</v>
-      </c>
-      <c r="D517" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
-    </row>
-    <row r="518">
-      <c r="A518" t="n">
-        <v>16</v>
-      </c>
-      <c r="B518" t="n">
-        <v>2004</v>
-      </c>
-      <c r="C518" t="n">
-        <v>64</v>
-      </c>
-      <c r="D518" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
-    </row>
-    <row r="519">
-      <c r="A519" t="n">
-        <v>16</v>
-      </c>
-      <c r="B519" t="n">
-        <v>2005</v>
-      </c>
-      <c r="C519" t="n">
-        <v>30</v>
-      </c>
-      <c r="D519" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
-    </row>
-    <row r="520">
-      <c r="A520" t="n">
-        <v>16</v>
-      </c>
-      <c r="B520" t="n">
-        <v>2006</v>
-      </c>
-      <c r="C520" t="n">
-        <v>46</v>
-      </c>
-      <c r="D520" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521" t="n">
-        <v>16</v>
-      </c>
-      <c r="B521" t="n">
-        <v>2008</v>
-      </c>
-      <c r="C521" t="n">
-        <v>7</v>
-      </c>
-      <c r="D521" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
-    </row>
-    <row r="522">
-      <c r="A522" t="n">
-        <v>16</v>
-      </c>
-      <c r="B522" t="n">
-        <v>2009</v>
-      </c>
-      <c r="C522" t="n">
-        <v>54</v>
-      </c>
-      <c r="D522" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
-    </row>
-    <row r="523">
-      <c r="A523" t="n">
-        <v>16</v>
-      </c>
-      <c r="B523" t="n">
-        <v>2010</v>
-      </c>
-      <c r="C523" t="n">
-        <v>118</v>
-      </c>
-      <c r="D523" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
-    </row>
-    <row r="524">
-      <c r="A524" t="n">
-        <v>16</v>
-      </c>
-      <c r="B524" t="n">
-        <v>2011</v>
-      </c>
-      <c r="C524" t="n">
-        <v>46</v>
-      </c>
-      <c r="D524" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
-    </row>
-    <row r="525">
-      <c r="A525" t="n">
-        <v>16</v>
-      </c>
-      <c r="B525" t="n">
-        <v>2012</v>
-      </c>
-      <c r="C525" t="n">
-        <v>44</v>
-      </c>
-      <c r="D525" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
-    </row>
-    <row r="526">
-      <c r="A526" t="n">
-        <v>16</v>
-      </c>
-      <c r="B526" t="n">
-        <v>2013</v>
-      </c>
-      <c r="C526" t="n">
-        <v>40</v>
-      </c>
-      <c r="D526" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
-    </row>
-    <row r="527">
-      <c r="A527" t="n">
-        <v>16</v>
-      </c>
-      <c r="B527" t="n">
-        <v>2014</v>
-      </c>
-      <c r="C527" t="n">
-        <v>50</v>
-      </c>
-      <c r="D527" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
-    </row>
-    <row r="528">
-      <c r="A528" t="n">
-        <v>16</v>
-      </c>
-      <c r="B528" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C528" t="n">
-        <v>49</v>
-      </c>
-      <c r="D528" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
-    </row>
-    <row r="529">
-      <c r="A529" t="n">
-        <v>16</v>
-      </c>
-      <c r="B529" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C529" t="n">
-        <v>128</v>
-      </c>
-      <c r="D529" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
-    </row>
-    <row r="530">
-      <c r="A530" t="n">
-        <v>16</v>
-      </c>
-      <c r="B530" t="n">
-        <v>2017</v>
-      </c>
-      <c r="C530" t="n">
-        <v>58</v>
-      </c>
-      <c r="D530" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
-    </row>
-    <row r="531">
-      <c r="A531" t="n">
-        <v>16</v>
-      </c>
-      <c r="B531" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C531" t="n">
-        <v>118</v>
-      </c>
-      <c r="D531" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
-    </row>
-    <row r="532">
-      <c r="A532" t="n">
-        <v>16</v>
-      </c>
-      <c r="B532" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C532" t="n">
-        <v>150</v>
-      </c>
-      <c r="D532" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
-    </row>
-    <row r="533">
-      <c r="A533" t="n">
-        <v>16</v>
-      </c>
-      <c r="B533" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C533" t="n">
-        <v>88</v>
-      </c>
-      <c r="D533" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
-    </row>
-    <row r="534">
-      <c r="A534" t="n">
-        <v>16</v>
-      </c>
-      <c r="B534" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C534" t="n">
-        <v>68</v>
-      </c>
-      <c r="D534" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
-    </row>
-    <row r="535">
-      <c r="A535" t="n">
-        <v>16</v>
-      </c>
-      <c r="B535" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C535" t="n">
-        <v>130</v>
-      </c>
-      <c r="D535" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
-    </row>
-    <row r="536">
-      <c r="A536" t="n">
-        <v>16</v>
-      </c>
-      <c r="B536" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C536" t="n">
-        <v>111</v>
-      </c>
-      <c r="D536" t="inlineStr">
         <is>
           <t>2020s</t>
         </is>

--- a/evolution/new_word_count_df.xlsx
+++ b/evolution/new_word_count_df.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="C2" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -487,10 +487,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>1984</v>
+        <v>1980</v>
       </c>
       <c r="C4" t="n">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -503,10 +503,10 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>1985</v>
+        <v>1981</v>
       </c>
       <c r="C5" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -519,10 +519,10 @@
         <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="C6" t="n">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -535,10 +535,10 @@
         <v>1</v>
       </c>
       <c r="B7" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="C7" t="n">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -551,10 +551,10 @@
         <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="C8" t="n">
-        <v>29</v>
+        <v>124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -567,14 +567,14 @@
         <v>1</v>
       </c>
       <c r="B9" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
         <v>1991</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
         <v>1992</v>
       </c>
       <c r="C11" t="n">
-        <v>206</v>
+        <v>175</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         <v>1993</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>167</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
         <v>1994</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>1995</v>
       </c>
       <c r="C14" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>1996</v>
       </c>
       <c r="C15" t="n">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         <v>1997</v>
       </c>
       <c r="C16" t="n">
-        <v>165</v>
+        <v>263</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>1998</v>
       </c>
       <c r="C17" t="n">
-        <v>78</v>
+        <v>247</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>1999</v>
       </c>
       <c r="C18" t="n">
-        <v>12</v>
+        <v>139</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>2000</v>
       </c>
       <c r="C19" t="n">
-        <v>38</v>
+        <v>131</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>2001</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         <v>2002</v>
       </c>
       <c r="C21" t="n">
-        <v>64</v>
+        <v>198</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>2003</v>
       </c>
       <c r="C22" t="n">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>2004</v>
       </c>
       <c r="C23" t="n">
-        <v>17</v>
+        <v>108</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>2005</v>
       </c>
       <c r="C24" t="n">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>2006</v>
       </c>
       <c r="C25" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         <v>2007</v>
       </c>
       <c r="C26" t="n">
-        <v>159</v>
+        <v>109</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>2008</v>
       </c>
       <c r="C27" t="n">
-        <v>35</v>
+        <v>175</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>2009</v>
       </c>
       <c r="C28" t="n">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>2010</v>
       </c>
       <c r="C29" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>2011</v>
       </c>
       <c r="C30" t="n">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>2012</v>
       </c>
       <c r="C31" t="n">
-        <v>174</v>
+        <v>215</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>2013</v>
       </c>
       <c r="C32" t="n">
-        <v>159</v>
+        <v>373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>2014</v>
       </c>
       <c r="C33" t="n">
-        <v>189</v>
+        <v>251</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>2015</v>
       </c>
       <c r="C34" t="n">
-        <v>229</v>
+        <v>145</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>2016</v>
       </c>
       <c r="C35" t="n">
-        <v>136</v>
+        <v>271</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>2017</v>
       </c>
       <c r="C36" t="n">
-        <v>203</v>
+        <v>292</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>2018</v>
       </c>
       <c r="C37" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>2019</v>
       </c>
       <c r="C38" t="n">
-        <v>155</v>
+        <v>434</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>2020</v>
       </c>
       <c r="C39" t="n">
-        <v>203</v>
+        <v>491</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>2021</v>
       </c>
       <c r="C40" t="n">
-        <v>237</v>
+        <v>402</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>2022</v>
       </c>
       <c r="C41" t="n">
-        <v>213</v>
+        <v>452</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>2023</v>
       </c>
       <c r="C42" t="n">
-        <v>278</v>
+        <v>639</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>2024</v>
       </c>
       <c r="C43" t="n">
-        <v>390</v>
+        <v>501</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1124,17 +1124,17 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B44" t="n">
-        <v>1972</v>
+        <v>2025</v>
       </c>
       <c r="C44" t="n">
-        <v>5</v>
+        <v>299</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -1143,10 +1143,10 @@
         <v>2</v>
       </c>
       <c r="B45" t="n">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="C45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1159,10 +1159,10 @@
         <v>2</v>
       </c>
       <c r="B46" t="n">
-        <v>1977</v>
+        <v>1973</v>
       </c>
       <c r="C46" t="n">
-        <v>147</v>
+        <v>6</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
         <v>2</v>
       </c>
       <c r="B47" t="n">
-        <v>1978</v>
+        <v>1974</v>
       </c>
       <c r="C47" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1191,10 +1191,10 @@
         <v>2</v>
       </c>
       <c r="B48" t="n">
-        <v>1979</v>
+        <v>1976</v>
       </c>
       <c r="C48" t="n">
-        <v>117</v>
+        <v>58</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1207,14 +1207,14 @@
         <v>2</v>
       </c>
       <c r="B49" t="n">
-        <v>1980</v>
+        <v>1977</v>
       </c>
       <c r="C49" t="n">
-        <v>213</v>
+        <v>138</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
@@ -1223,14 +1223,14 @@
         <v>2</v>
       </c>
       <c r="B50" t="n">
-        <v>1981</v>
+        <v>1978</v>
       </c>
       <c r="C50" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
@@ -1239,14 +1239,14 @@
         <v>2</v>
       </c>
       <c r="B51" t="n">
-        <v>1982</v>
+        <v>1979</v>
       </c>
       <c r="C51" t="n">
-        <v>36</v>
+        <v>238</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
@@ -1255,10 +1255,10 @@
         <v>2</v>
       </c>
       <c r="B52" t="n">
-        <v>1983</v>
+        <v>1980</v>
       </c>
       <c r="C52" t="n">
-        <v>69</v>
+        <v>152</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1271,10 +1271,10 @@
         <v>2</v>
       </c>
       <c r="B53" t="n">
-        <v>1984</v>
+        <v>1981</v>
       </c>
       <c r="C53" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
         <v>2</v>
       </c>
       <c r="B54" t="n">
-        <v>1986</v>
+        <v>1982</v>
       </c>
       <c r="C54" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -1303,14 +1303,14 @@
         <v>2</v>
       </c>
       <c r="B55" t="n">
-        <v>1990</v>
+        <v>1983</v>
       </c>
       <c r="C55" t="n">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -1319,14 +1319,14 @@
         <v>2</v>
       </c>
       <c r="B56" t="n">
-        <v>1991</v>
+        <v>1984</v>
       </c>
       <c r="C56" t="n">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -1335,14 +1335,14 @@
         <v>2</v>
       </c>
       <c r="B57" t="n">
-        <v>1992</v>
+        <v>1986</v>
       </c>
       <c r="C57" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -1351,14 +1351,14 @@
         <v>2</v>
       </c>
       <c r="B58" t="n">
-        <v>1994</v>
+        <v>1987</v>
       </c>
       <c r="C58" t="n">
-        <v>126</v>
+        <v>25</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -1367,10 +1367,10 @@
         <v>2</v>
       </c>
       <c r="B59" t="n">
-        <v>1995</v>
+        <v>1992</v>
       </c>
       <c r="C59" t="n">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -1383,10 +1383,10 @@
         <v>2</v>
       </c>
       <c r="B60" t="n">
-        <v>1996</v>
+        <v>1993</v>
       </c>
       <c r="C60" t="n">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -1399,10 +1399,10 @@
         <v>2</v>
       </c>
       <c r="B61" t="n">
-        <v>1997</v>
+        <v>1994</v>
       </c>
       <c r="C61" t="n">
-        <v>61</v>
+        <v>179</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -1415,10 +1415,10 @@
         <v>2</v>
       </c>
       <c r="B62" t="n">
-        <v>1998</v>
+        <v>1995</v>
       </c>
       <c r="C62" t="n">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         <v>2</v>
       </c>
       <c r="B63" t="n">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="C63" t="n">
-        <v>123</v>
+        <v>48</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -1447,14 +1447,14 @@
         <v>2</v>
       </c>
       <c r="B64" t="n">
-        <v>2000</v>
+        <v>1997</v>
       </c>
       <c r="C64" t="n">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -1463,14 +1463,14 @@
         <v>2</v>
       </c>
       <c r="B65" t="n">
-        <v>2001</v>
+        <v>1998</v>
       </c>
       <c r="C65" t="n">
-        <v>104</v>
+        <v>186</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -1479,14 +1479,14 @@
         <v>2</v>
       </c>
       <c r="B66" t="n">
-        <v>2002</v>
+        <v>1999</v>
       </c>
       <c r="C66" t="n">
-        <v>93</v>
+        <v>160</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -1495,10 +1495,10 @@
         <v>2</v>
       </c>
       <c r="B67" t="n">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="C67" t="n">
-        <v>41</v>
+        <v>164</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -1511,10 +1511,10 @@
         <v>2</v>
       </c>
       <c r="B68" t="n">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="C68" t="n">
-        <v>18</v>
+        <v>109</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -1527,10 +1527,10 @@
         <v>2</v>
       </c>
       <c r="B69" t="n">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="C69" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -1543,10 +1543,10 @@
         <v>2</v>
       </c>
       <c r="B70" t="n">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="C70" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
         <v>2</v>
       </c>
       <c r="B71" t="n">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="C71" t="n">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -1575,10 +1575,10 @@
         <v>2</v>
       </c>
       <c r="B72" t="n">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="C72" t="n">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
         <v>2</v>
       </c>
       <c r="B73" t="n">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="C73" t="n">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -1607,14 +1607,14 @@
         <v>2</v>
       </c>
       <c r="B74" t="n">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="C74" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -1623,14 +1623,14 @@
         <v>2</v>
       </c>
       <c r="B75" t="n">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="C75" t="n">
-        <v>201</v>
+        <v>85</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -1639,14 +1639,14 @@
         <v>2</v>
       </c>
       <c r="B76" t="n">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="C76" t="n">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -1655,10 +1655,10 @@
         <v>2</v>
       </c>
       <c r="B77" t="n">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="C77" t="n">
-        <v>196</v>
+        <v>130</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -1671,10 +1671,10 @@
         <v>2</v>
       </c>
       <c r="B78" t="n">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="C78" t="n">
-        <v>79</v>
+        <v>261</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -1687,10 +1687,10 @@
         <v>2</v>
       </c>
       <c r="B79" t="n">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="C79" t="n">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -1703,10 +1703,10 @@
         <v>2</v>
       </c>
       <c r="B80" t="n">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="C80" t="n">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -1719,10 +1719,10 @@
         <v>2</v>
       </c>
       <c r="B81" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="C81" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         <v>2</v>
       </c>
       <c r="B82" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="C82" t="n">
-        <v>188</v>
+        <v>144</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -1751,10 +1751,10 @@
         <v>2</v>
       </c>
       <c r="B83" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C83" t="n">
-        <v>104</v>
+        <v>140</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -1767,14 +1767,14 @@
         <v>2</v>
       </c>
       <c r="B84" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C84" t="n">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -1783,14 +1783,14 @@
         <v>2</v>
       </c>
       <c r="B85" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C85" t="n">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -1799,14 +1799,14 @@
         <v>2</v>
       </c>
       <c r="B86" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C86" t="n">
-        <v>99</v>
+        <v>166</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -1815,10 +1815,10 @@
         <v>2</v>
       </c>
       <c r="B87" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="C87" t="n">
-        <v>150</v>
+        <v>208</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -1831,10 +1831,10 @@
         <v>2</v>
       </c>
       <c r="B88" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="C88" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -1844,65 +1844,65 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B89" t="n">
-        <v>1972</v>
+        <v>2022</v>
       </c>
       <c r="C89" t="n">
-        <v>12</v>
+        <v>204</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B90" t="n">
-        <v>1974</v>
+        <v>2023</v>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>248</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B91" t="n">
-        <v>1975</v>
+        <v>2024</v>
       </c>
       <c r="C91" t="n">
-        <v>7</v>
+        <v>202</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B92" t="n">
-        <v>1977</v>
+        <v>2025</v>
       </c>
       <c r="C92" t="n">
-        <v>174</v>
+        <v>53</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -1911,10 +1911,10 @@
         <v>3</v>
       </c>
       <c r="B93" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="C93" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -1927,14 +1927,14 @@
         <v>3</v>
       </c>
       <c r="B94" t="n">
-        <v>1979</v>
+        <v>1987</v>
       </c>
       <c r="C94" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -1943,10 +1943,10 @@
         <v>3</v>
       </c>
       <c r="B95" t="n">
-        <v>1980</v>
+        <v>1988</v>
       </c>
       <c r="C95" t="n">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -1959,10 +1959,10 @@
         <v>3</v>
       </c>
       <c r="B96" t="n">
-        <v>1985</v>
+        <v>1989</v>
       </c>
       <c r="C96" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -1975,14 +1975,14 @@
         <v>3</v>
       </c>
       <c r="B97" t="n">
-        <v>1987</v>
+        <v>1991</v>
       </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -1991,14 +1991,14 @@
         <v>3</v>
       </c>
       <c r="B98" t="n">
-        <v>1989</v>
+        <v>1992</v>
       </c>
       <c r="C98" t="n">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -2007,10 +2007,10 @@
         <v>3</v>
       </c>
       <c r="B99" t="n">
-        <v>1990</v>
+        <v>1993</v>
       </c>
       <c r="C99" t="n">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -2023,10 +2023,10 @@
         <v>3</v>
       </c>
       <c r="B100" t="n">
-        <v>1991</v>
+        <v>1994</v>
       </c>
       <c r="C100" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -2039,10 +2039,10 @@
         <v>3</v>
       </c>
       <c r="B101" t="n">
-        <v>1992</v>
+        <v>1995</v>
       </c>
       <c r="C101" t="n">
-        <v>166</v>
+        <v>30</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -2055,10 +2055,10 @@
         <v>3</v>
       </c>
       <c r="B102" t="n">
-        <v>1993</v>
+        <v>1996</v>
       </c>
       <c r="C102" t="n">
-        <v>233</v>
+        <v>86</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -2071,10 +2071,10 @@
         <v>3</v>
       </c>
       <c r="B103" t="n">
-        <v>1994</v>
+        <v>1997</v>
       </c>
       <c r="C103" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -2087,10 +2087,10 @@
         <v>3</v>
       </c>
       <c r="B104" t="n">
-        <v>1995</v>
+        <v>1998</v>
       </c>
       <c r="C104" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -2103,10 +2103,10 @@
         <v>3</v>
       </c>
       <c r="B105" t="n">
-        <v>1996</v>
+        <v>1999</v>
       </c>
       <c r="C105" t="n">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -2119,14 +2119,14 @@
         <v>3</v>
       </c>
       <c r="B106" t="n">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="C106" t="n">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -2135,14 +2135,14 @@
         <v>3</v>
       </c>
       <c r="B107" t="n">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="C107" t="n">
         <v>20</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -2151,10 +2151,10 @@
         <v>3</v>
       </c>
       <c r="B108" t="n">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="C108" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -2167,10 +2167,10 @@
         <v>3</v>
       </c>
       <c r="B109" t="n">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="C109" t="n">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -2183,10 +2183,10 @@
         <v>3</v>
       </c>
       <c r="B110" t="n">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="C110" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -2199,10 +2199,10 @@
         <v>3</v>
       </c>
       <c r="B111" t="n">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="C111" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -2215,10 +2215,10 @@
         <v>3</v>
       </c>
       <c r="B112" t="n">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="C112" t="n">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -2231,10 +2231,10 @@
         <v>3</v>
       </c>
       <c r="B113" t="n">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="C113" t="n">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -2247,10 +2247,10 @@
         <v>3</v>
       </c>
       <c r="B114" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="C114" t="n">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -2263,10 +2263,10 @@
         <v>3</v>
       </c>
       <c r="B115" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="C115" t="n">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -2279,14 +2279,14 @@
         <v>3</v>
       </c>
       <c r="B116" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="C116" t="n">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -2295,10 +2295,10 @@
         <v>3</v>
       </c>
       <c r="B117" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="C117" t="n">
-        <v>34</v>
+        <v>108</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -2311,10 +2311,10 @@
         <v>3</v>
       </c>
       <c r="B118" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="C118" t="n">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -2327,10 +2327,10 @@
         <v>3</v>
       </c>
       <c r="B119" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="C119" t="n">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -2343,10 +2343,10 @@
         <v>3</v>
       </c>
       <c r="B120" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="C120" t="n">
-        <v>159</v>
+        <v>123</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -2359,10 +2359,10 @@
         <v>3</v>
       </c>
       <c r="B121" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="C121" t="n">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -2375,10 +2375,10 @@
         <v>3</v>
       </c>
       <c r="B122" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C122" t="n">
-        <v>185</v>
+        <v>114</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -2391,10 +2391,10 @@
         <v>3</v>
       </c>
       <c r="B123" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C123" t="n">
-        <v>153</v>
+        <v>224</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -2407,10 +2407,10 @@
         <v>3</v>
       </c>
       <c r="B124" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C124" t="n">
-        <v>189</v>
+        <v>133</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -2423,10 +2423,10 @@
         <v>3</v>
       </c>
       <c r="B125" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C125" t="n">
-        <v>256</v>
+        <v>144</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -2439,14 +2439,14 @@
         <v>3</v>
       </c>
       <c r="B126" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C126" t="n">
-        <v>270</v>
+        <v>151</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -2455,10 +2455,10 @@
         <v>3</v>
       </c>
       <c r="B127" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C127" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -2471,10 +2471,10 @@
         <v>3</v>
       </c>
       <c r="B128" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C128" t="n">
-        <v>204</v>
+        <v>153</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -2487,10 +2487,10 @@
         <v>3</v>
       </c>
       <c r="B129" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C129" t="n">
-        <v>263</v>
+        <v>165</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -2503,10 +2503,10 @@
         <v>3</v>
       </c>
       <c r="B130" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C130" t="n">
-        <v>278</v>
+        <v>208</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -2519,10 +2519,10 @@
         <v>3</v>
       </c>
       <c r="B131" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C131" t="n">
-        <v>380</v>
+        <v>87</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -2535,10 +2535,10 @@
         <v>4</v>
       </c>
       <c r="B132" t="n">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="C132" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -2551,14 +2551,14 @@
         <v>4</v>
       </c>
       <c r="B133" t="n">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="C133" t="n">
-        <v>182</v>
+        <v>4</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2570,7 @@
         <v>1985</v>
       </c>
       <c r="C134" t="n">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -2583,10 +2583,10 @@
         <v>4</v>
       </c>
       <c r="B135" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="C135" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -2599,14 +2599,14 @@
         <v>4</v>
       </c>
       <c r="B136" t="n">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="C136" t="n">
-        <v>132</v>
+        <v>200</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -2615,10 +2615,10 @@
         <v>4</v>
       </c>
       <c r="B137" t="n">
-        <v>1990</v>
+        <v>1993</v>
       </c>
       <c r="C137" t="n">
-        <v>110</v>
+        <v>162</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -2631,10 +2631,10 @@
         <v>4</v>
       </c>
       <c r="B138" t="n">
-        <v>1991</v>
+        <v>1996</v>
       </c>
       <c r="C138" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -2647,10 +2647,10 @@
         <v>4</v>
       </c>
       <c r="B139" t="n">
-        <v>1992</v>
+        <v>1997</v>
       </c>
       <c r="C139" t="n">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -2663,10 +2663,10 @@
         <v>4</v>
       </c>
       <c r="B140" t="n">
-        <v>1994</v>
+        <v>1998</v>
       </c>
       <c r="C140" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -2679,10 +2679,10 @@
         <v>4</v>
       </c>
       <c r="B141" t="n">
-        <v>1996</v>
+        <v>1999</v>
       </c>
       <c r="C141" t="n">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -2695,14 +2695,14 @@
         <v>4</v>
       </c>
       <c r="B142" t="n">
-        <v>1997</v>
+        <v>2000</v>
       </c>
       <c r="C142" t="n">
-        <v>268</v>
+        <v>68</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -2711,14 +2711,14 @@
         <v>4</v>
       </c>
       <c r="B143" t="n">
-        <v>1998</v>
+        <v>2001</v>
       </c>
       <c r="C143" t="n">
-        <v>247</v>
+        <v>130</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -2727,14 +2727,14 @@
         <v>4</v>
       </c>
       <c r="B144" t="n">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="C144" t="n">
-        <v>179</v>
+        <v>95</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -2743,10 +2743,10 @@
         <v>4</v>
       </c>
       <c r="B145" t="n">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="C145" t="n">
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -2759,10 +2759,10 @@
         <v>4</v>
       </c>
       <c r="B146" t="n">
-        <v>2001</v>
+        <v>2006</v>
       </c>
       <c r="C146" t="n">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="B147" t="n">
-        <v>2002</v>
+        <v>2007</v>
       </c>
       <c r="C147" t="n">
-        <v>154</v>
+        <v>48</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -2791,10 +2791,10 @@
         <v>4</v>
       </c>
       <c r="B148" t="n">
-        <v>2003</v>
+        <v>2009</v>
       </c>
       <c r="C148" t="n">
-        <v>160</v>
+        <v>36</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -2807,14 +2807,14 @@
         <v>4</v>
       </c>
       <c r="B149" t="n">
-        <v>2004</v>
+        <v>2010</v>
       </c>
       <c r="C149" t="n">
-        <v>39</v>
+        <v>111</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -2823,14 +2823,14 @@
         <v>4</v>
       </c>
       <c r="B150" t="n">
-        <v>2005</v>
+        <v>2011</v>
       </c>
       <c r="C150" t="n">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -2839,14 +2839,14 @@
         <v>4</v>
       </c>
       <c r="B151" t="n">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="C151" t="n">
-        <v>61</v>
+        <v>218</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -2855,14 +2855,14 @@
         <v>4</v>
       </c>
       <c r="B152" t="n">
-        <v>2007</v>
+        <v>2013</v>
       </c>
       <c r="C152" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -2871,14 +2871,14 @@
         <v>4</v>
       </c>
       <c r="B153" t="n">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="C153" t="n">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -2887,14 +2887,14 @@
         <v>4</v>
       </c>
       <c r="B154" t="n">
-        <v>2009</v>
+        <v>2015</v>
       </c>
       <c r="C154" t="n">
-        <v>99</v>
+        <v>299</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -2903,10 +2903,10 @@
         <v>4</v>
       </c>
       <c r="B155" t="n">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C155" t="n">
-        <v>88</v>
+        <v>180</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -2919,10 +2919,10 @@
         <v>4</v>
       </c>
       <c r="B156" t="n">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="C156" t="n">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -2935,10 +2935,10 @@
         <v>4</v>
       </c>
       <c r="B157" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="C157" t="n">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
         <v>4</v>
       </c>
       <c r="B158" t="n">
-        <v>2013</v>
+        <v>2019</v>
       </c>
       <c r="C158" t="n">
-        <v>289</v>
+        <v>234</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -2967,14 +2967,14 @@
         <v>4</v>
       </c>
       <c r="B159" t="n">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="C159" t="n">
-        <v>248</v>
+        <v>323</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -2983,14 +2983,14 @@
         <v>4</v>
       </c>
       <c r="B160" t="n">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="C160" t="n">
-        <v>223</v>
+        <v>277</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -2999,14 +2999,14 @@
         <v>4</v>
       </c>
       <c r="B161" t="n">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="C161" t="n">
-        <v>211</v>
+        <v>340</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -3015,14 +3015,14 @@
         <v>4</v>
       </c>
       <c r="B162" t="n">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="C162" t="n">
-        <v>102</v>
+        <v>537</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -3031,14 +3031,14 @@
         <v>4</v>
       </c>
       <c r="B163" t="n">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="C163" t="n">
-        <v>204</v>
+        <v>705</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -3047,94 +3047,94 @@
         <v>4</v>
       </c>
       <c r="B164" t="n">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C164" t="n">
-        <v>188</v>
+        <v>297</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B165" t="n">
-        <v>2020</v>
+        <v>1972</v>
       </c>
       <c r="C165" t="n">
-        <v>251</v>
+        <v>7</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B166" t="n">
-        <v>2021</v>
+        <v>1975</v>
       </c>
       <c r="C166" t="n">
-        <v>238</v>
+        <v>7</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B167" t="n">
-        <v>2022</v>
+        <v>1977</v>
       </c>
       <c r="C167" t="n">
-        <v>161</v>
+        <v>104</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B168" t="n">
-        <v>2023</v>
+        <v>1979</v>
       </c>
       <c r="C168" t="n">
-        <v>470</v>
+        <v>41</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B169" t="n">
-        <v>2024</v>
+        <v>1989</v>
       </c>
       <c r="C169" t="n">
-        <v>360</v>
+        <v>69</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -3143,14 +3143,14 @@
         <v>5</v>
       </c>
       <c r="B170" t="n">
-        <v>1972</v>
+        <v>1992</v>
       </c>
       <c r="C170" t="n">
-        <v>6</v>
+        <v>154</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -3159,14 +3159,14 @@
         <v>5</v>
       </c>
       <c r="B171" t="n">
-        <v>1985</v>
+        <v>1993</v>
       </c>
       <c r="C171" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -3175,14 +3175,14 @@
         <v>5</v>
       </c>
       <c r="B172" t="n">
-        <v>1987</v>
+        <v>1994</v>
       </c>
       <c r="C172" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -3191,10 +3191,10 @@
         <v>5</v>
       </c>
       <c r="B173" t="n">
-        <v>1991</v>
+        <v>1996</v>
       </c>
       <c r="C173" t="n">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -3207,10 +3207,10 @@
         <v>5</v>
       </c>
       <c r="B174" t="n">
-        <v>1992</v>
+        <v>1998</v>
       </c>
       <c r="C174" t="n">
-        <v>52</v>
+        <v>172</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -3223,14 +3223,14 @@
         <v>5</v>
       </c>
       <c r="B175" t="n">
-        <v>1993</v>
+        <v>2000</v>
       </c>
       <c r="C175" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3239,14 +3239,14 @@
         <v>5</v>
       </c>
       <c r="B176" t="n">
-        <v>1994</v>
+        <v>2001</v>
       </c>
       <c r="C176" t="n">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3255,14 +3255,14 @@
         <v>5</v>
       </c>
       <c r="B177" t="n">
-        <v>1995</v>
+        <v>2003</v>
       </c>
       <c r="C177" t="n">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3271,14 +3271,14 @@
         <v>5</v>
       </c>
       <c r="B178" t="n">
-        <v>1996</v>
+        <v>2004</v>
       </c>
       <c r="C178" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3287,14 +3287,14 @@
         <v>5</v>
       </c>
       <c r="B179" t="n">
-        <v>1997</v>
+        <v>2005</v>
       </c>
       <c r="C179" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3303,14 +3303,14 @@
         <v>5</v>
       </c>
       <c r="B180" t="n">
-        <v>1998</v>
+        <v>2007</v>
       </c>
       <c r="C180" t="n">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3319,14 +3319,14 @@
         <v>5</v>
       </c>
       <c r="B181" t="n">
-        <v>1999</v>
+        <v>2008</v>
       </c>
       <c r="C181" t="n">
-        <v>76</v>
+        <v>148</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3335,10 +3335,10 @@
         <v>5</v>
       </c>
       <c r="B182" t="n">
-        <v>2001</v>
+        <v>2009</v>
       </c>
       <c r="C182" t="n">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -3351,14 +3351,14 @@
         <v>5</v>
       </c>
       <c r="B183" t="n">
-        <v>2002</v>
+        <v>2010</v>
       </c>
       <c r="C183" t="n">
-        <v>181</v>
+        <v>27</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -3367,14 +3367,14 @@
         <v>5</v>
       </c>
       <c r="B184" t="n">
-        <v>2003</v>
+        <v>2011</v>
       </c>
       <c r="C184" t="n">
-        <v>80</v>
+        <v>189</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -3383,14 +3383,14 @@
         <v>5</v>
       </c>
       <c r="B185" t="n">
-        <v>2004</v>
+        <v>2012</v>
       </c>
       <c r="C185" t="n">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -3399,14 +3399,14 @@
         <v>5</v>
       </c>
       <c r="B186" t="n">
-        <v>2006</v>
+        <v>2013</v>
       </c>
       <c r="C186" t="n">
-        <v>130</v>
+        <v>275</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -3415,14 +3415,14 @@
         <v>5</v>
       </c>
       <c r="B187" t="n">
-        <v>2007</v>
+        <v>2014</v>
       </c>
       <c r="C187" t="n">
-        <v>85</v>
+        <v>166</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -3431,14 +3431,14 @@
         <v>5</v>
       </c>
       <c r="B188" t="n">
-        <v>2008</v>
+        <v>2015</v>
       </c>
       <c r="C188" t="n">
-        <v>135</v>
+        <v>217</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -3447,14 +3447,14 @@
         <v>5</v>
       </c>
       <c r="B189" t="n">
-        <v>2009</v>
+        <v>2016</v>
       </c>
       <c r="C189" t="n">
-        <v>101</v>
+        <v>208</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -3463,10 +3463,10 @@
         <v>5</v>
       </c>
       <c r="B190" t="n">
-        <v>2010</v>
+        <v>2017</v>
       </c>
       <c r="C190" t="n">
-        <v>96</v>
+        <v>274</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -3479,10 +3479,10 @@
         <v>5</v>
       </c>
       <c r="B191" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="C191" t="n">
-        <v>56</v>
+        <v>448</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -3495,10 +3495,10 @@
         <v>5</v>
       </c>
       <c r="B192" t="n">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="C192" t="n">
-        <v>39</v>
+        <v>231</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -3511,14 +3511,14 @@
         <v>5</v>
       </c>
       <c r="B193" t="n">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="C193" t="n">
-        <v>127</v>
+        <v>177</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -3527,14 +3527,14 @@
         <v>5</v>
       </c>
       <c r="B194" t="n">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="C194" t="n">
-        <v>167</v>
+        <v>458</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -3543,14 +3543,14 @@
         <v>5</v>
       </c>
       <c r="B195" t="n">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="C195" t="n">
-        <v>145</v>
+        <v>330</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -3559,14 +3559,14 @@
         <v>5</v>
       </c>
       <c r="B196" t="n">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="C196" t="n">
-        <v>147</v>
+        <v>190</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -3575,14 +3575,14 @@
         <v>5</v>
       </c>
       <c r="B197" t="n">
-        <v>2017</v>
+        <v>2024</v>
       </c>
       <c r="C197" t="n">
-        <v>85</v>
+        <v>482</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -3591,110 +3591,110 @@
         <v>5</v>
       </c>
       <c r="B198" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="C198" t="n">
-        <v>143</v>
+        <v>95</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B199" t="n">
-        <v>2019</v>
+        <v>1972</v>
       </c>
       <c r="C199" t="n">
-        <v>178</v>
+        <v>6</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B200" t="n">
-        <v>2020</v>
+        <v>1976</v>
       </c>
       <c r="C200" t="n">
-        <v>188</v>
+        <v>63</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B201" t="n">
-        <v>2021</v>
+        <v>1979</v>
       </c>
       <c r="C201" t="n">
-        <v>198</v>
+        <v>11</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B202" t="n">
-        <v>2022</v>
+        <v>1992</v>
       </c>
       <c r="C202" t="n">
-        <v>135</v>
+        <v>59</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B203" t="n">
-        <v>2023</v>
+        <v>1993</v>
       </c>
       <c r="C203" t="n">
-        <v>168</v>
+        <v>55</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B204" t="n">
-        <v>2024</v>
+        <v>1994</v>
       </c>
       <c r="C204" t="n">
-        <v>322</v>
+        <v>24</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -3703,14 +3703,14 @@
         <v>6</v>
       </c>
       <c r="B205" t="n">
-        <v>1976</v>
+        <v>1995</v>
       </c>
       <c r="C205" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -3719,14 +3719,14 @@
         <v>6</v>
       </c>
       <c r="B206" t="n">
-        <v>1978</v>
+        <v>1996</v>
       </c>
       <c r="C206" t="n">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -3735,14 +3735,14 @@
         <v>6</v>
       </c>
       <c r="B207" t="n">
-        <v>1981</v>
+        <v>1998</v>
       </c>
       <c r="C207" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -3751,14 +3751,14 @@
         <v>6</v>
       </c>
       <c r="B208" t="n">
-        <v>1992</v>
+        <v>2002</v>
       </c>
       <c r="C208" t="n">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3767,14 +3767,14 @@
         <v>6</v>
       </c>
       <c r="B209" t="n">
-        <v>1993</v>
+        <v>2003</v>
       </c>
       <c r="C209" t="n">
-        <v>123</v>
+        <v>75</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3783,14 +3783,14 @@
         <v>6</v>
       </c>
       <c r="B210" t="n">
-        <v>1994</v>
+        <v>2004</v>
       </c>
       <c r="C210" t="n">
-        <v>36</v>
+        <v>204</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3799,14 +3799,14 @@
         <v>6</v>
       </c>
       <c r="B211" t="n">
-        <v>1996</v>
+        <v>2006</v>
       </c>
       <c r="C211" t="n">
-        <v>29</v>
+        <v>135</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3815,14 +3815,14 @@
         <v>6</v>
       </c>
       <c r="B212" t="n">
-        <v>1998</v>
+        <v>2007</v>
       </c>
       <c r="C212" t="n">
-        <v>34</v>
+        <v>140</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -3831,10 +3831,10 @@
         <v>6</v>
       </c>
       <c r="B213" t="n">
-        <v>2000</v>
+        <v>2008</v>
       </c>
       <c r="C213" t="n">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -3847,10 +3847,10 @@
         <v>6</v>
       </c>
       <c r="B214" t="n">
-        <v>2002</v>
+        <v>2009</v>
       </c>
       <c r="C214" t="n">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -3863,14 +3863,14 @@
         <v>6</v>
       </c>
       <c r="B215" t="n">
-        <v>2003</v>
+        <v>2010</v>
       </c>
       <c r="C215" t="n">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -3879,14 +3879,14 @@
         <v>6</v>
       </c>
       <c r="B216" t="n">
-        <v>2004</v>
+        <v>2011</v>
       </c>
       <c r="C216" t="n">
-        <v>158</v>
+        <v>60</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -3895,14 +3895,14 @@
         <v>6</v>
       </c>
       <c r="B217" t="n">
-        <v>2005</v>
+        <v>2012</v>
       </c>
       <c r="C217" t="n">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -3911,14 +3911,14 @@
         <v>6</v>
       </c>
       <c r="B218" t="n">
-        <v>2006</v>
+        <v>2013</v>
       </c>
       <c r="C218" t="n">
-        <v>33</v>
+        <v>147</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -3927,14 +3927,14 @@
         <v>6</v>
       </c>
       <c r="B219" t="n">
-        <v>2007</v>
+        <v>2014</v>
       </c>
       <c r="C219" t="n">
-        <v>41</v>
+        <v>141</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -3943,14 +3943,14 @@
         <v>6</v>
       </c>
       <c r="B220" t="n">
-        <v>2008</v>
+        <v>2015</v>
       </c>
       <c r="C220" t="n">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -3959,14 +3959,14 @@
         <v>6</v>
       </c>
       <c r="B221" t="n">
-        <v>2009</v>
+        <v>2016</v>
       </c>
       <c r="C221" t="n">
-        <v>68</v>
+        <v>121</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -3975,10 +3975,10 @@
         <v>6</v>
       </c>
       <c r="B222" t="n">
-        <v>2010</v>
+        <v>2017</v>
       </c>
       <c r="C222" t="n">
-        <v>157</v>
+        <v>114</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -3991,10 +3991,10 @@
         <v>6</v>
       </c>
       <c r="B223" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="C223" t="n">
-        <v>269</v>
+        <v>133</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -4007,10 +4007,10 @@
         <v>6</v>
       </c>
       <c r="B224" t="n">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="C224" t="n">
-        <v>9</v>
+        <v>174</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -4023,14 +4023,14 @@
         <v>6</v>
       </c>
       <c r="B225" t="n">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="C225" t="n">
-        <v>294</v>
+        <v>217</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -4039,14 +4039,14 @@
         <v>6</v>
       </c>
       <c r="B226" t="n">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="C226" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -4055,14 +4055,14 @@
         <v>6</v>
       </c>
       <c r="B227" t="n">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="C227" t="n">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -4071,14 +4071,14 @@
         <v>6</v>
       </c>
       <c r="B228" t="n">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="C228" t="n">
-        <v>304</v>
+        <v>137</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -4087,14 +4087,14 @@
         <v>6</v>
       </c>
       <c r="B229" t="n">
-        <v>2017</v>
+        <v>2024</v>
       </c>
       <c r="C229" t="n">
-        <v>339</v>
+        <v>237</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -4103,110 +4103,110 @@
         <v>6</v>
       </c>
       <c r="B230" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="C230" t="n">
-        <v>201</v>
+        <v>90</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B231" t="n">
-        <v>2019</v>
+        <v>1981</v>
       </c>
       <c r="C231" t="n">
-        <v>325</v>
+        <v>11</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B232" t="n">
-        <v>2020</v>
+        <v>1991</v>
       </c>
       <c r="C232" t="n">
-        <v>346</v>
+        <v>11</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B233" t="n">
-        <v>2021</v>
+        <v>1992</v>
       </c>
       <c r="C233" t="n">
-        <v>389</v>
+        <v>108</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B234" t="n">
-        <v>2022</v>
+        <v>1993</v>
       </c>
       <c r="C234" t="n">
-        <v>555</v>
+        <v>72</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B235" t="n">
-        <v>2023</v>
+        <v>1995</v>
       </c>
       <c r="C235" t="n">
-        <v>449</v>
+        <v>47</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B236" t="n">
-        <v>2024</v>
+        <v>1996</v>
       </c>
       <c r="C236" t="n">
-        <v>587</v>
+        <v>54</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -4215,14 +4215,14 @@
         <v>7</v>
       </c>
       <c r="B237" t="n">
-        <v>1976</v>
+        <v>1997</v>
       </c>
       <c r="C237" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -4231,14 +4231,14 @@
         <v>7</v>
       </c>
       <c r="B238" t="n">
-        <v>1979</v>
+        <v>1998</v>
       </c>
       <c r="C238" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -4247,14 +4247,14 @@
         <v>7</v>
       </c>
       <c r="B239" t="n">
-        <v>1980</v>
+        <v>1999</v>
       </c>
       <c r="C239" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -4263,14 +4263,14 @@
         <v>7</v>
       </c>
       <c r="B240" t="n">
-        <v>1986</v>
+        <v>2000</v>
       </c>
       <c r="C240" t="n">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -4279,14 +4279,14 @@
         <v>7</v>
       </c>
       <c r="B241" t="n">
-        <v>1991</v>
+        <v>2001</v>
       </c>
       <c r="C241" t="n">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -4295,14 +4295,14 @@
         <v>7</v>
       </c>
       <c r="B242" t="n">
-        <v>1992</v>
+        <v>2002</v>
       </c>
       <c r="C242" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -4311,14 +4311,14 @@
         <v>7</v>
       </c>
       <c r="B243" t="n">
-        <v>1993</v>
+        <v>2003</v>
       </c>
       <c r="C243" t="n">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -4327,14 +4327,14 @@
         <v>7</v>
       </c>
       <c r="B244" t="n">
-        <v>1994</v>
+        <v>2004</v>
       </c>
       <c r="C244" t="n">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -4343,14 +4343,14 @@
         <v>7</v>
       </c>
       <c r="B245" t="n">
-        <v>1995</v>
+        <v>2005</v>
       </c>
       <c r="C245" t="n">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -4359,14 +4359,14 @@
         <v>7</v>
       </c>
       <c r="B246" t="n">
-        <v>1996</v>
+        <v>2006</v>
       </c>
       <c r="C246" t="n">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -4375,14 +4375,14 @@
         <v>7</v>
       </c>
       <c r="B247" t="n">
-        <v>1997</v>
+        <v>2007</v>
       </c>
       <c r="C247" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -4391,14 +4391,14 @@
         <v>7</v>
       </c>
       <c r="B248" t="n">
-        <v>1998</v>
+        <v>2008</v>
       </c>
       <c r="C248" t="n">
-        <v>151</v>
+        <v>58</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -4407,14 +4407,14 @@
         <v>7</v>
       </c>
       <c r="B249" t="n">
-        <v>1999</v>
+        <v>2009</v>
       </c>
       <c r="C249" t="n">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -4423,14 +4423,14 @@
         <v>7</v>
       </c>
       <c r="B250" t="n">
-        <v>2000</v>
+        <v>2010</v>
       </c>
       <c r="C250" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -4439,14 +4439,14 @@
         <v>7</v>
       </c>
       <c r="B251" t="n">
-        <v>2002</v>
+        <v>2011</v>
       </c>
       <c r="C251" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -4455,14 +4455,14 @@
         <v>7</v>
       </c>
       <c r="B252" t="n">
-        <v>2003</v>
+        <v>2012</v>
       </c>
       <c r="C252" t="n">
-        <v>10</v>
+        <v>118</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -4471,14 +4471,14 @@
         <v>7</v>
       </c>
       <c r="B253" t="n">
-        <v>2005</v>
+        <v>2013</v>
       </c>
       <c r="C253" t="n">
-        <v>61</v>
+        <v>207</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -4487,14 +4487,14 @@
         <v>7</v>
       </c>
       <c r="B254" t="n">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="C254" t="n">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -4503,14 +4503,14 @@
         <v>7</v>
       </c>
       <c r="B255" t="n">
-        <v>2007</v>
+        <v>2015</v>
       </c>
       <c r="C255" t="n">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -4519,14 +4519,14 @@
         <v>7</v>
       </c>
       <c r="B256" t="n">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="C256" t="n">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -4535,14 +4535,14 @@
         <v>7</v>
       </c>
       <c r="B257" t="n">
-        <v>2009</v>
+        <v>2017</v>
       </c>
       <c r="C257" t="n">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -4551,10 +4551,10 @@
         <v>7</v>
       </c>
       <c r="B258" t="n">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="C258" t="n">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>7</v>
       </c>
       <c r="B259" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="C259" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -4583,14 +4583,14 @@
         <v>7</v>
       </c>
       <c r="B260" t="n">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C260" t="n">
-        <v>116</v>
+        <v>186</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -4599,14 +4599,14 @@
         <v>7</v>
       </c>
       <c r="B261" t="n">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="C261" t="n">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -4615,14 +4615,14 @@
         <v>7</v>
       </c>
       <c r="B262" t="n">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="C262" t="n">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -4631,14 +4631,14 @@
         <v>7</v>
       </c>
       <c r="B263" t="n">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="C263" t="n">
-        <v>124</v>
+        <v>187</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -4647,14 +4647,14 @@
         <v>7</v>
       </c>
       <c r="B264" t="n">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="C264" t="n">
-        <v>84</v>
+        <v>321</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -4663,126 +4663,126 @@
         <v>7</v>
       </c>
       <c r="B265" t="n">
-        <v>2017</v>
+        <v>2025</v>
       </c>
       <c r="C265" t="n">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B266" t="n">
-        <v>2018</v>
+        <v>1978</v>
       </c>
       <c r="C266" t="n">
-        <v>167</v>
+        <v>48</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B267" t="n">
-        <v>2019</v>
+        <v>1979</v>
       </c>
       <c r="C267" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B268" t="n">
-        <v>2020</v>
+        <v>1984</v>
       </c>
       <c r="C268" t="n">
-        <v>201</v>
+        <v>49</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B269" t="n">
-        <v>2021</v>
+        <v>1986</v>
       </c>
       <c r="C269" t="n">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B270" t="n">
-        <v>2022</v>
+        <v>1987</v>
       </c>
       <c r="C270" t="n">
-        <v>161</v>
+        <v>47</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B271" t="n">
-        <v>2023</v>
+        <v>1988</v>
       </c>
       <c r="C271" t="n">
-        <v>169</v>
+        <v>27</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B272" t="n">
-        <v>2024</v>
+        <v>1991</v>
       </c>
       <c r="C272" t="n">
-        <v>171</v>
+        <v>9</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -4791,14 +4791,14 @@
         <v>8</v>
       </c>
       <c r="B273" t="n">
-        <v>1981</v>
+        <v>1992</v>
       </c>
       <c r="C273" t="n">
-        <v>11</v>
+        <v>190</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -4807,10 +4807,10 @@
         <v>8</v>
       </c>
       <c r="B274" t="n">
-        <v>1991</v>
+        <v>1993</v>
       </c>
       <c r="C274" t="n">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -4823,10 +4823,10 @@
         <v>8</v>
       </c>
       <c r="B275" t="n">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="C275" t="n">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -4839,10 +4839,10 @@
         <v>8</v>
       </c>
       <c r="B276" t="n">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="C276" t="n">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -4855,10 +4855,10 @@
         <v>8</v>
       </c>
       <c r="B277" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="C277" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -4871,10 +4871,10 @@
         <v>8</v>
       </c>
       <c r="B278" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="C278" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -4887,10 +4887,10 @@
         <v>8</v>
       </c>
       <c r="B279" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="C279" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -4903,10 +4903,10 @@
         <v>8</v>
       </c>
       <c r="B280" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="C280" t="n">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -4919,10 +4919,10 @@
         <v>8</v>
       </c>
       <c r="B281" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="C281" t="n">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B282" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="C282" t="n">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -4951,10 +4951,10 @@
         <v>8</v>
       </c>
       <c r="B283" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="C283" t="n">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -4967,10 +4967,10 @@
         <v>8</v>
       </c>
       <c r="B284" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="C284" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -4983,10 +4983,10 @@
         <v>8</v>
       </c>
       <c r="B285" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="C285" t="n">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -4999,10 +4999,10 @@
         <v>8</v>
       </c>
       <c r="B286" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="C286" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -5015,10 +5015,10 @@
         <v>8</v>
       </c>
       <c r="B287" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="C287" t="n">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -5031,10 +5031,10 @@
         <v>8</v>
       </c>
       <c r="B288" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="C288" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -5047,10 +5047,10 @@
         <v>8</v>
       </c>
       <c r="B289" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="C289" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -5063,14 +5063,14 @@
         <v>8</v>
       </c>
       <c r="B290" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="C290" t="n">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -5079,10 +5079,10 @@
         <v>8</v>
       </c>
       <c r="B291" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="C291" t="n">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -5095,10 +5095,10 @@
         <v>8</v>
       </c>
       <c r="B292" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="C292" t="n">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -5111,10 +5111,10 @@
         <v>8</v>
       </c>
       <c r="B293" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="C293" t="n">
-        <v>134</v>
+        <v>31</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -5127,10 +5127,10 @@
         <v>8</v>
       </c>
       <c r="B294" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="C294" t="n">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -5143,10 +5143,10 @@
         <v>8</v>
       </c>
       <c r="B295" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="C295" t="n">
-        <v>95</v>
+        <v>192</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -5159,10 +5159,10 @@
         <v>8</v>
       </c>
       <c r="B296" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C296" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -5175,10 +5175,10 @@
         <v>8</v>
       </c>
       <c r="B297" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C297" t="n">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -5191,10 +5191,10 @@
         <v>8</v>
       </c>
       <c r="B298" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C298" t="n">
-        <v>138</v>
+        <v>199</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -5207,10 +5207,10 @@
         <v>8</v>
       </c>
       <c r="B299" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C299" t="n">
-        <v>85</v>
+        <v>156</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -5223,14 +5223,14 @@
         <v>8</v>
       </c>
       <c r="B300" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C300" t="n">
-        <v>105</v>
+        <v>177</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -5239,10 +5239,10 @@
         <v>8</v>
       </c>
       <c r="B301" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C301" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -5255,10 +5255,10 @@
         <v>8</v>
       </c>
       <c r="B302" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C302" t="n">
-        <v>102</v>
+        <v>164</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -5271,10 +5271,10 @@
         <v>8</v>
       </c>
       <c r="B303" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C303" t="n">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -5287,10 +5287,10 @@
         <v>8</v>
       </c>
       <c r="B304" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C304" t="n">
-        <v>222</v>
+        <v>360</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -5303,10 +5303,10 @@
         <v>8</v>
       </c>
       <c r="B305" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C305" t="n">
-        <v>381</v>
+        <v>60</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -5319,14 +5319,14 @@
         <v>9</v>
       </c>
       <c r="B306" t="n">
-        <v>1989</v>
+        <v>1976</v>
       </c>
       <c r="C306" t="n">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
@@ -5335,14 +5335,14 @@
         <v>9</v>
       </c>
       <c r="B307" t="n">
-        <v>1993</v>
+        <v>1980</v>
       </c>
       <c r="C307" t="n">
-        <v>17</v>
+        <v>286</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -5351,14 +5351,14 @@
         <v>9</v>
       </c>
       <c r="B308" t="n">
-        <v>1997</v>
+        <v>1985</v>
       </c>
       <c r="C308" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -5367,14 +5367,14 @@
         <v>9</v>
       </c>
       <c r="B309" t="n">
-        <v>1999</v>
+        <v>1986</v>
       </c>
       <c r="C309" t="n">
-        <v>174</v>
+        <v>27</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -5383,14 +5383,14 @@
         <v>9</v>
       </c>
       <c r="B310" t="n">
-        <v>2000</v>
+        <v>1991</v>
       </c>
       <c r="C310" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -5399,14 +5399,14 @@
         <v>9</v>
       </c>
       <c r="B311" t="n">
-        <v>2001</v>
+        <v>1992</v>
       </c>
       <c r="C311" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -5415,14 +5415,14 @@
         <v>9</v>
       </c>
       <c r="B312" t="n">
-        <v>2002</v>
+        <v>1993</v>
       </c>
       <c r="C312" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -5431,14 +5431,14 @@
         <v>9</v>
       </c>
       <c r="B313" t="n">
-        <v>2006</v>
+        <v>1994</v>
       </c>
       <c r="C313" t="n">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -5447,14 +5447,14 @@
         <v>9</v>
       </c>
       <c r="B314" t="n">
-        <v>2007</v>
+        <v>1995</v>
       </c>
       <c r="C314" t="n">
-        <v>29</v>
+        <v>105</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -5463,14 +5463,14 @@
         <v>9</v>
       </c>
       <c r="B315" t="n">
-        <v>2008</v>
+        <v>1996</v>
       </c>
       <c r="C315" t="n">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -5479,14 +5479,14 @@
         <v>9</v>
       </c>
       <c r="B316" t="n">
-        <v>2010</v>
+        <v>1997</v>
       </c>
       <c r="C316" t="n">
-        <v>164</v>
+        <v>30</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -5495,14 +5495,14 @@
         <v>9</v>
       </c>
       <c r="B317" t="n">
-        <v>2011</v>
+        <v>1998</v>
       </c>
       <c r="C317" t="n">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -5511,14 +5511,14 @@
         <v>9</v>
       </c>
       <c r="B318" t="n">
-        <v>2012</v>
+        <v>1999</v>
       </c>
       <c r="C318" t="n">
-        <v>221</v>
+        <v>21</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -5527,14 +5527,14 @@
         <v>9</v>
       </c>
       <c r="B319" t="n">
-        <v>2013</v>
+        <v>2000</v>
       </c>
       <c r="C319" t="n">
-        <v>73</v>
+        <v>146</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -5543,14 +5543,14 @@
         <v>9</v>
       </c>
       <c r="B320" t="n">
-        <v>2014</v>
+        <v>2001</v>
       </c>
       <c r="C320" t="n">
-        <v>176</v>
+        <v>59</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -5559,14 +5559,14 @@
         <v>9</v>
       </c>
       <c r="B321" t="n">
-        <v>2015</v>
+        <v>2002</v>
       </c>
       <c r="C321" t="n">
-        <v>253</v>
+        <v>63</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -5575,14 +5575,14 @@
         <v>9</v>
       </c>
       <c r="B322" t="n">
-        <v>2016</v>
+        <v>2003</v>
       </c>
       <c r="C322" t="n">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -5591,14 +5591,14 @@
         <v>9</v>
       </c>
       <c r="B323" t="n">
-        <v>2017</v>
+        <v>2004</v>
       </c>
       <c r="C323" t="n">
-        <v>279</v>
+        <v>47</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -5607,14 +5607,14 @@
         <v>9</v>
       </c>
       <c r="B324" t="n">
-        <v>2018</v>
+        <v>2005</v>
       </c>
       <c r="C324" t="n">
-        <v>146</v>
+        <v>23</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -5623,14 +5623,14 @@
         <v>9</v>
       </c>
       <c r="B325" t="n">
-        <v>2019</v>
+        <v>2006</v>
       </c>
       <c r="C325" t="n">
-        <v>342</v>
+        <v>57</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -5639,14 +5639,14 @@
         <v>9</v>
       </c>
       <c r="B326" t="n">
-        <v>2020</v>
+        <v>2007</v>
       </c>
       <c r="C326" t="n">
-        <v>333</v>
+        <v>35</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -5655,14 +5655,14 @@
         <v>9</v>
       </c>
       <c r="B327" t="n">
-        <v>2021</v>
+        <v>2008</v>
       </c>
       <c r="C327" t="n">
-        <v>242</v>
+        <v>27</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -5671,14 +5671,14 @@
         <v>9</v>
       </c>
       <c r="B328" t="n">
-        <v>2022</v>
+        <v>2009</v>
       </c>
       <c r="C328" t="n">
-        <v>295</v>
+        <v>68</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -5687,14 +5687,14 @@
         <v>9</v>
       </c>
       <c r="B329" t="n">
-        <v>2023</v>
+        <v>2010</v>
       </c>
       <c r="C329" t="n">
-        <v>403</v>
+        <v>103</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -5703,238 +5703,238 @@
         <v>9</v>
       </c>
       <c r="B330" t="n">
-        <v>2024</v>
+        <v>2011</v>
       </c>
       <c r="C330" t="n">
-        <v>662</v>
+        <v>62</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B331" t="n">
-        <v>1984</v>
+        <v>2012</v>
       </c>
       <c r="C331" t="n">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B332" t="n">
-        <v>1994</v>
+        <v>2013</v>
       </c>
       <c r="C332" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B333" t="n">
-        <v>1995</v>
+        <v>2014</v>
       </c>
       <c r="C333" t="n">
-        <v>38</v>
+        <v>138</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B334" t="n">
-        <v>1999</v>
+        <v>2015</v>
       </c>
       <c r="C334" t="n">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B335" t="n">
-        <v>2000</v>
+        <v>2016</v>
       </c>
       <c r="C335" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B336" t="n">
-        <v>2001</v>
+        <v>2017</v>
       </c>
       <c r="C336" t="n">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B337" t="n">
-        <v>2002</v>
+        <v>2018</v>
       </c>
       <c r="C337" t="n">
-        <v>46</v>
+        <v>134</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B338" t="n">
-        <v>2005</v>
+        <v>2019</v>
       </c>
       <c r="C338" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B339" t="n">
-        <v>2006</v>
+        <v>2020</v>
       </c>
       <c r="C339" t="n">
-        <v>38</v>
+        <v>193</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B340" t="n">
-        <v>2007</v>
+        <v>2021</v>
       </c>
       <c r="C340" t="n">
-        <v>55</v>
+        <v>124</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B341" t="n">
-        <v>2008</v>
+        <v>2022</v>
       </c>
       <c r="C341" t="n">
-        <v>167</v>
+        <v>116</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B342" t="n">
-        <v>2009</v>
+        <v>2023</v>
       </c>
       <c r="C342" t="n">
-        <v>61</v>
+        <v>150</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B343" t="n">
-        <v>2010</v>
+        <v>2024</v>
       </c>
       <c r="C343" t="n">
-        <v>42</v>
+        <v>155</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B344" t="n">
-        <v>2011</v>
+        <v>2025</v>
       </c>
       <c r="C344" t="n">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -5943,14 +5943,14 @@
         <v>10</v>
       </c>
       <c r="B345" t="n">
-        <v>2012</v>
+        <v>1984</v>
       </c>
       <c r="C345" t="n">
-        <v>118</v>
+        <v>15</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -5959,14 +5959,14 @@
         <v>10</v>
       </c>
       <c r="B346" t="n">
-        <v>2013</v>
+        <v>1985</v>
       </c>
       <c r="C346" t="n">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -5975,14 +5975,14 @@
         <v>10</v>
       </c>
       <c r="B347" t="n">
-        <v>2014</v>
+        <v>1987</v>
       </c>
       <c r="C347" t="n">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -5991,14 +5991,14 @@
         <v>10</v>
       </c>
       <c r="B348" t="n">
-        <v>2015</v>
+        <v>1992</v>
       </c>
       <c r="C348" t="n">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -6007,14 +6007,14 @@
         <v>10</v>
       </c>
       <c r="B349" t="n">
-        <v>2016</v>
+        <v>1993</v>
       </c>
       <c r="C349" t="n">
-        <v>226</v>
+        <v>44</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -6023,14 +6023,14 @@
         <v>10</v>
       </c>
       <c r="B350" t="n">
-        <v>2017</v>
+        <v>1994</v>
       </c>
       <c r="C350" t="n">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -6039,14 +6039,14 @@
         <v>10</v>
       </c>
       <c r="B351" t="n">
-        <v>2018</v>
+        <v>1995</v>
       </c>
       <c r="C351" t="n">
-        <v>216</v>
+        <v>34</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -6055,14 +6055,14 @@
         <v>10</v>
       </c>
       <c r="B352" t="n">
-        <v>2019</v>
+        <v>1998</v>
       </c>
       <c r="C352" t="n">
-        <v>127</v>
+        <v>31</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -6071,14 +6071,14 @@
         <v>10</v>
       </c>
       <c r="B353" t="n">
-        <v>2020</v>
+        <v>1999</v>
       </c>
       <c r="C353" t="n">
-        <v>269</v>
+        <v>34</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -6087,14 +6087,14 @@
         <v>10</v>
       </c>
       <c r="B354" t="n">
-        <v>2021</v>
+        <v>2000</v>
       </c>
       <c r="C354" t="n">
-        <v>285</v>
+        <v>34</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -6103,14 +6103,14 @@
         <v>10</v>
       </c>
       <c r="B355" t="n">
-        <v>2022</v>
+        <v>2001</v>
       </c>
       <c r="C355" t="n">
-        <v>209</v>
+        <v>26</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -6119,14 +6119,14 @@
         <v>10</v>
       </c>
       <c r="B356" t="n">
-        <v>2023</v>
+        <v>2002</v>
       </c>
       <c r="C356" t="n">
-        <v>149</v>
+        <v>48</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -6135,318 +6135,318 @@
         <v>10</v>
       </c>
       <c r="B357" t="n">
-        <v>2024</v>
+        <v>2005</v>
       </c>
       <c r="C357" t="n">
-        <v>444</v>
+        <v>45</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B358" t="n">
-        <v>1972</v>
+        <v>2006</v>
       </c>
       <c r="C358" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B359" t="n">
-        <v>1973</v>
+        <v>2007</v>
       </c>
       <c r="C359" t="n">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B360" t="n">
-        <v>1974</v>
+        <v>2009</v>
       </c>
       <c r="C360" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B361" t="n">
-        <v>1977</v>
+        <v>2010</v>
       </c>
       <c r="C361" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B362" t="n">
-        <v>1981</v>
+        <v>2011</v>
       </c>
       <c r="C362" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B363" t="n">
-        <v>1983</v>
+        <v>2012</v>
       </c>
       <c r="C363" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B364" t="n">
-        <v>1994</v>
+        <v>2013</v>
       </c>
       <c r="C364" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B365" t="n">
-        <v>1995</v>
+        <v>2014</v>
       </c>
       <c r="C365" t="n">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B366" t="n">
-        <v>1998</v>
+        <v>2015</v>
       </c>
       <c r="C366" t="n">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B367" t="n">
-        <v>1999</v>
+        <v>2016</v>
       </c>
       <c r="C367" t="n">
-        <v>59</v>
+        <v>133</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B368" t="n">
-        <v>2000</v>
+        <v>2017</v>
       </c>
       <c r="C368" t="n">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B369" t="n">
-        <v>2001</v>
+        <v>2018</v>
       </c>
       <c r="C369" t="n">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B370" t="n">
-        <v>2002</v>
+        <v>2019</v>
       </c>
       <c r="C370" t="n">
-        <v>15</v>
+        <v>176</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B371" t="n">
-        <v>2004</v>
+        <v>2020</v>
       </c>
       <c r="C371" t="n">
-        <v>92</v>
+        <v>232</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B372" t="n">
-        <v>2005</v>
+        <v>2021</v>
       </c>
       <c r="C372" t="n">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B373" t="n">
-        <v>2006</v>
+        <v>2022</v>
       </c>
       <c r="C373" t="n">
-        <v>34</v>
+        <v>218</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B374" t="n">
-        <v>2009</v>
+        <v>2023</v>
       </c>
       <c r="C374" t="n">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B375" t="n">
-        <v>2010</v>
+        <v>2024</v>
       </c>
       <c r="C375" t="n">
-        <v>55</v>
+        <v>364</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B376" t="n">
-        <v>2011</v>
+        <v>2025</v>
       </c>
       <c r="C376" t="n">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -6455,14 +6455,14 @@
         <v>11</v>
       </c>
       <c r="B377" t="n">
-        <v>2012</v>
+        <v>1991</v>
       </c>
       <c r="C377" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -6471,14 +6471,14 @@
         <v>11</v>
       </c>
       <c r="B378" t="n">
-        <v>2013</v>
+        <v>1993</v>
       </c>
       <c r="C378" t="n">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -6487,14 +6487,14 @@
         <v>11</v>
       </c>
       <c r="B379" t="n">
-        <v>2014</v>
+        <v>2003</v>
       </c>
       <c r="C379" t="n">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -6503,14 +6503,14 @@
         <v>11</v>
       </c>
       <c r="B380" t="n">
-        <v>2015</v>
+        <v>2005</v>
       </c>
       <c r="C380" t="n">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -6519,14 +6519,14 @@
         <v>11</v>
       </c>
       <c r="B381" t="n">
-        <v>2016</v>
+        <v>2006</v>
       </c>
       <c r="C381" t="n">
-        <v>172</v>
+        <v>37</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="B382" t="n">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="C382" t="n">
-        <v>209</v>
+        <v>61</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -6551,10 +6551,10 @@
         <v>11</v>
       </c>
       <c r="B383" t="n">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="C383" t="n">
-        <v>233</v>
+        <v>59</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -6567,10 +6567,10 @@
         <v>11</v>
       </c>
       <c r="B384" t="n">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="C384" t="n">
-        <v>171</v>
+        <v>63</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -6583,14 +6583,14 @@
         <v>11</v>
       </c>
       <c r="B385" t="n">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="C385" t="n">
-        <v>174</v>
+        <v>32</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -6599,14 +6599,14 @@
         <v>11</v>
       </c>
       <c r="B386" t="n">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="C386" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -6615,14 +6615,14 @@
         <v>11</v>
       </c>
       <c r="B387" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C387" t="n">
-        <v>217</v>
+        <v>99</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -6631,14 +6631,14 @@
         <v>11</v>
       </c>
       <c r="B388" t="n">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="C388" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -6647,126 +6647,126 @@
         <v>11</v>
       </c>
       <c r="B389" t="n">
-        <v>2024</v>
+        <v>2018</v>
       </c>
       <c r="C389" t="n">
-        <v>172</v>
+        <v>102</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B390" t="n">
-        <v>1992</v>
+        <v>2019</v>
       </c>
       <c r="C390" t="n">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B391" t="n">
-        <v>1993</v>
+        <v>2020</v>
       </c>
       <c r="C391" t="n">
-        <v>68</v>
+        <v>572</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B392" t="n">
-        <v>2005</v>
+        <v>2021</v>
       </c>
       <c r="C392" t="n">
-        <v>53</v>
+        <v>337</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B393" t="n">
-        <v>2006</v>
+        <v>2022</v>
       </c>
       <c r="C393" t="n">
-        <v>38</v>
+        <v>263</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B394" t="n">
-        <v>2010</v>
+        <v>2023</v>
       </c>
       <c r="C394" t="n">
-        <v>61</v>
+        <v>484</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B395" t="n">
-        <v>2011</v>
+        <v>2024</v>
       </c>
       <c r="C395" t="n">
-        <v>67</v>
+        <v>163</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B396" t="n">
-        <v>2013</v>
+        <v>2025</v>
       </c>
       <c r="C396" t="n">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -6775,14 +6775,14 @@
         <v>12</v>
       </c>
       <c r="B397" t="n">
-        <v>2014</v>
+        <v>1980</v>
       </c>
       <c r="C397" t="n">
-        <v>29</v>
+        <v>121</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -6791,14 +6791,14 @@
         <v>12</v>
       </c>
       <c r="B398" t="n">
-        <v>2015</v>
+        <v>1986</v>
       </c>
       <c r="C398" t="n">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -6807,14 +6807,14 @@
         <v>12</v>
       </c>
       <c r="B399" t="n">
-        <v>2016</v>
+        <v>1987</v>
       </c>
       <c r="C399" t="n">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -6823,14 +6823,14 @@
         <v>12</v>
       </c>
       <c r="B400" t="n">
-        <v>2017</v>
+        <v>1990</v>
       </c>
       <c r="C400" t="n">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -6839,14 +6839,14 @@
         <v>12</v>
       </c>
       <c r="B401" t="n">
-        <v>2018</v>
+        <v>1991</v>
       </c>
       <c r="C401" t="n">
-        <v>92</v>
+        <v>6</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -6855,14 +6855,14 @@
         <v>12</v>
       </c>
       <c r="B402" t="n">
-        <v>2019</v>
+        <v>1992</v>
       </c>
       <c r="C402" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -6871,14 +6871,14 @@
         <v>12</v>
       </c>
       <c r="B403" t="n">
-        <v>2020</v>
+        <v>1993</v>
       </c>
       <c r="C403" t="n">
-        <v>498</v>
+        <v>42</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -6887,14 +6887,14 @@
         <v>12</v>
       </c>
       <c r="B404" t="n">
-        <v>2021</v>
+        <v>1994</v>
       </c>
       <c r="C404" t="n">
-        <v>403</v>
+        <v>39</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -6903,14 +6903,14 @@
         <v>12</v>
       </c>
       <c r="B405" t="n">
-        <v>2022</v>
+        <v>1998</v>
       </c>
       <c r="C405" t="n">
-        <v>280</v>
+        <v>32</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -6919,14 +6919,14 @@
         <v>12</v>
       </c>
       <c r="B406" t="n">
-        <v>2023</v>
+        <v>1999</v>
       </c>
       <c r="C406" t="n">
-        <v>493</v>
+        <v>105</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -6935,154 +6935,154 @@
         <v>12</v>
       </c>
       <c r="B407" t="n">
-        <v>2024</v>
+        <v>2000</v>
       </c>
       <c r="C407" t="n">
-        <v>208</v>
+        <v>35</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B408" t="n">
-        <v>1971</v>
+        <v>2001</v>
       </c>
       <c r="C408" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B409" t="n">
-        <v>1976</v>
+        <v>2002</v>
       </c>
       <c r="C409" t="n">
-        <v>65</v>
+        <v>166</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B410" t="n">
-        <v>1978</v>
+        <v>2003</v>
       </c>
       <c r="C410" t="n">
-        <v>37</v>
+        <v>103</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B411" t="n">
-        <v>1986</v>
+        <v>2004</v>
       </c>
       <c r="C411" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B412" t="n">
-        <v>1987</v>
+        <v>2005</v>
       </c>
       <c r="C412" t="n">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B413" t="n">
-        <v>1991</v>
+        <v>2006</v>
       </c>
       <c r="C413" t="n">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B414" t="n">
-        <v>1992</v>
+        <v>2007</v>
       </c>
       <c r="C414" t="n">
-        <v>56</v>
+        <v>143</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B415" t="n">
-        <v>1993</v>
+        <v>2008</v>
       </c>
       <c r="C415" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B416" t="n">
-        <v>2001</v>
+        <v>2009</v>
       </c>
       <c r="C416" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -7092,109 +7092,109 @@
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B417" t="n">
-        <v>2003</v>
+        <v>2010</v>
       </c>
       <c r="C417" t="n">
-        <v>56</v>
+        <v>135</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B418" t="n">
-        <v>2004</v>
+        <v>2012</v>
       </c>
       <c r="C418" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B419" t="n">
-        <v>2005</v>
+        <v>2013</v>
       </c>
       <c r="C419" t="n">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B420" t="n">
-        <v>2007</v>
+        <v>2014</v>
       </c>
       <c r="C420" t="n">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B421" t="n">
-        <v>2008</v>
+        <v>2015</v>
       </c>
       <c r="C421" t="n">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B422" t="n">
-        <v>2009</v>
+        <v>2016</v>
       </c>
       <c r="C422" t="n">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B423" t="n">
-        <v>2010</v>
+        <v>2017</v>
       </c>
       <c r="C423" t="n">
-        <v>182</v>
+        <v>56</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -7204,13 +7204,13 @@
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B424" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="C424" t="n">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -7220,13 +7220,13 @@
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B425" t="n">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="C425" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -7236,97 +7236,97 @@
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B426" t="n">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="C426" t="n">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B427" t="n">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="C427" t="n">
-        <v>158</v>
+        <v>102</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B428" t="n">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="C428" t="n">
-        <v>67</v>
+        <v>172</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B429" t="n">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="C429" t="n">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B430" t="n">
-        <v>2017</v>
+        <v>2024</v>
       </c>
       <c r="C430" t="n">
-        <v>88</v>
+        <v>214</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B431" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="C431" t="n">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -7335,14 +7335,14 @@
         <v>13</v>
       </c>
       <c r="B432" t="n">
-        <v>2019</v>
+        <v>1971</v>
       </c>
       <c r="C432" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>1970s</t>
         </is>
       </c>
     </row>
@@ -7351,14 +7351,14 @@
         <v>13</v>
       </c>
       <c r="B433" t="n">
-        <v>2020</v>
+        <v>1986</v>
       </c>
       <c r="C433" t="n">
-        <v>154</v>
+        <v>47</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -7367,14 +7367,14 @@
         <v>13</v>
       </c>
       <c r="B434" t="n">
-        <v>2021</v>
+        <v>1991</v>
       </c>
       <c r="C434" t="n">
-        <v>233</v>
+        <v>10</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -7383,14 +7383,14 @@
         <v>13</v>
       </c>
       <c r="B435" t="n">
-        <v>2022</v>
+        <v>1992</v>
       </c>
       <c r="C435" t="n">
-        <v>174</v>
+        <v>63</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -7399,14 +7399,14 @@
         <v>13</v>
       </c>
       <c r="B436" t="n">
-        <v>2023</v>
+        <v>1993</v>
       </c>
       <c r="C436" t="n">
         <v>49</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -7415,334 +7415,334 @@
         <v>13</v>
       </c>
       <c r="B437" t="n">
-        <v>2024</v>
+        <v>1997</v>
       </c>
       <c r="C437" t="n">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B438" t="n">
-        <v>1980</v>
+        <v>1998</v>
       </c>
       <c r="C438" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B439" t="n">
-        <v>1982</v>
+        <v>2003</v>
       </c>
       <c r="C439" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B440" t="n">
-        <v>1986</v>
+        <v>2005</v>
       </c>
       <c r="C440" t="n">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B441" t="n">
-        <v>1987</v>
+        <v>2008</v>
       </c>
       <c r="C441" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B442" t="n">
-        <v>1991</v>
+        <v>2009</v>
       </c>
       <c r="C442" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B443" t="n">
-        <v>1992</v>
+        <v>2010</v>
       </c>
       <c r="C443" t="n">
-        <v>104</v>
+        <v>154</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B444" t="n">
-        <v>1993</v>
+        <v>2011</v>
       </c>
       <c r="C444" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B445" t="n">
-        <v>1994</v>
+        <v>2012</v>
       </c>
       <c r="C445" t="n">
-        <v>40</v>
+        <v>132</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B446" t="n">
-        <v>1995</v>
+        <v>2013</v>
       </c>
       <c r="C446" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B447" t="n">
-        <v>1996</v>
+        <v>2014</v>
       </c>
       <c r="C447" t="n">
-        <v>44</v>
+        <v>231</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B448" t="n">
-        <v>1999</v>
+        <v>2015</v>
       </c>
       <c r="C448" t="n">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B449" t="n">
-        <v>2000</v>
+        <v>2016</v>
       </c>
       <c r="C449" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B450" t="n">
-        <v>2001</v>
+        <v>2017</v>
       </c>
       <c r="C450" t="n">
-        <v>39</v>
+        <v>104</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B451" t="n">
-        <v>2002</v>
+        <v>2019</v>
       </c>
       <c r="C451" t="n">
-        <v>174</v>
+        <v>37</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B452" t="n">
-        <v>2003</v>
+        <v>2020</v>
       </c>
       <c r="C452" t="n">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B453" t="n">
-        <v>2004</v>
+        <v>2021</v>
       </c>
       <c r="C453" t="n">
-        <v>43</v>
+        <v>124</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B454" t="n">
-        <v>2005</v>
+        <v>2022</v>
       </c>
       <c r="C454" t="n">
-        <v>211</v>
+        <v>168</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B455" t="n">
-        <v>2006</v>
+        <v>2023</v>
       </c>
       <c r="C455" t="n">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B456" t="n">
-        <v>2007</v>
+        <v>2024</v>
       </c>
       <c r="C456" t="n">
-        <v>242</v>
+        <v>48</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B457" t="n">
-        <v>2008</v>
+        <v>2025</v>
       </c>
       <c r="C457" t="n">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -7751,14 +7751,14 @@
         <v>14</v>
       </c>
       <c r="B458" t="n">
-        <v>2009</v>
+        <v>1996</v>
       </c>
       <c r="C458" t="n">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>1990s</t>
         </is>
       </c>
     </row>
@@ -7767,14 +7767,14 @@
         <v>14</v>
       </c>
       <c r="B459" t="n">
-        <v>2010</v>
+        <v>2000</v>
       </c>
       <c r="C459" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -7783,14 +7783,14 @@
         <v>14</v>
       </c>
       <c r="B460" t="n">
-        <v>2011</v>
+        <v>2003</v>
       </c>
       <c r="C460" t="n">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -7799,14 +7799,14 @@
         <v>14</v>
       </c>
       <c r="B461" t="n">
-        <v>2012</v>
+        <v>2007</v>
       </c>
       <c r="C461" t="n">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -7815,10 +7815,10 @@
         <v>14</v>
       </c>
       <c r="B462" t="n">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="C462" t="n">
-        <v>64</v>
+        <v>153</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -7831,10 +7831,10 @@
         <v>14</v>
       </c>
       <c r="B463" t="n">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="C463" t="n">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -7847,10 +7847,10 @@
         <v>14</v>
       </c>
       <c r="B464" t="n">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="C464" t="n">
-        <v>139</v>
+        <v>51</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -7863,10 +7863,10 @@
         <v>14</v>
       </c>
       <c r="B465" t="n">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="C465" t="n">
-        <v>99</v>
+        <v>154</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -7879,10 +7879,10 @@
         <v>14</v>
       </c>
       <c r="B466" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="C466" t="n">
-        <v>29</v>
+        <v>264</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -7895,10 +7895,10 @@
         <v>14</v>
       </c>
       <c r="B467" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="C467" t="n">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -7911,10 +7911,10 @@
         <v>14</v>
       </c>
       <c r="B468" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C468" t="n">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -7927,14 +7927,14 @@
         <v>14</v>
       </c>
       <c r="B469" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C469" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -7943,14 +7943,14 @@
         <v>14</v>
       </c>
       <c r="B470" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C470" t="n">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -7959,14 +7959,14 @@
         <v>14</v>
       </c>
       <c r="B471" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C471" t="n">
-        <v>144</v>
+        <v>36</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
     </row>
@@ -7975,10 +7975,10 @@
         <v>14</v>
       </c>
       <c r="B472" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="C472" t="n">
-        <v>190</v>
+        <v>81</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -7991,10 +7991,10 @@
         <v>14</v>
       </c>
       <c r="B473" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="C473" t="n">
-        <v>227</v>
+        <v>97</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -8004,65 +8004,65 @@
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B474" t="n">
-        <v>1980</v>
+        <v>2022</v>
       </c>
       <c r="C474" t="n">
-        <v>146</v>
+        <v>222</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B475" t="n">
-        <v>1982</v>
+        <v>2023</v>
       </c>
       <c r="C475" t="n">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B476" t="n">
-        <v>1985</v>
+        <v>2024</v>
       </c>
       <c r="C476" t="n">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B477" t="n">
-        <v>1987</v>
+        <v>2025</v>
       </c>
       <c r="C477" t="n">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>1980s</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
@@ -8071,14 +8071,14 @@
         <v>15</v>
       </c>
       <c r="B478" t="n">
-        <v>1991</v>
+        <v>1982</v>
       </c>
       <c r="C478" t="n">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>1980s</t>
         </is>
       </c>
     </row>
@@ -8087,10 +8087,10 @@
         <v>15</v>
       </c>
       <c r="B479" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="C479" t="n">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>1994</v>
       </c>
       <c r="C480" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>1995</v>
       </c>
       <c r="C481" t="n">
-        <v>33</v>
+        <v>106</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>1996</v>
       </c>
       <c r="C482" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -8151,10 +8151,10 @@
         <v>15</v>
       </c>
       <c r="B483" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="C483" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -8167,10 +8167,10 @@
         <v>15</v>
       </c>
       <c r="B484" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="C484" t="n">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -8183,14 +8183,14 @@
         <v>15</v>
       </c>
       <c r="B485" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="C485" t="n">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>2000s</t>
         </is>
       </c>
     </row>
@@ -8199,10 +8199,10 @@
         <v>15</v>
       </c>
       <c r="B486" t="n">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="C486" t="n">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -8215,10 +8215,10 @@
         <v>15</v>
       </c>
       <c r="B487" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="C487" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -8231,10 +8231,10 @@
         <v>15</v>
       </c>
       <c r="B488" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="C488" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -8247,10 +8247,10 @@
         <v>15</v>
       </c>
       <c r="B489" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="C489" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -8263,10 +8263,10 @@
         <v>15</v>
       </c>
       <c r="B490" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="C490" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>2008</v>
       </c>
       <c r="C491" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>2009</v>
       </c>
       <c r="C492" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>2010</v>
       </c>
       <c r="C493" t="n">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>2011</v>
       </c>
       <c r="C494" t="n">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>2012</v>
       </c>
       <c r="C495" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -8359,10 +8359,10 @@
         <v>15</v>
       </c>
       <c r="B496" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="C496" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -8375,10 +8375,10 @@
         <v>15</v>
       </c>
       <c r="B497" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="C497" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -8391,10 +8391,10 @@
         <v>15</v>
       </c>
       <c r="B498" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C498" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -8407,10 +8407,10 @@
         <v>15</v>
       </c>
       <c r="B499" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C499" t="n">
-        <v>128</v>
+        <v>9</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -8423,10 +8423,10 @@
         <v>15</v>
       </c>
       <c r="B500" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C500" t="n">
-        <v>58</v>
+        <v>124</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>2019</v>
       </c>
       <c r="C501" t="n">
-        <v>118</v>
+        <v>14</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>2020</v>
       </c>
       <c r="C502" t="n">
-        <v>150</v>
+        <v>23</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         <v>2021</v>
       </c>
       <c r="C503" t="n">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         <v>2022</v>
       </c>
       <c r="C504" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>2023</v>
       </c>
       <c r="C505" t="n">
-        <v>130</v>
+        <v>43</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         <v>2024</v>
       </c>
       <c r="C506" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>

--- a/evolution/new_word_count_df.xlsx
+++ b/evolution/new_word_count_df.xlsx
@@ -434,10 +434,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="C2" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -448,10 +448,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="C3" t="n">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
@@ -462,13 +462,13 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="C4" t="n">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -476,10 +476,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="C5" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
         <v>6</v>
@@ -490,10 +490,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1985</v>
+        <v>1981</v>
       </c>
       <c r="C6" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
         <v>6</v>
@@ -504,10 +504,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="n">
-        <v>1988</v>
+        <v>1985</v>
       </c>
       <c r="C7" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
         <v>6</v>
@@ -518,10 +518,10 @@
         <v>4</v>
       </c>
       <c r="B8" t="n">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="C8" t="n">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
         <v>6</v>
@@ -532,13 +532,13 @@
         <v>4</v>
       </c>
       <c r="B9" t="n">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="C9" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -546,13 +546,13 @@
         <v>4</v>
       </c>
       <c r="B10" t="n">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="C10" t="n">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -560,10 +560,10 @@
         <v>4</v>
       </c>
       <c r="B11" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="C11" t="n">
-        <v>175</v>
+        <v>117</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
@@ -574,10 +574,10 @@
         <v>4</v>
       </c>
       <c r="B12" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="C12" t="n">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
@@ -588,10 +588,10 @@
         <v>4</v>
       </c>
       <c r="B13" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="C13" t="n">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
@@ -602,10 +602,10 @@
         <v>4</v>
       </c>
       <c r="B14" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="C14" t="n">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
@@ -616,10 +616,10 @@
         <v>4</v>
       </c>
       <c r="B15" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="C15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -630,10 +630,10 @@
         <v>4</v>
       </c>
       <c r="B16" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="C16" t="n">
-        <v>263</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -644,10 +644,10 @@
         <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="C17" t="n">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -658,10 +658,10 @@
         <v>4</v>
       </c>
       <c r="B18" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="C18" t="n">
-        <v>139</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -672,13 +672,13 @@
         <v>4</v>
       </c>
       <c r="B19" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="C19" t="n">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="D19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         <v>4</v>
       </c>
       <c r="B20" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C20" t="n">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="D20" t="s">
         <v>8</v>
@@ -700,10 +700,10 @@
         <v>4</v>
       </c>
       <c r="B21" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C21" t="n">
-        <v>198</v>
+        <v>158</v>
       </c>
       <c r="D21" t="s">
         <v>8</v>
@@ -714,10 +714,10 @@
         <v>4</v>
       </c>
       <c r="B22" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="C22" t="n">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="D22" t="s">
         <v>8</v>
@@ -728,10 +728,10 @@
         <v>4</v>
       </c>
       <c r="B23" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="C23" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="D23" t="s">
         <v>8</v>
@@ -742,10 +742,10 @@
         <v>4</v>
       </c>
       <c r="B24" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="C24" t="n">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="D24" t="s">
         <v>8</v>
@@ -756,10 +756,10 @@
         <v>4</v>
       </c>
       <c r="B25" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="C25" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="D25" t="s">
         <v>8</v>
@@ -770,10 +770,10 @@
         <v>4</v>
       </c>
       <c r="B26" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="C26" t="n">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="D26" t="s">
         <v>8</v>
@@ -784,10 +784,10 @@
         <v>4</v>
       </c>
       <c r="B27" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="C27" t="n">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="D27" t="s">
         <v>8</v>
@@ -798,10 +798,10 @@
         <v>4</v>
       </c>
       <c r="B28" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="C28" t="n">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="D28" t="s">
         <v>8</v>
@@ -812,13 +812,13 @@
         <v>4</v>
       </c>
       <c r="B29" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="C29" t="n">
-        <v>109</v>
+        <v>207</v>
       </c>
       <c r="D29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
@@ -826,10 +826,10 @@
         <v>4</v>
       </c>
       <c r="B30" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="C30" t="n">
-        <v>154</v>
+        <v>86</v>
       </c>
       <c r="D30" t="s">
         <v>9</v>
@@ -840,10 +840,10 @@
         <v>4</v>
       </c>
       <c r="B31" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="C31" t="n">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D31" t="s">
         <v>9</v>
@@ -854,10 +854,10 @@
         <v>4</v>
       </c>
       <c r="B32" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="C32" t="n">
-        <v>373</v>
+        <v>194</v>
       </c>
       <c r="D32" t="s">
         <v>9</v>
@@ -868,10 +868,10 @@
         <v>4</v>
       </c>
       <c r="B33" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="C33" t="n">
-        <v>251</v>
+        <v>385</v>
       </c>
       <c r="D33" t="s">
         <v>9</v>
@@ -882,10 +882,10 @@
         <v>4</v>
       </c>
       <c r="B34" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="C34" t="n">
-        <v>145</v>
+        <v>287</v>
       </c>
       <c r="D34" t="s">
         <v>9</v>
@@ -896,10 +896,10 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="C35" t="n">
-        <v>271</v>
+        <v>188</v>
       </c>
       <c r="D35" t="s">
         <v>9</v>
@@ -910,10 +910,10 @@
         <v>4</v>
       </c>
       <c r="B36" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="C36" t="n">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="D36" t="s">
         <v>9</v>
@@ -924,10 +924,10 @@
         <v>4</v>
       </c>
       <c r="B37" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C37" t="n">
-        <v>240</v>
+        <v>188</v>
       </c>
       <c r="D37" t="s">
         <v>9</v>
@@ -938,10 +938,10 @@
         <v>4</v>
       </c>
       <c r="B38" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C38" t="n">
-        <v>434</v>
+        <v>259</v>
       </c>
       <c r="D38" t="s">
         <v>9</v>
@@ -952,13 +952,13 @@
         <v>4</v>
       </c>
       <c r="B39" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C39" t="n">
-        <v>491</v>
+        <v>343</v>
       </c>
       <c r="D39" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
@@ -966,10 +966,10 @@
         <v>4</v>
       </c>
       <c r="B40" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C40" t="n">
-        <v>402</v>
+        <v>467</v>
       </c>
       <c r="D40" t="s">
         <v>10</v>
@@ -980,10 +980,10 @@
         <v>4</v>
       </c>
       <c r="B41" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C41" t="n">
-        <v>452</v>
+        <v>406</v>
       </c>
       <c r="D41" t="s">
         <v>10</v>
@@ -994,10 +994,10 @@
         <v>4</v>
       </c>
       <c r="B42" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C42" t="n">
-        <v>639</v>
+        <v>442</v>
       </c>
       <c r="D42" t="s">
         <v>10</v>
@@ -1008,10 +1008,10 @@
         <v>4</v>
       </c>
       <c r="B43" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C43" t="n">
-        <v>501</v>
+        <v>625</v>
       </c>
       <c r="D43" t="s">
         <v>10</v>
@@ -1022,10 +1022,10 @@
         <v>4</v>
       </c>
       <c r="B44" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C44" t="n">
-        <v>299</v>
+        <v>459</v>
       </c>
       <c r="D44" t="s">
         <v>10</v>
@@ -1033,16 +1033,16 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B45" t="n">
-        <v>1984</v>
+        <v>2025</v>
       </c>
       <c r="C45" t="n">
-        <v>15</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46">
@@ -1050,10 +1050,10 @@
         <v>11</v>
       </c>
       <c r="B46" t="n">
-        <v>1985</v>
+        <v>1980</v>
       </c>
       <c r="C46" t="n">
-        <v>51</v>
+        <v>121</v>
       </c>
       <c r="D46" t="s">
         <v>6</v>
@@ -1064,10 +1064,10 @@
         <v>11</v>
       </c>
       <c r="B47" t="n">
-        <v>1987</v>
+        <v>1982</v>
       </c>
       <c r="C47" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D47" t="s">
         <v>6</v>
@@ -1078,13 +1078,13 @@
         <v>11</v>
       </c>
       <c r="B48" t="n">
-        <v>1992</v>
+        <v>1986</v>
       </c>
       <c r="C48" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="D48" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
@@ -1092,13 +1092,13 @@
         <v>11</v>
       </c>
       <c r="B49" t="n">
-        <v>1993</v>
+        <v>1987</v>
       </c>
       <c r="C49" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D49" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
@@ -1106,13 +1106,13 @@
         <v>11</v>
       </c>
       <c r="B50" t="n">
-        <v>1994</v>
+        <v>1989</v>
       </c>
       <c r="C50" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D50" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
@@ -1120,10 +1120,10 @@
         <v>11</v>
       </c>
       <c r="B51" t="n">
-        <v>1995</v>
+        <v>1990</v>
       </c>
       <c r="C51" t="n">
-        <v>34</v>
+        <v>174</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -1134,10 +1134,10 @@
         <v>11</v>
       </c>
       <c r="B52" t="n">
-        <v>1998</v>
+        <v>1991</v>
       </c>
       <c r="C52" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -1148,10 +1148,10 @@
         <v>11</v>
       </c>
       <c r="B53" t="n">
-        <v>1999</v>
+        <v>1992</v>
       </c>
       <c r="C53" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -1162,13 +1162,13 @@
         <v>11</v>
       </c>
       <c r="B54" t="n">
-        <v>2000</v>
+        <v>1993</v>
       </c>
       <c r="C54" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D54" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55">
@@ -1176,13 +1176,13 @@
         <v>11</v>
       </c>
       <c r="B55" t="n">
-        <v>2001</v>
+        <v>1994</v>
       </c>
       <c r="C55" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="D55" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56">
@@ -1190,13 +1190,13 @@
         <v>11</v>
       </c>
       <c r="B56" t="n">
-        <v>2002</v>
+        <v>1995</v>
       </c>
       <c r="C56" t="n">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="D56" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
@@ -1204,13 +1204,13 @@
         <v>11</v>
       </c>
       <c r="B57" t="n">
-        <v>2005</v>
+        <v>1998</v>
       </c>
       <c r="C57" t="n">
-        <v>45</v>
+        <v>265</v>
       </c>
       <c r="D57" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58">
@@ -1218,13 +1218,13 @@
         <v>11</v>
       </c>
       <c r="B58" t="n">
-        <v>2006</v>
+        <v>1999</v>
       </c>
       <c r="C58" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D58" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
@@ -1232,10 +1232,10 @@
         <v>11</v>
       </c>
       <c r="B59" t="n">
-        <v>2007</v>
+        <v>2000</v>
       </c>
       <c r="C59" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D59" t="s">
         <v>8</v>
@@ -1246,10 +1246,10 @@
         <v>11</v>
       </c>
       <c r="B60" t="n">
-        <v>2009</v>
+        <v>2001</v>
       </c>
       <c r="C60" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="D60" t="s">
         <v>8</v>
@@ -1260,13 +1260,13 @@
         <v>11</v>
       </c>
       <c r="B61" t="n">
-        <v>2010</v>
+        <v>2002</v>
       </c>
       <c r="C61" t="n">
-        <v>42</v>
+        <v>175</v>
       </c>
       <c r="D61" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62">
@@ -1274,13 +1274,13 @@
         <v>11</v>
       </c>
       <c r="B62" t="n">
-        <v>2011</v>
+        <v>2003</v>
       </c>
       <c r="C62" t="n">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="D62" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63">
@@ -1288,13 +1288,13 @@
         <v>11</v>
       </c>
       <c r="B63" t="n">
-        <v>2012</v>
+        <v>2004</v>
       </c>
       <c r="C63" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D63" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64">
@@ -1302,13 +1302,13 @@
         <v>11</v>
       </c>
       <c r="B64" t="n">
-        <v>2013</v>
+        <v>2005</v>
       </c>
       <c r="C64" t="n">
-        <v>52</v>
+        <v>165</v>
       </c>
       <c r="D64" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
@@ -1316,13 +1316,13 @@
         <v>11</v>
       </c>
       <c r="B65" t="n">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="C65" t="n">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="D65" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66">
@@ -1330,13 +1330,13 @@
         <v>11</v>
       </c>
       <c r="B66" t="n">
-        <v>2015</v>
+        <v>2007</v>
       </c>
       <c r="C66" t="n">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="D66" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67">
@@ -1344,13 +1344,13 @@
         <v>11</v>
       </c>
       <c r="B67" t="n">
-        <v>2016</v>
+        <v>2009</v>
       </c>
       <c r="C67" t="n">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="D67" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68">
@@ -1358,10 +1358,10 @@
         <v>11</v>
       </c>
       <c r="B68" t="n">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="C68" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D68" t="s">
         <v>9</v>
@@ -1372,10 +1372,10 @@
         <v>11</v>
       </c>
       <c r="B69" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="C69" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D69" t="s">
         <v>9</v>
@@ -1386,10 +1386,10 @@
         <v>11</v>
       </c>
       <c r="B70" t="n">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="C70" t="n">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="D70" t="s">
         <v>9</v>
@@ -1400,13 +1400,13 @@
         <v>11</v>
       </c>
       <c r="B71" t="n">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="C71" t="n">
-        <v>232</v>
+        <v>36</v>
       </c>
       <c r="D71" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72">
@@ -1414,13 +1414,13 @@
         <v>11</v>
       </c>
       <c r="B72" t="n">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="C72" t="n">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="D72" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73">
@@ -1428,13 +1428,13 @@
         <v>11</v>
       </c>
       <c r="B73" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C73" t="n">
-        <v>218</v>
+        <v>145</v>
       </c>
       <c r="D73" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74">
@@ -1442,13 +1442,13 @@
         <v>11</v>
       </c>
       <c r="B74" t="n">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="C74" t="n">
-        <v>100</v>
+        <v>178</v>
       </c>
       <c r="D74" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75">
@@ -1456,13 +1456,13 @@
         <v>11</v>
       </c>
       <c r="B75" t="n">
-        <v>2024</v>
+        <v>2018</v>
       </c>
       <c r="C75" t="n">
-        <v>364</v>
+        <v>94</v>
       </c>
       <c r="D75" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76">
@@ -1470,97 +1470,97 @@
         <v>11</v>
       </c>
       <c r="B76" t="n">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="C76" t="n">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="D76" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B77" t="n">
-        <v>1991</v>
+        <v>2020</v>
       </c>
       <c r="C77" t="n">
-        <v>8</v>
+        <v>137</v>
       </c>
       <c r="D77" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B78" t="n">
-        <v>1993</v>
+        <v>2021</v>
       </c>
       <c r="C78" t="n">
-        <v>71</v>
+        <v>164</v>
       </c>
       <c r="D78" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B79" t="n">
-        <v>2003</v>
+        <v>2022</v>
       </c>
       <c r="C79" t="n">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="D79" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B80" t="n">
-        <v>2005</v>
+        <v>2023</v>
       </c>
       <c r="C80" t="n">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="D80" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B81" t="n">
-        <v>2006</v>
+        <v>2024</v>
       </c>
       <c r="C81" t="n">
-        <v>37</v>
+        <v>228</v>
       </c>
       <c r="D81" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B82" t="n">
-        <v>2010</v>
+        <v>2025</v>
       </c>
       <c r="C82" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="D82" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">
@@ -1568,13 +1568,13 @@
         <v>12</v>
       </c>
       <c r="B83" t="n">
-        <v>2011</v>
+        <v>1985</v>
       </c>
       <c r="C83" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D83" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
@@ -1582,13 +1582,13 @@
         <v>12</v>
       </c>
       <c r="B84" t="n">
-        <v>2013</v>
+        <v>1992</v>
       </c>
       <c r="C84" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D84" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85">
@@ -1596,13 +1596,13 @@
         <v>12</v>
       </c>
       <c r="B85" t="n">
-        <v>2014</v>
+        <v>1994</v>
       </c>
       <c r="C85" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D85" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86">
@@ -1610,13 +1610,13 @@
         <v>12</v>
       </c>
       <c r="B86" t="n">
-        <v>2015</v>
+        <v>1995</v>
       </c>
       <c r="C86" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D86" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87">
@@ -1624,13 +1624,13 @@
         <v>12</v>
       </c>
       <c r="B87" t="n">
-        <v>2016</v>
+        <v>2001</v>
       </c>
       <c r="C87" t="n">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="D87" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88">
@@ -1638,13 +1638,13 @@
         <v>12</v>
       </c>
       <c r="B88" t="n">
-        <v>2017</v>
+        <v>2002</v>
       </c>
       <c r="C88" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D88" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89">
@@ -1652,13 +1652,13 @@
         <v>12</v>
       </c>
       <c r="B89" t="n">
-        <v>2018</v>
+        <v>2005</v>
       </c>
       <c r="C89" t="n">
-        <v>102</v>
+        <v>45</v>
       </c>
       <c r="D89" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90">
@@ -1666,13 +1666,13 @@
         <v>12</v>
       </c>
       <c r="B90" t="n">
-        <v>2019</v>
+        <v>2006</v>
       </c>
       <c r="C90" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D90" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91">
@@ -1680,13 +1680,13 @@
         <v>12</v>
       </c>
       <c r="B91" t="n">
-        <v>2020</v>
+        <v>2007</v>
       </c>
       <c r="C91" t="n">
-        <v>572</v>
+        <v>47</v>
       </c>
       <c r="D91" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92">
@@ -1694,13 +1694,13 @@
         <v>12</v>
       </c>
       <c r="B92" t="n">
-        <v>2021</v>
+        <v>2009</v>
       </c>
       <c r="C92" t="n">
-        <v>337</v>
+        <v>62</v>
       </c>
       <c r="D92" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93">
@@ -1708,13 +1708,13 @@
         <v>12</v>
       </c>
       <c r="B93" t="n">
-        <v>2022</v>
+        <v>2010</v>
       </c>
       <c r="C93" t="n">
-        <v>263</v>
+        <v>28</v>
       </c>
       <c r="D93" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="94">
@@ -1722,13 +1722,13 @@
         <v>12</v>
       </c>
       <c r="B94" t="n">
-        <v>2023</v>
+        <v>2012</v>
       </c>
       <c r="C94" t="n">
-        <v>484</v>
+        <v>34</v>
       </c>
       <c r="D94" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95">
@@ -1736,13 +1736,13 @@
         <v>12</v>
       </c>
       <c r="B95" t="n">
-        <v>2024</v>
+        <v>2013</v>
       </c>
       <c r="C95" t="n">
-        <v>163</v>
+        <v>73</v>
       </c>
       <c r="D95" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="96">
@@ -1750,167 +1750,167 @@
         <v>12</v>
       </c>
       <c r="B96" t="n">
-        <v>2025</v>
+        <v>2014</v>
       </c>
       <c r="C96" t="n">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="D96" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B97" t="n">
-        <v>1980</v>
+        <v>2015</v>
       </c>
       <c r="C97" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D97" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B98" t="n">
-        <v>1986</v>
+        <v>2016</v>
       </c>
       <c r="C98" t="n">
-        <v>74</v>
+        <v>153</v>
       </c>
       <c r="D98" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B99" t="n">
-        <v>1987</v>
+        <v>2017</v>
       </c>
       <c r="C99" t="n">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="D99" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B100" t="n">
-        <v>1990</v>
+        <v>2018</v>
       </c>
       <c r="C100" t="n">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="D100" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B101" t="n">
-        <v>1991</v>
+        <v>2019</v>
       </c>
       <c r="C101" t="n">
-        <v>6</v>
+        <v>154</v>
       </c>
       <c r="D101" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B102" t="n">
-        <v>1992</v>
+        <v>2020</v>
       </c>
       <c r="C102" t="n">
-        <v>50</v>
+        <v>203</v>
       </c>
       <c r="D102" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B103" t="n">
-        <v>1993</v>
+        <v>2021</v>
       </c>
       <c r="C103" t="n">
-        <v>42</v>
+        <v>104</v>
       </c>
       <c r="D103" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B104" t="n">
-        <v>1994</v>
+        <v>2022</v>
       </c>
       <c r="C104" t="n">
-        <v>39</v>
+        <v>160</v>
       </c>
       <c r="D104" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B105" t="n">
-        <v>1998</v>
+        <v>2023</v>
       </c>
       <c r="C105" t="n">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="D105" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B106" t="n">
-        <v>1999</v>
+        <v>2024</v>
       </c>
       <c r="C106" t="n">
-        <v>105</v>
+        <v>324</v>
       </c>
       <c r="D106" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B107" t="n">
-        <v>2000</v>
+        <v>2025</v>
       </c>
       <c r="C107" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D107" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="108">
@@ -1918,13 +1918,13 @@
         <v>13</v>
       </c>
       <c r="B108" t="n">
-        <v>2001</v>
+        <v>1978</v>
       </c>
       <c r="C108" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="D108" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109">
@@ -1932,13 +1932,13 @@
         <v>13</v>
       </c>
       <c r="B109" t="n">
-        <v>2002</v>
+        <v>1979</v>
       </c>
       <c r="C109" t="n">
-        <v>166</v>
+        <v>66</v>
       </c>
       <c r="D109" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110">
@@ -1946,13 +1946,13 @@
         <v>13</v>
       </c>
       <c r="B110" t="n">
-        <v>2003</v>
+        <v>1984</v>
       </c>
       <c r="C110" t="n">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="D110" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111">
@@ -1960,13 +1960,13 @@
         <v>13</v>
       </c>
       <c r="B111" t="n">
-        <v>2004</v>
+        <v>1986</v>
       </c>
       <c r="C111" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D111" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112">
@@ -1974,13 +1974,13 @@
         <v>13</v>
       </c>
       <c r="B112" t="n">
-        <v>2005</v>
+        <v>1987</v>
       </c>
       <c r="C112" t="n">
-        <v>121</v>
+        <v>47</v>
       </c>
       <c r="D112" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113">
@@ -1988,13 +1988,13 @@
         <v>13</v>
       </c>
       <c r="B113" t="n">
-        <v>2006</v>
+        <v>1988</v>
       </c>
       <c r="C113" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D113" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114">
@@ -2002,13 +2002,13 @@
         <v>13</v>
       </c>
       <c r="B114" t="n">
-        <v>2007</v>
+        <v>1991</v>
       </c>
       <c r="C114" t="n">
-        <v>143</v>
+        <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115">
@@ -2016,13 +2016,13 @@
         <v>13</v>
       </c>
       <c r="B115" t="n">
-        <v>2008</v>
+        <v>1992</v>
       </c>
       <c r="C115" t="n">
-        <v>32</v>
+        <v>104</v>
       </c>
       <c r="D115" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116">
@@ -2030,13 +2030,13 @@
         <v>13</v>
       </c>
       <c r="B116" t="n">
-        <v>2009</v>
+        <v>1994</v>
       </c>
       <c r="C116" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="D116" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117">
@@ -2044,13 +2044,13 @@
         <v>13</v>
       </c>
       <c r="B117" t="n">
-        <v>2010</v>
+        <v>1995</v>
       </c>
       <c r="C117" t="n">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="D117" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118">
@@ -2058,13 +2058,13 @@
         <v>13</v>
       </c>
       <c r="B118" t="n">
-        <v>2012</v>
+        <v>1996</v>
       </c>
       <c r="C118" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D118" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119">
@@ -2072,13 +2072,13 @@
         <v>13</v>
       </c>
       <c r="B119" t="n">
-        <v>2013</v>
+        <v>1997</v>
       </c>
       <c r="C119" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="D119" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120">
@@ -2086,13 +2086,13 @@
         <v>13</v>
       </c>
       <c r="B120" t="n">
-        <v>2014</v>
+        <v>2001</v>
       </c>
       <c r="C120" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D120" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="121">
@@ -2100,13 +2100,13 @@
         <v>13</v>
       </c>
       <c r="B121" t="n">
-        <v>2015</v>
+        <v>2002</v>
       </c>
       <c r="C121" t="n">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="D121" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="122">
@@ -2114,13 +2114,13 @@
         <v>13</v>
       </c>
       <c r="B122" t="n">
-        <v>2016</v>
+        <v>2003</v>
       </c>
       <c r="C122" t="n">
-        <v>99</v>
+        <v>48</v>
       </c>
       <c r="D122" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="123">
@@ -2128,13 +2128,13 @@
         <v>13</v>
       </c>
       <c r="B123" t="n">
-        <v>2017</v>
+        <v>2004</v>
       </c>
       <c r="C123" t="n">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="D123" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="124">
@@ -2142,13 +2142,13 @@
         <v>13</v>
       </c>
       <c r="B124" t="n">
-        <v>2018</v>
+        <v>2005</v>
       </c>
       <c r="C124" t="n">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="D124" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="125">
@@ -2156,13 +2156,13 @@
         <v>13</v>
       </c>
       <c r="B125" t="n">
-        <v>2019</v>
+        <v>2006</v>
       </c>
       <c r="C125" t="n">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="D125" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="126">
@@ -2170,13 +2170,13 @@
         <v>13</v>
       </c>
       <c r="B126" t="n">
-        <v>2020</v>
+        <v>2007</v>
       </c>
       <c r="C126" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D126" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="127">
@@ -2184,13 +2184,13 @@
         <v>13</v>
       </c>
       <c r="B127" t="n">
-        <v>2021</v>
+        <v>2008</v>
       </c>
       <c r="C127" t="n">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D127" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="128">
@@ -2198,13 +2198,13 @@
         <v>13</v>
       </c>
       <c r="B128" t="n">
-        <v>2022</v>
+        <v>2009</v>
       </c>
       <c r="C128" t="n">
-        <v>172</v>
+        <v>61</v>
       </c>
       <c r="D128" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="129">
@@ -2212,13 +2212,13 @@
         <v>13</v>
       </c>
       <c r="B129" t="n">
-        <v>2023</v>
+        <v>2010</v>
       </c>
       <c r="C129" t="n">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="D129" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="130">
@@ -2226,13 +2226,13 @@
         <v>13</v>
       </c>
       <c r="B130" t="n">
-        <v>2024</v>
+        <v>2011</v>
       </c>
       <c r="C130" t="n">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="D130" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="131">
@@ -2240,195 +2240,195 @@
         <v>13</v>
       </c>
       <c r="B131" t="n">
-        <v>2025</v>
+        <v>2012</v>
       </c>
       <c r="C131" t="n">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="D131" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B132" t="n">
-        <v>1971</v>
+        <v>2013</v>
       </c>
       <c r="C132" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D132" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B133" t="n">
-        <v>1986</v>
+        <v>2014</v>
       </c>
       <c r="C133" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D133" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B134" t="n">
-        <v>1991</v>
+        <v>2015</v>
       </c>
       <c r="C134" t="n">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="D134" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B135" t="n">
-        <v>1992</v>
+        <v>2016</v>
       </c>
       <c r="C135" t="n">
         <v>63</v>
       </c>
       <c r="D135" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B136" t="n">
-        <v>1993</v>
+        <v>2017</v>
       </c>
       <c r="C136" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="D136" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B137" t="n">
-        <v>1997</v>
+        <v>2018</v>
       </c>
       <c r="C137" t="n">
-        <v>34</v>
+        <v>223</v>
       </c>
       <c r="D137" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B138" t="n">
-        <v>1998</v>
+        <v>2019</v>
       </c>
       <c r="C138" t="n">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="D138" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B139" t="n">
-        <v>2003</v>
+        <v>2020</v>
       </c>
       <c r="C139" t="n">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="D139" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B140" t="n">
-        <v>2005</v>
+        <v>2021</v>
       </c>
       <c r="C140" t="n">
-        <v>33</v>
+        <v>115</v>
       </c>
       <c r="D140" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B141" t="n">
-        <v>2008</v>
+        <v>2022</v>
       </c>
       <c r="C141" t="n">
-        <v>33</v>
+        <v>171</v>
       </c>
       <c r="D141" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B142" t="n">
-        <v>2009</v>
+        <v>2023</v>
       </c>
       <c r="C142" t="n">
-        <v>41</v>
+        <v>117</v>
       </c>
       <c r="D142" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B143" t="n">
-        <v>2010</v>
+        <v>2024</v>
       </c>
       <c r="C143" t="n">
-        <v>154</v>
+        <v>210</v>
       </c>
       <c r="D143" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B144" t="n">
-        <v>2011</v>
+        <v>2025</v>
       </c>
       <c r="C144" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D144" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="145">
@@ -2436,13 +2436,13 @@
         <v>14</v>
       </c>
       <c r="B145" t="n">
-        <v>2012</v>
+        <v>1971</v>
       </c>
       <c r="C145" t="n">
-        <v>132</v>
+        <v>5</v>
       </c>
       <c r="D145" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146">
@@ -2450,13 +2450,13 @@
         <v>14</v>
       </c>
       <c r="B146" t="n">
-        <v>2013</v>
+        <v>1986</v>
       </c>
       <c r="C146" t="n">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="D146" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="147">
@@ -2464,13 +2464,13 @@
         <v>14</v>
       </c>
       <c r="B147" t="n">
-        <v>2014</v>
+        <v>1991</v>
       </c>
       <c r="C147" t="n">
-        <v>231</v>
+        <v>10</v>
       </c>
       <c r="D147" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148">
@@ -2478,13 +2478,13 @@
         <v>14</v>
       </c>
       <c r="B148" t="n">
-        <v>2015</v>
+        <v>1992</v>
       </c>
       <c r="C148" t="n">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="D148" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149">
@@ -2492,13 +2492,13 @@
         <v>14</v>
       </c>
       <c r="B149" t="n">
-        <v>2016</v>
+        <v>1993</v>
       </c>
       <c r="C149" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D149" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150">
@@ -2506,13 +2506,13 @@
         <v>14</v>
       </c>
       <c r="B150" t="n">
-        <v>2017</v>
+        <v>1997</v>
       </c>
       <c r="C150" t="n">
-        <v>104</v>
+        <v>34</v>
       </c>
       <c r="D150" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="151">
@@ -2520,13 +2520,13 @@
         <v>14</v>
       </c>
       <c r="B151" t="n">
-        <v>2019</v>
+        <v>1998</v>
       </c>
       <c r="C151" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="D151" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="152">
@@ -2534,13 +2534,13 @@
         <v>14</v>
       </c>
       <c r="B152" t="n">
-        <v>2020</v>
+        <v>2003</v>
       </c>
       <c r="C152" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D152" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="153">
@@ -2548,13 +2548,13 @@
         <v>14</v>
       </c>
       <c r="B153" t="n">
-        <v>2021</v>
+        <v>2005</v>
       </c>
       <c r="C153" t="n">
-        <v>124</v>
+        <v>33</v>
       </c>
       <c r="D153" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="154">
@@ -2562,13 +2562,13 @@
         <v>14</v>
       </c>
       <c r="B154" t="n">
-        <v>2022</v>
+        <v>2008</v>
       </c>
       <c r="C154" t="n">
-        <v>168</v>
+        <v>33</v>
       </c>
       <c r="D154" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="155">
@@ -2576,13 +2576,13 @@
         <v>14</v>
       </c>
       <c r="B155" t="n">
-        <v>2023</v>
+        <v>2010</v>
       </c>
       <c r="C155" t="n">
-        <v>83</v>
+        <v>159</v>
       </c>
       <c r="D155" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="156">
@@ -2590,13 +2590,13 @@
         <v>14</v>
       </c>
       <c r="B156" t="n">
-        <v>2024</v>
+        <v>2011</v>
       </c>
       <c r="C156" t="n">
         <v>48</v>
       </c>
       <c r="D156" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="157">
@@ -2604,80 +2604,80 @@
         <v>14</v>
       </c>
       <c r="B157" t="n">
-        <v>2025</v>
+        <v>2012</v>
       </c>
       <c r="C157" t="n">
-        <v>46</v>
+        <v>137</v>
       </c>
       <c r="D157" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B158" t="n">
-        <v>1996</v>
+        <v>2013</v>
       </c>
       <c r="C158" t="n">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="D158" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B159" t="n">
-        <v>2000</v>
+        <v>2014</v>
       </c>
       <c r="C159" t="n">
-        <v>59</v>
+        <v>248</v>
       </c>
       <c r="D159" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B160" t="n">
-        <v>2003</v>
+        <v>2015</v>
       </c>
       <c r="C160" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D160" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B161" t="n">
-        <v>2007</v>
+        <v>2016</v>
       </c>
       <c r="C161" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D161" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B162" t="n">
-        <v>2010</v>
+        <v>2017</v>
       </c>
       <c r="C162" t="n">
-        <v>153</v>
+        <v>69</v>
       </c>
       <c r="D162" t="s">
         <v>9</v>
@@ -2685,13 +2685,13 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B163" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="C163" t="n">
-        <v>105</v>
+        <v>24</v>
       </c>
       <c r="D163" t="s">
         <v>9</v>
@@ -2699,13 +2699,13 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B164" t="n">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="C164" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="D164" t="s">
         <v>9</v>
@@ -2713,86 +2713,86 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B165" t="n">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="C165" t="n">
-        <v>154</v>
+        <v>64</v>
       </c>
       <c r="D165" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B166" t="n">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="C166" t="n">
-        <v>264</v>
+        <v>115</v>
       </c>
       <c r="D166" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B167" t="n">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="C167" t="n">
-        <v>129</v>
+        <v>231</v>
       </c>
       <c r="D167" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B168" t="n">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="C168" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="D168" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B169" t="n">
-        <v>2017</v>
+        <v>2024</v>
       </c>
       <c r="C169" t="n">
-        <v>14</v>
+        <v>89</v>
       </c>
       <c r="D169" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B170" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="C170" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D170" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="171">
@@ -2800,13 +2800,13 @@
         <v>15</v>
       </c>
       <c r="B171" t="n">
-        <v>2019</v>
+        <v>1976</v>
       </c>
       <c r="C171" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="D171" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172">
@@ -2814,13 +2814,13 @@
         <v>15</v>
       </c>
       <c r="B172" t="n">
-        <v>2020</v>
+        <v>1991</v>
       </c>
       <c r="C172" t="n">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="D172" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="173">
@@ -2828,13 +2828,13 @@
         <v>15</v>
       </c>
       <c r="B173" t="n">
-        <v>2021</v>
+        <v>1993</v>
       </c>
       <c r="C173" t="n">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="D173" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="174">
@@ -2842,13 +2842,13 @@
         <v>15</v>
       </c>
       <c r="B174" t="n">
-        <v>2022</v>
+        <v>1994</v>
       </c>
       <c r="C174" t="n">
-        <v>222</v>
+        <v>58</v>
       </c>
       <c r="D174" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="175">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B175" t="n">
-        <v>2023</v>
+        <v>1995</v>
       </c>
       <c r="C175" t="n">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="D175" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="176">
@@ -2870,13 +2870,13 @@
         <v>15</v>
       </c>
       <c r="B176" t="n">
-        <v>2024</v>
+        <v>1996</v>
       </c>
       <c r="C176" t="n">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="D176" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="177">
@@ -2884,38 +2884,38 @@
         <v>15</v>
       </c>
       <c r="B177" t="n">
-        <v>2025</v>
+        <v>1997</v>
       </c>
       <c r="C177" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="D177" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B178" t="n">
-        <v>1982</v>
+        <v>1998</v>
       </c>
       <c r="C178" t="n">
-        <v>7</v>
+        <v>112</v>
       </c>
       <c r="D178" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B179" t="n">
-        <v>1991</v>
+        <v>1999</v>
       </c>
       <c r="C179" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D179" t="s">
         <v>7</v>
@@ -2923,83 +2923,83 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B180" t="n">
-        <v>1994</v>
+        <v>2000</v>
       </c>
       <c r="C180" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="D180" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B181" t="n">
-        <v>1995</v>
+        <v>2002</v>
       </c>
       <c r="C181" t="n">
-        <v>106</v>
+        <v>22</v>
       </c>
       <c r="D181" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B182" t="n">
-        <v>1996</v>
+        <v>2005</v>
       </c>
       <c r="C182" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="D182" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B183" t="n">
-        <v>1998</v>
+        <v>2006</v>
       </c>
       <c r="C183" t="n">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="D183" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B184" t="n">
-        <v>1999</v>
+        <v>2007</v>
       </c>
       <c r="C184" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D184" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B185" t="n">
-        <v>2000</v>
+        <v>2009</v>
       </c>
       <c r="C185" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D185" t="s">
         <v>8</v>
@@ -3007,111 +3007,111 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B186" t="n">
-        <v>2002</v>
+        <v>2010</v>
       </c>
       <c r="C186" t="n">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="D186" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B187" t="n">
-        <v>2003</v>
+        <v>2011</v>
       </c>
       <c r="C187" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D187" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B188" t="n">
-        <v>2005</v>
+        <v>2012</v>
       </c>
       <c r="C188" t="n">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="D188" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B189" t="n">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="C189" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="D189" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B190" t="n">
-        <v>2007</v>
+        <v>2015</v>
       </c>
       <c r="C190" t="n">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="D190" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B191" t="n">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="C191" t="n">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="D191" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B192" t="n">
-        <v>2009</v>
+        <v>2017</v>
       </c>
       <c r="C192" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="D192" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B193" t="n">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="C193" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D193" t="s">
         <v>9</v>
@@ -3119,13 +3119,13 @@
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B194" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="C194" t="n">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="D194" t="s">
         <v>9</v>
@@ -3133,86 +3133,86 @@
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B195" t="n">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C195" t="n">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="D195" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B196" t="n">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="C196" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D196" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B197" t="n">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="C197" t="n">
-        <v>74</v>
+        <v>145</v>
       </c>
       <c r="D197" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B198" t="n">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="C198" t="n">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="D198" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B199" t="n">
-        <v>2017</v>
+        <v>2024</v>
       </c>
       <c r="C199" t="n">
-        <v>9</v>
+        <v>155</v>
       </c>
       <c r="D199" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B200" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="C200" t="n">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="D200" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="201">
@@ -3220,13 +3220,13 @@
         <v>16</v>
       </c>
       <c r="B201" t="n">
-        <v>2019</v>
+        <v>1993</v>
       </c>
       <c r="C201" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D201" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="202">
@@ -3234,13 +3234,13 @@
         <v>16</v>
       </c>
       <c r="B202" t="n">
-        <v>2020</v>
+        <v>1996</v>
       </c>
       <c r="C202" t="n">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="D202" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="203">
@@ -3248,13 +3248,13 @@
         <v>16</v>
       </c>
       <c r="B203" t="n">
-        <v>2021</v>
+        <v>2003</v>
       </c>
       <c r="C203" t="n">
-        <v>41</v>
+        <v>171</v>
       </c>
       <c r="D203" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="204">
@@ -3262,13 +3262,13 @@
         <v>16</v>
       </c>
       <c r="B204" t="n">
-        <v>2022</v>
+        <v>2004</v>
       </c>
       <c r="C204" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="D204" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="205">
@@ -3276,13 +3276,13 @@
         <v>16</v>
       </c>
       <c r="B205" t="n">
-        <v>2023</v>
+        <v>2007</v>
       </c>
       <c r="C205" t="n">
-        <v>43</v>
+        <v>124</v>
       </c>
       <c r="D205" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="206">
@@ -3290,237 +3290,237 @@
         <v>16</v>
       </c>
       <c r="B206" t="n">
-        <v>2024</v>
+        <v>2009</v>
       </c>
       <c r="C206" t="n">
-        <v>110</v>
+        <v>47</v>
       </c>
       <c r="D206" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B207" t="n">
-        <v>1972</v>
+        <v>2010</v>
       </c>
       <c r="C207" t="n">
-        <v>7</v>
+        <v>142</v>
       </c>
       <c r="D207" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B208" t="n">
-        <v>1973</v>
+        <v>2011</v>
       </c>
       <c r="C208" t="n">
-        <v>6</v>
+        <v>117</v>
       </c>
       <c r="D208" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B209" t="n">
-        <v>1974</v>
+        <v>2012</v>
       </c>
       <c r="C209" t="n">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="D209" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B210" t="n">
-        <v>1976</v>
+        <v>2013</v>
       </c>
       <c r="C210" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D210" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B211" t="n">
-        <v>1977</v>
+        <v>2014</v>
       </c>
       <c r="C211" t="n">
-        <v>138</v>
+        <v>271</v>
       </c>
       <c r="D211" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B212" t="n">
-        <v>1978</v>
+        <v>2015</v>
       </c>
       <c r="C212" t="n">
-        <v>35</v>
+        <v>115</v>
       </c>
       <c r="D212" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B213" t="n">
-        <v>1979</v>
+        <v>2016</v>
       </c>
       <c r="C213" t="n">
-        <v>238</v>
+        <v>106</v>
       </c>
       <c r="D213" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B214" t="n">
-        <v>1980</v>
+        <v>2017</v>
       </c>
       <c r="C214" t="n">
-        <v>152</v>
+        <v>43</v>
       </c>
       <c r="D214" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B215" t="n">
-        <v>1981</v>
+        <v>2018</v>
       </c>
       <c r="C215" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D215" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B216" t="n">
-        <v>1982</v>
+        <v>2019</v>
       </c>
       <c r="C216" t="n">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="D216" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B217" t="n">
-        <v>1983</v>
+        <v>2020</v>
       </c>
       <c r="C217" t="n">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D217" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B218" t="n">
-        <v>1984</v>
+        <v>2021</v>
       </c>
       <c r="C218" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="D218" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B219" t="n">
-        <v>1986</v>
+        <v>2022</v>
       </c>
       <c r="C219" t="n">
-        <v>17</v>
+        <v>193</v>
       </c>
       <c r="D219" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B220" t="n">
-        <v>1987</v>
+        <v>2023</v>
       </c>
       <c r="C220" t="n">
-        <v>25</v>
+        <v>142</v>
       </c>
       <c r="D220" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B221" t="n">
-        <v>1992</v>
+        <v>2024</v>
       </c>
       <c r="C221" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D221" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B222" t="n">
-        <v>1993</v>
+        <v>2025</v>
       </c>
       <c r="C222" t="n">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="D222" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="223">
@@ -3528,13 +3528,13 @@
         <v>17</v>
       </c>
       <c r="B223" t="n">
-        <v>1994</v>
+        <v>1977</v>
       </c>
       <c r="C223" t="n">
-        <v>179</v>
+        <v>49</v>
       </c>
       <c r="D223" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="224">
@@ -3542,13 +3542,13 @@
         <v>17</v>
       </c>
       <c r="B224" t="n">
-        <v>1995</v>
+        <v>1980</v>
       </c>
       <c r="C224" t="n">
-        <v>121</v>
+        <v>34</v>
       </c>
       <c r="D224" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="225">
@@ -3556,13 +3556,13 @@
         <v>17</v>
       </c>
       <c r="B225" t="n">
-        <v>1996</v>
+        <v>1982</v>
       </c>
       <c r="C225" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="D225" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="226">
@@ -3570,13 +3570,13 @@
         <v>17</v>
       </c>
       <c r="B226" t="n">
-        <v>1997</v>
+        <v>1987</v>
       </c>
       <c r="C226" t="n">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="D226" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="227">
@@ -3584,13 +3584,13 @@
         <v>17</v>
       </c>
       <c r="B227" t="n">
-        <v>1998</v>
+        <v>1988</v>
       </c>
       <c r="C227" t="n">
-        <v>186</v>
+        <v>3</v>
       </c>
       <c r="D227" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="228">
@@ -3598,13 +3598,13 @@
         <v>17</v>
       </c>
       <c r="B228" t="n">
-        <v>1999</v>
+        <v>1989</v>
       </c>
       <c r="C228" t="n">
-        <v>160</v>
+        <v>2</v>
       </c>
       <c r="D228" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="229">
@@ -3612,13 +3612,13 @@
         <v>17</v>
       </c>
       <c r="B229" t="n">
-        <v>2000</v>
+        <v>1991</v>
       </c>
       <c r="C229" t="n">
-        <v>164</v>
+        <v>9</v>
       </c>
       <c r="D229" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="230">
@@ -3626,13 +3626,13 @@
         <v>17</v>
       </c>
       <c r="B230" t="n">
-        <v>2001</v>
+        <v>1992</v>
       </c>
       <c r="C230" t="n">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="D230" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="231">
@@ -3640,13 +3640,13 @@
         <v>17</v>
       </c>
       <c r="B231" t="n">
-        <v>2002</v>
+        <v>1993</v>
       </c>
       <c r="C231" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D231" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="232">
@@ -3654,13 +3654,13 @@
         <v>17</v>
       </c>
       <c r="B232" t="n">
-        <v>2003</v>
+        <v>1994</v>
       </c>
       <c r="C232" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D232" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="233">
@@ -3668,13 +3668,13 @@
         <v>17</v>
       </c>
       <c r="B233" t="n">
-        <v>2004</v>
+        <v>1995</v>
       </c>
       <c r="C233" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="D233" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="234">
@@ -3682,13 +3682,13 @@
         <v>17</v>
       </c>
       <c r="B234" t="n">
-        <v>2005</v>
+        <v>1996</v>
       </c>
       <c r="C234" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D234" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="235">
@@ -3696,13 +3696,13 @@
         <v>17</v>
       </c>
       <c r="B235" t="n">
-        <v>2006</v>
+        <v>1997</v>
       </c>
       <c r="C235" t="n">
-        <v>22</v>
+        <v>155</v>
       </c>
       <c r="D235" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="236">
@@ -3710,13 +3710,13 @@
         <v>17</v>
       </c>
       <c r="B236" t="n">
-        <v>2007</v>
+        <v>1998</v>
       </c>
       <c r="C236" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D236" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="237">
@@ -3724,13 +3724,13 @@
         <v>17</v>
       </c>
       <c r="B237" t="n">
-        <v>2008</v>
+        <v>1999</v>
       </c>
       <c r="C237" t="n">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="D237" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="238">
@@ -3738,10 +3738,10 @@
         <v>17</v>
       </c>
       <c r="B238" t="n">
-        <v>2009</v>
+        <v>2000</v>
       </c>
       <c r="C238" t="n">
-        <v>128</v>
+        <v>57</v>
       </c>
       <c r="D238" t="s">
         <v>8</v>
@@ -3752,13 +3752,13 @@
         <v>17</v>
       </c>
       <c r="B239" t="n">
-        <v>2010</v>
+        <v>2001</v>
       </c>
       <c r="C239" t="n">
-        <v>130</v>
+        <v>18</v>
       </c>
       <c r="D239" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="240">
@@ -3766,13 +3766,13 @@
         <v>17</v>
       </c>
       <c r="B240" t="n">
-        <v>2011</v>
+        <v>2002</v>
       </c>
       <c r="C240" t="n">
-        <v>261</v>
+        <v>67</v>
       </c>
       <c r="D240" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="241">
@@ -3780,13 +3780,13 @@
         <v>17</v>
       </c>
       <c r="B241" t="n">
-        <v>2012</v>
+        <v>2003</v>
       </c>
       <c r="C241" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D241" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="242">
@@ -3794,13 +3794,13 @@
         <v>17</v>
       </c>
       <c r="B242" t="n">
-        <v>2013</v>
+        <v>2004</v>
       </c>
       <c r="C242" t="n">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="D242" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="243">
@@ -3808,13 +3808,13 @@
         <v>17</v>
       </c>
       <c r="B243" t="n">
-        <v>2014</v>
+        <v>2005</v>
       </c>
       <c r="C243" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="D243" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="244">
@@ -3822,13 +3822,13 @@
         <v>17</v>
       </c>
       <c r="B244" t="n">
-        <v>2015</v>
+        <v>2006</v>
       </c>
       <c r="C244" t="n">
-        <v>144</v>
+        <v>61</v>
       </c>
       <c r="D244" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="245">
@@ -3836,13 +3836,13 @@
         <v>17</v>
       </c>
       <c r="B245" t="n">
-        <v>2016</v>
+        <v>2007</v>
       </c>
       <c r="C245" t="n">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="D245" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="246">
@@ -3850,13 +3850,13 @@
         <v>17</v>
       </c>
       <c r="B246" t="n">
-        <v>2017</v>
+        <v>2008</v>
       </c>
       <c r="C246" t="n">
-        <v>146</v>
+        <v>17</v>
       </c>
       <c r="D246" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="247">
@@ -3864,13 +3864,13 @@
         <v>17</v>
       </c>
       <c r="B247" t="n">
-        <v>2018</v>
+        <v>2009</v>
       </c>
       <c r="C247" t="n">
-        <v>205</v>
+        <v>86</v>
       </c>
       <c r="D247" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="248">
@@ -3878,10 +3878,10 @@
         <v>17</v>
       </c>
       <c r="B248" t="n">
-        <v>2019</v>
+        <v>2010</v>
       </c>
       <c r="C248" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D248" t="s">
         <v>9</v>
@@ -3892,13 +3892,13 @@
         <v>17</v>
       </c>
       <c r="B249" t="n">
-        <v>2020</v>
+        <v>2011</v>
       </c>
       <c r="C249" t="n">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="D249" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="250">
@@ -3906,13 +3906,13 @@
         <v>17</v>
       </c>
       <c r="B250" t="n">
-        <v>2021</v>
+        <v>2012</v>
       </c>
       <c r="C250" t="n">
-        <v>128</v>
+        <v>220</v>
       </c>
       <c r="D250" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="251">
@@ -3920,13 +3920,13 @@
         <v>17</v>
       </c>
       <c r="B251" t="n">
-        <v>2022</v>
+        <v>2013</v>
       </c>
       <c r="C251" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D251" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="252">
@@ -3934,13 +3934,13 @@
         <v>17</v>
       </c>
       <c r="B252" t="n">
-        <v>2023</v>
+        <v>2014</v>
       </c>
       <c r="C252" t="n">
-        <v>248</v>
+        <v>173</v>
       </c>
       <c r="D252" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="253">
@@ -3948,13 +3948,13 @@
         <v>17</v>
       </c>
       <c r="B253" t="n">
-        <v>2024</v>
+        <v>2015</v>
       </c>
       <c r="C253" t="n">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="D253" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="254">
@@ -3962,139 +3962,139 @@
         <v>17</v>
       </c>
       <c r="B254" t="n">
-        <v>2025</v>
+        <v>2016</v>
       </c>
       <c r="C254" t="n">
-        <v>53</v>
+        <v>138</v>
       </c>
       <c r="D254" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B255" t="n">
-        <v>1977</v>
+        <v>2017</v>
       </c>
       <c r="C255" t="n">
-        <v>49</v>
+        <v>205</v>
       </c>
       <c r="D255" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B256" t="n">
-        <v>1987</v>
+        <v>2018</v>
       </c>
       <c r="C256" t="n">
-        <v>75</v>
+        <v>215</v>
       </c>
       <c r="D256" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B257" t="n">
-        <v>1988</v>
+        <v>2019</v>
       </c>
       <c r="C257" t="n">
-        <v>4</v>
+        <v>168</v>
       </c>
       <c r="D257" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B258" t="n">
-        <v>1989</v>
+        <v>2020</v>
       </c>
       <c r="C258" t="n">
-        <v>2</v>
+        <v>172</v>
       </c>
       <c r="D258" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B259" t="n">
-        <v>1991</v>
+        <v>2021</v>
       </c>
       <c r="C259" t="n">
-        <v>9</v>
+        <v>236</v>
       </c>
       <c r="D259" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B260" t="n">
-        <v>1992</v>
+        <v>2022</v>
       </c>
       <c r="C260" t="n">
-        <v>90</v>
+        <v>158</v>
       </c>
       <c r="D260" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B261" t="n">
-        <v>1993</v>
+        <v>2023</v>
       </c>
       <c r="C261" t="n">
-        <v>113</v>
+        <v>194</v>
       </c>
       <c r="D261" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B262" t="n">
-        <v>1994</v>
+        <v>2024</v>
       </c>
       <c r="C262" t="n">
-        <v>54</v>
+        <v>356</v>
       </c>
       <c r="D262" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B263" t="n">
-        <v>1995</v>
+        <v>2025</v>
       </c>
       <c r="C263" t="n">
-        <v>30</v>
+        <v>121</v>
       </c>
       <c r="D263" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="264">
@@ -4102,13 +4102,13 @@
         <v>18</v>
       </c>
       <c r="B264" t="n">
-        <v>1996</v>
+        <v>1976</v>
       </c>
       <c r="C264" t="n">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="D264" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="265">
@@ -4116,13 +4116,13 @@
         <v>18</v>
       </c>
       <c r="B265" t="n">
-        <v>1997</v>
+        <v>1985</v>
       </c>
       <c r="C265" t="n">
-        <v>160</v>
+        <v>101</v>
       </c>
       <c r="D265" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="266">
@@ -4130,13 +4130,13 @@
         <v>18</v>
       </c>
       <c r="B266" t="n">
-        <v>1998</v>
+        <v>1986</v>
       </c>
       <c r="C266" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D266" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="267">
@@ -4144,13 +4144,13 @@
         <v>18</v>
       </c>
       <c r="B267" t="n">
-        <v>1999</v>
+        <v>1989</v>
       </c>
       <c r="C267" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D267" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="268">
@@ -4158,13 +4158,13 @@
         <v>18</v>
       </c>
       <c r="B268" t="n">
-        <v>2000</v>
+        <v>1991</v>
       </c>
       <c r="C268" t="n">
-        <v>45</v>
+        <v>133</v>
       </c>
       <c r="D268" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="269">
@@ -4172,13 +4172,13 @@
         <v>18</v>
       </c>
       <c r="B269" t="n">
-        <v>2001</v>
+        <v>1992</v>
       </c>
       <c r="C269" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D269" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="270">
@@ -4186,13 +4186,13 @@
         <v>18</v>
       </c>
       <c r="B270" t="n">
-        <v>2002</v>
+        <v>1993</v>
       </c>
       <c r="C270" t="n">
-        <v>73</v>
+        <v>146</v>
       </c>
       <c r="D270" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="271">
@@ -4200,13 +4200,13 @@
         <v>18</v>
       </c>
       <c r="B271" t="n">
-        <v>2003</v>
+        <v>1996</v>
       </c>
       <c r="C271" t="n">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="D271" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="272">
@@ -4214,13 +4214,13 @@
         <v>18</v>
       </c>
       <c r="B272" t="n">
-        <v>2004</v>
+        <v>1997</v>
       </c>
       <c r="C272" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D272" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="273">
@@ -4228,13 +4228,13 @@
         <v>18</v>
       </c>
       <c r="B273" t="n">
-        <v>2005</v>
+        <v>1998</v>
       </c>
       <c r="C273" t="n">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="D273" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="274">
@@ -4242,13 +4242,13 @@
         <v>18</v>
       </c>
       <c r="B274" t="n">
-        <v>2006</v>
+        <v>1999</v>
       </c>
       <c r="C274" t="n">
-        <v>46</v>
+        <v>109</v>
       </c>
       <c r="D274" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="275">
@@ -4256,10 +4256,10 @@
         <v>18</v>
       </c>
       <c r="B275" t="n">
-        <v>2007</v>
+        <v>2000</v>
       </c>
       <c r="C275" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D275" t="s">
         <v>8</v>
@@ -4270,10 +4270,10 @@
         <v>18</v>
       </c>
       <c r="B276" t="n">
-        <v>2008</v>
+        <v>2001</v>
       </c>
       <c r="C276" t="n">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="D276" t="s">
         <v>8</v>
@@ -4284,10 +4284,10 @@
         <v>18</v>
       </c>
       <c r="B277" t="n">
-        <v>2009</v>
+        <v>2002</v>
       </c>
       <c r="C277" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="D277" t="s">
         <v>8</v>
@@ -4298,13 +4298,13 @@
         <v>18</v>
       </c>
       <c r="B278" t="n">
-        <v>2010</v>
+        <v>2005</v>
       </c>
       <c r="C278" t="n">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="D278" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="279">
@@ -4312,13 +4312,13 @@
         <v>18</v>
       </c>
       <c r="B279" t="n">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="C279" t="n">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="D279" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="280">
@@ -4326,13 +4326,13 @@
         <v>18</v>
       </c>
       <c r="B280" t="n">
-        <v>2012</v>
+        <v>2007</v>
       </c>
       <c r="C280" t="n">
-        <v>167</v>
+        <v>56</v>
       </c>
       <c r="D280" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="281">
@@ -4340,13 +4340,13 @@
         <v>18</v>
       </c>
       <c r="B281" t="n">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="C281" t="n">
-        <v>190</v>
+        <v>35</v>
       </c>
       <c r="D281" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="282">
@@ -4354,13 +4354,13 @@
         <v>18</v>
       </c>
       <c r="B282" t="n">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="C282" t="n">
-        <v>123</v>
+        <v>29</v>
       </c>
       <c r="D282" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="283">
@@ -4368,10 +4368,10 @@
         <v>18</v>
       </c>
       <c r="B283" t="n">
-        <v>2015</v>
+        <v>2010</v>
       </c>
       <c r="C283" t="n">
-        <v>185</v>
+        <v>124</v>
       </c>
       <c r="D283" t="s">
         <v>9</v>
@@ -4382,10 +4382,10 @@
         <v>18</v>
       </c>
       <c r="B284" t="n">
-        <v>2016</v>
+        <v>2011</v>
       </c>
       <c r="C284" t="n">
-        <v>114</v>
+        <v>186</v>
       </c>
       <c r="D284" t="s">
         <v>9</v>
@@ -4396,10 +4396,10 @@
         <v>18</v>
       </c>
       <c r="B285" t="n">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="C285" t="n">
-        <v>224</v>
+        <v>195</v>
       </c>
       <c r="D285" t="s">
         <v>9</v>
@@ -4410,10 +4410,10 @@
         <v>18</v>
       </c>
       <c r="B286" t="n">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="C286" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D286" t="s">
         <v>9</v>
@@ -4424,10 +4424,10 @@
         <v>18</v>
       </c>
       <c r="B287" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="C287" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D287" t="s">
         <v>9</v>
@@ -4438,13 +4438,13 @@
         <v>18</v>
       </c>
       <c r="B288" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="C288" t="n">
-        <v>151</v>
+        <v>312</v>
       </c>
       <c r="D288" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="289">
@@ -4452,13 +4452,13 @@
         <v>18</v>
       </c>
       <c r="B289" t="n">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="C289" t="n">
-        <v>146</v>
+        <v>181</v>
       </c>
       <c r="D289" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="290">
@@ -4466,13 +4466,13 @@
         <v>18</v>
       </c>
       <c r="B290" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C290" t="n">
-        <v>153</v>
+        <v>193</v>
       </c>
       <c r="D290" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="291">
@@ -4480,13 +4480,13 @@
         <v>18</v>
       </c>
       <c r="B291" t="n">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="C291" t="n">
-        <v>165</v>
+        <v>205</v>
       </c>
       <c r="D291" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="292">
@@ -4494,13 +4494,13 @@
         <v>18</v>
       </c>
       <c r="B292" t="n">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="C292" t="n">
-        <v>208</v>
+        <v>289</v>
       </c>
       <c r="D292" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="293">
@@ -4508,10 +4508,10 @@
         <v>18</v>
       </c>
       <c r="B293" t="n">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="C293" t="n">
-        <v>87</v>
+        <v>576</v>
       </c>
       <c r="D293" t="s">
         <v>10</v>
@@ -4519,72 +4519,72 @@
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B294" t="n">
-        <v>1977</v>
+        <v>2021</v>
       </c>
       <c r="C294" t="n">
-        <v>76</v>
+        <v>440</v>
       </c>
       <c r="D294" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B295" t="n">
-        <v>1978</v>
+        <v>2022</v>
       </c>
       <c r="C295" t="n">
-        <v>4</v>
+        <v>453</v>
       </c>
       <c r="D295" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B296" t="n">
-        <v>1985</v>
+        <v>2023</v>
       </c>
       <c r="C296" t="n">
-        <v>87</v>
+        <v>669</v>
       </c>
       <c r="D296" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B297" t="n">
-        <v>1989</v>
+        <v>2024</v>
       </c>
       <c r="C297" t="n">
-        <v>6</v>
+        <v>715</v>
       </c>
       <c r="D297" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B298" t="n">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C298" t="n">
-        <v>200</v>
+        <v>331</v>
       </c>
       <c r="D298" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="299">
@@ -4592,13 +4592,13 @@
         <v>19</v>
       </c>
       <c r="B299" t="n">
-        <v>1993</v>
+        <v>1972</v>
       </c>
       <c r="C299" t="n">
-        <v>162</v>
+        <v>10</v>
       </c>
       <c r="D299" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="300">
@@ -4606,13 +4606,13 @@
         <v>19</v>
       </c>
       <c r="B300" t="n">
-        <v>1996</v>
+        <v>1974</v>
       </c>
       <c r="C300" t="n">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="D300" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="301">
@@ -4620,13 +4620,13 @@
         <v>19</v>
       </c>
       <c r="B301" t="n">
-        <v>1997</v>
+        <v>1975</v>
       </c>
       <c r="C301" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D301" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="302">
@@ -4634,13 +4634,13 @@
         <v>19</v>
       </c>
       <c r="B302" t="n">
-        <v>1998</v>
+        <v>1976</v>
       </c>
       <c r="C302" t="n">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="D302" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="303">
@@ -4648,13 +4648,13 @@
         <v>19</v>
       </c>
       <c r="B303" t="n">
-        <v>1999</v>
+        <v>1977</v>
       </c>
       <c r="C303" t="n">
-        <v>107</v>
+        <v>202</v>
       </c>
       <c r="D303" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="304">
@@ -4662,13 +4662,13 @@
         <v>19</v>
       </c>
       <c r="B304" t="n">
-        <v>2000</v>
+        <v>1978</v>
       </c>
       <c r="C304" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="D304" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="305">
@@ -4676,13 +4676,13 @@
         <v>19</v>
       </c>
       <c r="B305" t="n">
-        <v>2001</v>
+        <v>1979</v>
       </c>
       <c r="C305" t="n">
-        <v>130</v>
+        <v>219</v>
       </c>
       <c r="D305" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="306">
@@ -4690,13 +4690,13 @@
         <v>19</v>
       </c>
       <c r="B306" t="n">
-        <v>2002</v>
+        <v>1980</v>
       </c>
       <c r="C306" t="n">
-        <v>95</v>
+        <v>213</v>
       </c>
       <c r="D306" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="307">
@@ -4704,13 +4704,13 @@
         <v>19</v>
       </c>
       <c r="B307" t="n">
-        <v>2004</v>
+        <v>1981</v>
       </c>
       <c r="C307" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="D307" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="308">
@@ -4718,13 +4718,13 @@
         <v>19</v>
       </c>
       <c r="B308" t="n">
-        <v>2006</v>
+        <v>1983</v>
       </c>
       <c r="C308" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D308" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="309">
@@ -4732,13 +4732,13 @@
         <v>19</v>
       </c>
       <c r="B309" t="n">
-        <v>2007</v>
+        <v>1984</v>
       </c>
       <c r="C309" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D309" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="310">
@@ -4746,13 +4746,13 @@
         <v>19</v>
       </c>
       <c r="B310" t="n">
-        <v>2009</v>
+        <v>1985</v>
       </c>
       <c r="C310" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D310" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="311">
@@ -4760,13 +4760,13 @@
         <v>19</v>
       </c>
       <c r="B311" t="n">
-        <v>2010</v>
+        <v>1986</v>
       </c>
       <c r="C311" t="n">
-        <v>111</v>
+        <v>3</v>
       </c>
       <c r="D311" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="312">
@@ -4774,13 +4774,13 @@
         <v>19</v>
       </c>
       <c r="B312" t="n">
-        <v>2011</v>
+        <v>1987</v>
       </c>
       <c r="C312" t="n">
-        <v>82</v>
+        <v>1</v>
       </c>
       <c r="D312" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="313">
@@ -4788,13 +4788,13 @@
         <v>19</v>
       </c>
       <c r="B313" t="n">
-        <v>2012</v>
+        <v>1989</v>
       </c>
       <c r="C313" t="n">
-        <v>218</v>
+        <v>36</v>
       </c>
       <c r="D313" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="314">
@@ -4802,13 +4802,13 @@
         <v>19</v>
       </c>
       <c r="B314" t="n">
-        <v>2013</v>
+        <v>1991</v>
       </c>
       <c r="C314" t="n">
-        <v>119</v>
+        <v>47</v>
       </c>
       <c r="D314" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="315">
@@ -4816,13 +4816,13 @@
         <v>19</v>
       </c>
       <c r="B315" t="n">
-        <v>2014</v>
+        <v>1992</v>
       </c>
       <c r="C315" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D315" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="316">
@@ -4830,13 +4830,13 @@
         <v>19</v>
       </c>
       <c r="B316" t="n">
-        <v>2015</v>
+        <v>1993</v>
       </c>
       <c r="C316" t="n">
-        <v>299</v>
+        <v>115</v>
       </c>
       <c r="D316" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="317">
@@ -4844,13 +4844,13 @@
         <v>19</v>
       </c>
       <c r="B317" t="n">
-        <v>2016</v>
+        <v>1994</v>
       </c>
       <c r="C317" t="n">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="D317" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="318">
@@ -4858,13 +4858,13 @@
         <v>19</v>
       </c>
       <c r="B318" t="n">
-        <v>2017</v>
+        <v>1995</v>
       </c>
       <c r="C318" t="n">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="D318" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="319">
@@ -4872,13 +4872,13 @@
         <v>19</v>
       </c>
       <c r="B319" t="n">
-        <v>2018</v>
+        <v>1996</v>
       </c>
       <c r="C319" t="n">
-        <v>180</v>
+        <v>49</v>
       </c>
       <c r="D319" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="320">
@@ -4886,13 +4886,13 @@
         <v>19</v>
       </c>
       <c r="B320" t="n">
-        <v>2019</v>
+        <v>1997</v>
       </c>
       <c r="C320" t="n">
-        <v>234</v>
+        <v>39</v>
       </c>
       <c r="D320" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="321">
@@ -4900,13 +4900,13 @@
         <v>19</v>
       </c>
       <c r="B321" t="n">
-        <v>2020</v>
+        <v>1998</v>
       </c>
       <c r="C321" t="n">
-        <v>323</v>
+        <v>126</v>
       </c>
       <c r="D321" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="322">
@@ -4914,13 +4914,13 @@
         <v>19</v>
       </c>
       <c r="B322" t="n">
-        <v>2021</v>
+        <v>1999</v>
       </c>
       <c r="C322" t="n">
-        <v>277</v>
+        <v>130</v>
       </c>
       <c r="D322" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="323">
@@ -4928,13 +4928,13 @@
         <v>19</v>
       </c>
       <c r="B323" t="n">
-        <v>2022</v>
+        <v>2000</v>
       </c>
       <c r="C323" t="n">
-        <v>340</v>
+        <v>157</v>
       </c>
       <c r="D323" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="324">
@@ -4942,13 +4942,13 @@
         <v>19</v>
       </c>
       <c r="B324" t="n">
-        <v>2023</v>
+        <v>2001</v>
       </c>
       <c r="C324" t="n">
-        <v>537</v>
+        <v>130</v>
       </c>
       <c r="D324" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="325">
@@ -4956,13 +4956,13 @@
         <v>19</v>
       </c>
       <c r="B325" t="n">
-        <v>2024</v>
+        <v>2002</v>
       </c>
       <c r="C325" t="n">
-        <v>705</v>
+        <v>82</v>
       </c>
       <c r="D325" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="326">
@@ -4970,321 +4970,321 @@
         <v>19</v>
       </c>
       <c r="B326" t="n">
-        <v>2025</v>
+        <v>2003</v>
       </c>
       <c r="C326" t="n">
-        <v>297</v>
+        <v>55</v>
       </c>
       <c r="D326" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B327" t="n">
-        <v>1972</v>
+        <v>2004</v>
       </c>
       <c r="C327" t="n">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="D327" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B328" t="n">
-        <v>1975</v>
+        <v>2005</v>
       </c>
       <c r="C328" t="n">
-        <v>7</v>
+        <v>88</v>
       </c>
       <c r="D328" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B329" t="n">
-        <v>1977</v>
+        <v>2006</v>
       </c>
       <c r="C329" t="n">
-        <v>104</v>
+        <v>6</v>
       </c>
       <c r="D329" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B330" t="n">
-        <v>1979</v>
+        <v>2007</v>
       </c>
       <c r="C330" t="n">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="D330" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B331" t="n">
-        <v>1989</v>
+        <v>2008</v>
       </c>
       <c r="C331" t="n">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="D331" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B332" t="n">
-        <v>1992</v>
+        <v>2009</v>
       </c>
       <c r="C332" t="n">
-        <v>154</v>
+        <v>111</v>
       </c>
       <c r="D332" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B333" t="n">
-        <v>1993</v>
+        <v>2010</v>
       </c>
       <c r="C333" t="n">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="D333" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B334" t="n">
-        <v>1994</v>
+        <v>2011</v>
       </c>
       <c r="C334" t="n">
-        <v>58</v>
+        <v>216</v>
       </c>
       <c r="D334" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B335" t="n">
-        <v>1996</v>
+        <v>2012</v>
       </c>
       <c r="C335" t="n">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="D335" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B336" t="n">
-        <v>1998</v>
+        <v>2013</v>
       </c>
       <c r="C336" t="n">
-        <v>172</v>
+        <v>115</v>
       </c>
       <c r="D336" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B337" t="n">
-        <v>2000</v>
+        <v>2014</v>
       </c>
       <c r="C337" t="n">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="D337" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B338" t="n">
-        <v>2001</v>
+        <v>2015</v>
       </c>
       <c r="C338" t="n">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="D338" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B339" t="n">
-        <v>2003</v>
+        <v>2016</v>
       </c>
       <c r="C339" t="n">
-        <v>150</v>
+        <v>113</v>
       </c>
       <c r="D339" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B340" t="n">
-        <v>2004</v>
+        <v>2017</v>
       </c>
       <c r="C340" t="n">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="D340" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B341" t="n">
-        <v>2005</v>
+        <v>2018</v>
       </c>
       <c r="C341" t="n">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="D341" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B342" t="n">
-        <v>2007</v>
+        <v>2019</v>
       </c>
       <c r="C342" t="n">
-        <v>91</v>
+        <v>162</v>
       </c>
       <c r="D342" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B343" t="n">
-        <v>2008</v>
+        <v>2020</v>
       </c>
       <c r="C343" t="n">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="D343" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B344" t="n">
-        <v>2009</v>
+        <v>2021</v>
       </c>
       <c r="C344" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="D344" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B345" t="n">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C345" t="n">
-        <v>27</v>
+        <v>160</v>
       </c>
       <c r="D345" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B346" t="n">
-        <v>2011</v>
+        <v>2023</v>
       </c>
       <c r="C346" t="n">
-        <v>189</v>
+        <v>273</v>
       </c>
       <c r="D346" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B347" t="n">
-        <v>2012</v>
+        <v>2024</v>
       </c>
       <c r="C347" t="n">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="D347" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B348" t="n">
-        <v>2013</v>
+        <v>2025</v>
       </c>
       <c r="C348" t="n">
-        <v>275</v>
+        <v>13</v>
       </c>
       <c r="D348" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="349">
@@ -5292,13 +5292,13 @@
         <v>20</v>
       </c>
       <c r="B349" t="n">
-        <v>2014</v>
+        <v>1972</v>
       </c>
       <c r="C349" t="n">
-        <v>166</v>
+        <v>7</v>
       </c>
       <c r="D349" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="350">
@@ -5306,13 +5306,13 @@
         <v>20</v>
       </c>
       <c r="B350" t="n">
-        <v>2015</v>
+        <v>1977</v>
       </c>
       <c r="C350" t="n">
-        <v>217</v>
+        <v>107</v>
       </c>
       <c r="D350" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="351">
@@ -5320,13 +5320,13 @@
         <v>20</v>
       </c>
       <c r="B351" t="n">
-        <v>2016</v>
+        <v>1979</v>
       </c>
       <c r="C351" t="n">
-        <v>208</v>
+        <v>10</v>
       </c>
       <c r="D351" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="352">
@@ -5334,13 +5334,13 @@
         <v>20</v>
       </c>
       <c r="B352" t="n">
-        <v>2017</v>
+        <v>1980</v>
       </c>
       <c r="C352" t="n">
-        <v>274</v>
+        <v>3</v>
       </c>
       <c r="D352" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="353">
@@ -5348,13 +5348,13 @@
         <v>20</v>
       </c>
       <c r="B353" t="n">
-        <v>2018</v>
+        <v>1984</v>
       </c>
       <c r="C353" t="n">
-        <v>448</v>
+        <v>11</v>
       </c>
       <c r="D353" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="354">
@@ -5362,13 +5362,13 @@
         <v>20</v>
       </c>
       <c r="B354" t="n">
-        <v>2019</v>
+        <v>1988</v>
       </c>
       <c r="C354" t="n">
-        <v>231</v>
+        <v>6</v>
       </c>
       <c r="D354" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="355">
@@ -5376,13 +5376,13 @@
         <v>20</v>
       </c>
       <c r="B355" t="n">
-        <v>2020</v>
+        <v>1989</v>
       </c>
       <c r="C355" t="n">
-        <v>177</v>
+        <v>2</v>
       </c>
       <c r="D355" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="356">
@@ -5390,13 +5390,13 @@
         <v>20</v>
       </c>
       <c r="B356" t="n">
-        <v>2021</v>
+        <v>1990</v>
       </c>
       <c r="C356" t="n">
-        <v>458</v>
+        <v>62</v>
       </c>
       <c r="D356" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="357">
@@ -5404,13 +5404,13 @@
         <v>20</v>
       </c>
       <c r="B357" t="n">
-        <v>2022</v>
+        <v>1992</v>
       </c>
       <c r="C357" t="n">
-        <v>330</v>
+        <v>156</v>
       </c>
       <c r="D357" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="358">
@@ -5418,13 +5418,13 @@
         <v>20</v>
       </c>
       <c r="B358" t="n">
-        <v>2023</v>
+        <v>1993</v>
       </c>
       <c r="C358" t="n">
-        <v>190</v>
+        <v>35</v>
       </c>
       <c r="D358" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="359">
@@ -5432,13 +5432,13 @@
         <v>20</v>
       </c>
       <c r="B359" t="n">
-        <v>2024</v>
+        <v>1994</v>
       </c>
       <c r="C359" t="n">
-        <v>482</v>
+        <v>88</v>
       </c>
       <c r="D359" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="360">
@@ -5446,150 +5446,150 @@
         <v>20</v>
       </c>
       <c r="B360" t="n">
-        <v>2025</v>
+        <v>1996</v>
       </c>
       <c r="C360" t="n">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="D360" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B361" t="n">
-        <v>1972</v>
+        <v>1998</v>
       </c>
       <c r="C361" t="n">
-        <v>6</v>
+        <v>218</v>
       </c>
       <c r="D361" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B362" t="n">
-        <v>1976</v>
+        <v>1999</v>
       </c>
       <c r="C362" t="n">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="D362" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B363" t="n">
-        <v>1979</v>
+        <v>2000</v>
       </c>
       <c r="C363" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="D363" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B364" t="n">
-        <v>1992</v>
+        <v>2002</v>
       </c>
       <c r="C364" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D364" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B365" t="n">
-        <v>1993</v>
+        <v>2003</v>
       </c>
       <c r="C365" t="n">
-        <v>55</v>
+        <v>198</v>
       </c>
       <c r="D365" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B366" t="n">
-        <v>1994</v>
+        <v>2004</v>
       </c>
       <c r="C366" t="n">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="D366" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B367" t="n">
-        <v>1995</v>
+        <v>2005</v>
       </c>
       <c r="C367" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D367" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B368" t="n">
-        <v>1996</v>
+        <v>2007</v>
       </c>
       <c r="C368" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D368" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B369" t="n">
-        <v>1998</v>
+        <v>2008</v>
       </c>
       <c r="C369" t="n">
-        <v>61</v>
+        <v>270</v>
       </c>
       <c r="D369" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B370" t="n">
-        <v>2002</v>
+        <v>2009</v>
       </c>
       <c r="C370" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="D370" t="s">
         <v>8</v>
@@ -5597,97 +5597,97 @@
     </row>
     <row r="371">
       <c r="A371" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B371" t="n">
-        <v>2003</v>
+        <v>2010</v>
       </c>
       <c r="C371" t="n">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="D371" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B372" t="n">
-        <v>2004</v>
+        <v>2011</v>
       </c>
       <c r="C372" t="n">
-        <v>204</v>
+        <v>243</v>
       </c>
       <c r="D372" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B373" t="n">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="C373" t="n">
-        <v>135</v>
+        <v>240</v>
       </c>
       <c r="D373" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B374" t="n">
-        <v>2007</v>
+        <v>2013</v>
       </c>
       <c r="C374" t="n">
-        <v>140</v>
+        <v>280</v>
       </c>
       <c r="D374" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B375" t="n">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="C375" t="n">
-        <v>95</v>
+        <v>272</v>
       </c>
       <c r="D375" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B376" t="n">
-        <v>2009</v>
+        <v>2015</v>
       </c>
       <c r="C376" t="n">
-        <v>144</v>
+        <v>244</v>
       </c>
       <c r="D376" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B377" t="n">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C377" t="n">
-        <v>84</v>
+        <v>196</v>
       </c>
       <c r="D377" t="s">
         <v>9</v>
@@ -5695,13 +5695,13 @@
     </row>
     <row r="378">
       <c r="A378" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B378" t="n">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="C378" t="n">
-        <v>60</v>
+        <v>311</v>
       </c>
       <c r="D378" t="s">
         <v>9</v>
@@ -5709,13 +5709,13 @@
     </row>
     <row r="379">
       <c r="A379" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B379" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="C379" t="n">
-        <v>43</v>
+        <v>326</v>
       </c>
       <c r="D379" t="s">
         <v>9</v>
@@ -5723,13 +5723,13 @@
     </row>
     <row r="380">
       <c r="A380" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B380" t="n">
-        <v>2013</v>
+        <v>2019</v>
       </c>
       <c r="C380" t="n">
-        <v>147</v>
+        <v>309</v>
       </c>
       <c r="D380" t="s">
         <v>9</v>
@@ -5737,86 +5737,86 @@
     </row>
     <row r="381">
       <c r="A381" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B381" t="n">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="C381" t="n">
-        <v>141</v>
+        <v>253</v>
       </c>
       <c r="D381" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B382" t="n">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="C382" t="n">
-        <v>144</v>
+        <v>362</v>
       </c>
       <c r="D382" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B383" t="n">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="C383" t="n">
-        <v>121</v>
+        <v>285</v>
       </c>
       <c r="D383" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B384" t="n">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="C384" t="n">
-        <v>114</v>
+        <v>269</v>
       </c>
       <c r="D384" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B385" t="n">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="C385" t="n">
-        <v>133</v>
+        <v>451</v>
       </c>
       <c r="D385" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B386" t="n">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C386" t="n">
-        <v>174</v>
+        <v>125</v>
       </c>
       <c r="D386" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="387">
@@ -5824,13 +5824,13 @@
         <v>21</v>
       </c>
       <c r="B387" t="n">
-        <v>2020</v>
+        <v>1972</v>
       </c>
       <c r="C387" t="n">
-        <v>217</v>
+        <v>6</v>
       </c>
       <c r="D387" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="388">
@@ -5838,13 +5838,13 @@
         <v>21</v>
       </c>
       <c r="B388" t="n">
-        <v>2021</v>
+        <v>1991</v>
       </c>
       <c r="C388" t="n">
-        <v>220</v>
+        <v>11</v>
       </c>
       <c r="D388" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="389">
@@ -5852,13 +5852,13 @@
         <v>21</v>
       </c>
       <c r="B389" t="n">
-        <v>2022</v>
+        <v>1992</v>
       </c>
       <c r="C389" t="n">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="D389" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="390">
@@ -5866,13 +5866,13 @@
         <v>21</v>
       </c>
       <c r="B390" t="n">
-        <v>2023</v>
+        <v>1993</v>
       </c>
       <c r="C390" t="n">
-        <v>137</v>
+        <v>60</v>
       </c>
       <c r="D390" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="391">
@@ -5880,13 +5880,13 @@
         <v>21</v>
       </c>
       <c r="B391" t="n">
-        <v>2024</v>
+        <v>1995</v>
       </c>
       <c r="C391" t="n">
-        <v>237</v>
+        <v>69</v>
       </c>
       <c r="D391" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="392">
@@ -5894,38 +5894,38 @@
         <v>21</v>
       </c>
       <c r="B392" t="n">
-        <v>2025</v>
+        <v>1996</v>
       </c>
       <c r="C392" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="D392" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B393" t="n">
-        <v>1981</v>
+        <v>1998</v>
       </c>
       <c r="C393" t="n">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="D393" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B394" t="n">
-        <v>1991</v>
+        <v>1999</v>
       </c>
       <c r="C394" t="n">
-        <v>11</v>
+        <v>89</v>
       </c>
       <c r="D394" t="s">
         <v>7</v>
@@ -5933,324 +5933,324 @@
     </row>
     <row r="395">
       <c r="A395" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B395" t="n">
-        <v>1992</v>
+        <v>2002</v>
       </c>
       <c r="C395" t="n">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="D395" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B396" t="n">
-        <v>1993</v>
+        <v>2003</v>
       </c>
       <c r="C396" t="n">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="D396" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B397" t="n">
-        <v>1995</v>
+        <v>2004</v>
       </c>
       <c r="C397" t="n">
-        <v>47</v>
+        <v>141</v>
       </c>
       <c r="D397" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B398" t="n">
-        <v>1996</v>
+        <v>2006</v>
       </c>
       <c r="C398" t="n">
-        <v>54</v>
+        <v>153</v>
       </c>
       <c r="D398" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B399" t="n">
-        <v>1997</v>
+        <v>2007</v>
       </c>
       <c r="C399" t="n">
-        <v>59</v>
+        <v>155</v>
       </c>
       <c r="D399" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B400" t="n">
-        <v>1998</v>
+        <v>2008</v>
       </c>
       <c r="C400" t="n">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="D400" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B401" t="n">
-        <v>1999</v>
+        <v>2009</v>
       </c>
       <c r="C401" t="n">
-        <v>62</v>
+        <v>141</v>
       </c>
       <c r="D401" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B402" t="n">
-        <v>2000</v>
+        <v>2010</v>
       </c>
       <c r="C402" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="D402" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B403" t="n">
-        <v>2001</v>
+        <v>2011</v>
       </c>
       <c r="C403" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D403" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B404" t="n">
-        <v>2002</v>
+        <v>2012</v>
       </c>
       <c r="C404" t="n">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="D404" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B405" t="n">
-        <v>2003</v>
+        <v>2013</v>
       </c>
       <c r="C405" t="n">
-        <v>88</v>
+        <v>168</v>
       </c>
       <c r="D405" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B406" t="n">
-        <v>2004</v>
+        <v>2014</v>
       </c>
       <c r="C406" t="n">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="D406" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B407" t="n">
-        <v>2005</v>
+        <v>2015</v>
       </c>
       <c r="C407" t="n">
-        <v>31</v>
+        <v>146</v>
       </c>
       <c r="D407" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B408" t="n">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C408" t="n">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="D408" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B409" t="n">
-        <v>2007</v>
+        <v>2017</v>
       </c>
       <c r="C409" t="n">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="D409" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B410" t="n">
-        <v>2008</v>
+        <v>2018</v>
       </c>
       <c r="C410" t="n">
-        <v>58</v>
+        <v>165</v>
       </c>
       <c r="D410" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B411" t="n">
-        <v>2009</v>
+        <v>2019</v>
       </c>
       <c r="C411" t="n">
-        <v>53</v>
+        <v>165</v>
       </c>
       <c r="D411" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B412" t="n">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="C412" t="n">
-        <v>83</v>
+        <v>182</v>
       </c>
       <c r="D412" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B413" t="n">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="C413" t="n">
-        <v>65</v>
+        <v>191</v>
       </c>
       <c r="D413" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B414" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="C414" t="n">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="D414" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B415" t="n">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="C415" t="n">
-        <v>207</v>
+        <v>151</v>
       </c>
       <c r="D415" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B416" t="n">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="C416" t="n">
-        <v>123</v>
+        <v>366</v>
       </c>
       <c r="D416" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B417" t="n">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="C417" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="D417" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="418">
@@ -6258,13 +6258,13 @@
         <v>22</v>
       </c>
       <c r="B418" t="n">
-        <v>2016</v>
+        <v>1979</v>
       </c>
       <c r="C418" t="n">
-        <v>133</v>
+        <v>47</v>
       </c>
       <c r="D418" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="419">
@@ -6272,13 +6272,13 @@
         <v>22</v>
       </c>
       <c r="B419" t="n">
-        <v>2017</v>
+        <v>1980</v>
       </c>
       <c r="C419" t="n">
-        <v>125</v>
+        <v>260</v>
       </c>
       <c r="D419" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="420">
@@ -6286,13 +6286,13 @@
         <v>22</v>
       </c>
       <c r="B420" t="n">
-        <v>2018</v>
+        <v>1985</v>
       </c>
       <c r="C420" t="n">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="D420" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="421">
@@ -6300,13 +6300,13 @@
         <v>22</v>
       </c>
       <c r="B421" t="n">
-        <v>2019</v>
+        <v>1986</v>
       </c>
       <c r="C421" t="n">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="D421" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="422">
@@ -6314,13 +6314,13 @@
         <v>22</v>
       </c>
       <c r="B422" t="n">
-        <v>2020</v>
+        <v>1987</v>
       </c>
       <c r="C422" t="n">
-        <v>186</v>
+        <v>40</v>
       </c>
       <c r="D422" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="423">
@@ -6328,13 +6328,13 @@
         <v>22</v>
       </c>
       <c r="B423" t="n">
-        <v>2021</v>
+        <v>1991</v>
       </c>
       <c r="C423" t="n">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="D423" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="424">
@@ -6342,13 +6342,13 @@
         <v>22</v>
       </c>
       <c r="B424" t="n">
-        <v>2022</v>
+        <v>1992</v>
       </c>
       <c r="C424" t="n">
-        <v>168</v>
+        <v>108</v>
       </c>
       <c r="D424" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="425">
@@ -6356,13 +6356,13 @@
         <v>22</v>
       </c>
       <c r="B425" t="n">
-        <v>2023</v>
+        <v>1993</v>
       </c>
       <c r="C425" t="n">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="D425" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="426">
@@ -6370,13 +6370,13 @@
         <v>22</v>
       </c>
       <c r="B426" t="n">
-        <v>2024</v>
+        <v>1994</v>
       </c>
       <c r="C426" t="n">
-        <v>321</v>
+        <v>157</v>
       </c>
       <c r="D426" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="427">
@@ -6384,433 +6384,433 @@
         <v>22</v>
       </c>
       <c r="B427" t="n">
-        <v>2025</v>
+        <v>1995</v>
       </c>
       <c r="C427" t="n">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="D427" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B428" t="n">
-        <v>1978</v>
+        <v>1996</v>
       </c>
       <c r="C428" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="D428" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B429" t="n">
-        <v>1979</v>
+        <v>1997</v>
       </c>
       <c r="C429" t="n">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="D429" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B430" t="n">
-        <v>1984</v>
+        <v>1998</v>
       </c>
       <c r="C430" t="n">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="D430" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B431" t="n">
-        <v>1986</v>
+        <v>1999</v>
       </c>
       <c r="C431" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="D431" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B432" t="n">
-        <v>1987</v>
+        <v>2000</v>
       </c>
       <c r="C432" t="n">
-        <v>47</v>
+        <v>116</v>
       </c>
       <c r="D432" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B433" t="n">
-        <v>1988</v>
+        <v>2001</v>
       </c>
       <c r="C433" t="n">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="D433" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B434" t="n">
-        <v>1991</v>
+        <v>2002</v>
       </c>
       <c r="C434" t="n">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="D434" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B435" t="n">
-        <v>1992</v>
+        <v>2003</v>
       </c>
       <c r="C435" t="n">
-        <v>190</v>
+        <v>6</v>
       </c>
       <c r="D435" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B436" t="n">
-        <v>1993</v>
+        <v>2004</v>
       </c>
       <c r="C436" t="n">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="D436" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="s">
+        <v>22</v>
+      </c>
+      <c r="B437" t="n">
+        <v>2005</v>
+      </c>
+      <c r="C437" t="n">
         <v>23</v>
       </c>
-      <c r="B437" t="n">
-        <v>1994</v>
-      </c>
-      <c r="C437" t="n">
-        <v>90</v>
-      </c>
       <c r="D437" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B438" t="n">
-        <v>1995</v>
+        <v>2006</v>
       </c>
       <c r="C438" t="n">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="D438" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B439" t="n">
-        <v>1996</v>
+        <v>2007</v>
       </c>
       <c r="C439" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="D439" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B440" t="n">
-        <v>1997</v>
+        <v>2008</v>
       </c>
       <c r="C440" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D440" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B441" t="n">
-        <v>1998</v>
+        <v>2009</v>
       </c>
       <c r="C441" t="n">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="D441" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B442" t="n">
-        <v>1999</v>
+        <v>2010</v>
       </c>
       <c r="C442" t="n">
-        <v>25</v>
+        <v>123</v>
       </c>
       <c r="D442" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B443" t="n">
-        <v>2001</v>
+        <v>2011</v>
       </c>
       <c r="C443" t="n">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="D443" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B444" t="n">
-        <v>2002</v>
+        <v>2012</v>
       </c>
       <c r="C444" t="n">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="D444" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B445" t="n">
-        <v>2003</v>
+        <v>2013</v>
       </c>
       <c r="C445" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="D445" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B446" t="n">
-        <v>2004</v>
+        <v>2014</v>
       </c>
       <c r="C446" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D446" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B447" t="n">
-        <v>2005</v>
+        <v>2015</v>
       </c>
       <c r="C447" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D447" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B448" t="n">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C448" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D448" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B449" t="n">
-        <v>2007</v>
+        <v>2017</v>
       </c>
       <c r="C449" t="n">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="D449" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B450" t="n">
-        <v>2008</v>
+        <v>2018</v>
       </c>
       <c r="C450" t="n">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="D450" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B451" t="n">
-        <v>2009</v>
+        <v>2019</v>
       </c>
       <c r="C451" t="n">
-        <v>54</v>
+        <v>121</v>
       </c>
       <c r="D451" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B452" t="n">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="C452" t="n">
-        <v>85</v>
+        <v>220</v>
       </c>
       <c r="D452" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B453" t="n">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="C453" t="n">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="D453" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B454" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="C454" t="n">
-        <v>98</v>
+        <v>186</v>
       </c>
       <c r="D454" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B455" t="n">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="C455" t="n">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="D455" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B456" t="n">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="C456" t="n">
-        <v>170</v>
+        <v>128</v>
       </c>
       <c r="D456" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B457" t="n">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="C457" t="n">
-        <v>192</v>
+        <v>62</v>
       </c>
       <c r="D457" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="458">
@@ -6818,13 +6818,13 @@
         <v>23</v>
       </c>
       <c r="B458" t="n">
-        <v>2016</v>
+        <v>1981</v>
       </c>
       <c r="C458" t="n">
-        <v>102</v>
+        <v>11</v>
       </c>
       <c r="D458" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="459">
@@ -6832,13 +6832,13 @@
         <v>23</v>
       </c>
       <c r="B459" t="n">
-        <v>2017</v>
+        <v>1991</v>
       </c>
       <c r="C459" t="n">
-        <v>117</v>
+        <v>11</v>
       </c>
       <c r="D459" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="460">
@@ -6846,13 +6846,13 @@
         <v>23</v>
       </c>
       <c r="B460" t="n">
-        <v>2018</v>
+        <v>1992</v>
       </c>
       <c r="C460" t="n">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="D460" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="461">
@@ -6860,13 +6860,13 @@
         <v>23</v>
       </c>
       <c r="B461" t="n">
-        <v>2019</v>
+        <v>1993</v>
       </c>
       <c r="C461" t="n">
-        <v>156</v>
+        <v>72</v>
       </c>
       <c r="D461" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="462">
@@ -6874,13 +6874,13 @@
         <v>23</v>
       </c>
       <c r="B462" t="n">
-        <v>2020</v>
+        <v>1996</v>
       </c>
       <c r="C462" t="n">
-        <v>177</v>
+        <v>55</v>
       </c>
       <c r="D462" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="463">
@@ -6888,13 +6888,13 @@
         <v>23</v>
       </c>
       <c r="B463" t="n">
-        <v>2021</v>
+        <v>1997</v>
       </c>
       <c r="C463" t="n">
-        <v>162</v>
+        <v>63</v>
       </c>
       <c r="D463" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="464">
@@ -6902,13 +6902,13 @@
         <v>23</v>
       </c>
       <c r="B464" t="n">
-        <v>2022</v>
+        <v>1998</v>
       </c>
       <c r="C464" t="n">
-        <v>164</v>
+        <v>72</v>
       </c>
       <c r="D464" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="465">
@@ -6916,13 +6916,13 @@
         <v>23</v>
       </c>
       <c r="B465" t="n">
-        <v>2023</v>
+        <v>1999</v>
       </c>
       <c r="C465" t="n">
-        <v>199</v>
+        <v>63</v>
       </c>
       <c r="D465" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="466">
@@ -6930,13 +6930,13 @@
         <v>23</v>
       </c>
       <c r="B466" t="n">
-        <v>2024</v>
+        <v>2000</v>
       </c>
       <c r="C466" t="n">
-        <v>360</v>
+        <v>74</v>
       </c>
       <c r="D466" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="467">
@@ -6944,349 +6944,349 @@
         <v>23</v>
       </c>
       <c r="B467" t="n">
-        <v>2025</v>
+        <v>2001</v>
       </c>
       <c r="C467" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D467" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B468" t="n">
-        <v>1976</v>
+        <v>2002</v>
       </c>
       <c r="C468" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D468" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B469" t="n">
-        <v>1980</v>
+        <v>2003</v>
       </c>
       <c r="C469" t="n">
-        <v>286</v>
+        <v>70</v>
       </c>
       <c r="D469" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B470" t="n">
-        <v>1985</v>
+        <v>2004</v>
       </c>
       <c r="C470" t="n">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c r="D470" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B471" t="n">
-        <v>1986</v>
+        <v>2005</v>
       </c>
       <c r="C471" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D471" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B472" t="n">
-        <v>1991</v>
+        <v>2006</v>
       </c>
       <c r="C472" t="n">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="D472" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B473" t="n">
-        <v>1992</v>
+        <v>2007</v>
       </c>
       <c r="C473" t="n">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D473" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B474" t="n">
-        <v>1993</v>
+        <v>2008</v>
       </c>
       <c r="C474" t="n">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="D474" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B475" t="n">
-        <v>1994</v>
+        <v>2009</v>
       </c>
       <c r="C475" t="n">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="D475" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B476" t="n">
-        <v>1995</v>
+        <v>2010</v>
       </c>
       <c r="C476" t="n">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="D476" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B477" t="n">
-        <v>1996</v>
+        <v>2011</v>
       </c>
       <c r="C477" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="D477" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B478" t="n">
-        <v>1997</v>
+        <v>2012</v>
       </c>
       <c r="C478" t="n">
-        <v>30</v>
+        <v>123</v>
       </c>
       <c r="D478" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B479" t="n">
-        <v>1998</v>
+        <v>2013</v>
       </c>
       <c r="C479" t="n">
-        <v>130</v>
+        <v>219</v>
       </c>
       <c r="D479" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B480" t="n">
-        <v>1999</v>
+        <v>2014</v>
       </c>
       <c r="C480" t="n">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="D480" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B481" t="n">
-        <v>2000</v>
+        <v>2015</v>
       </c>
       <c r="C481" t="n">
-        <v>146</v>
+        <v>81</v>
       </c>
       <c r="D481" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B482" t="n">
-        <v>2001</v>
+        <v>2016</v>
       </c>
       <c r="C482" t="n">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="D482" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B483" t="n">
-        <v>2002</v>
+        <v>2017</v>
       </c>
       <c r="C483" t="n">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="D483" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B484" t="n">
-        <v>2003</v>
+        <v>2018</v>
       </c>
       <c r="C484" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="D484" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B485" t="n">
-        <v>2004</v>
+        <v>2019</v>
       </c>
       <c r="C485" t="n">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="D485" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B486" t="n">
-        <v>2005</v>
+        <v>2020</v>
       </c>
       <c r="C486" t="n">
-        <v>23</v>
+        <v>165</v>
       </c>
       <c r="D486" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B487" t="n">
-        <v>2006</v>
+        <v>2021</v>
       </c>
       <c r="C487" t="n">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="D487" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B488" t="n">
-        <v>2007</v>
+        <v>2022</v>
       </c>
       <c r="C488" t="n">
-        <v>35</v>
+        <v>168</v>
       </c>
       <c r="D488" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B489" t="n">
-        <v>2008</v>
+        <v>2023</v>
       </c>
       <c r="C489" t="n">
-        <v>27</v>
+        <v>226</v>
       </c>
       <c r="D489" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B490" t="n">
-        <v>2009</v>
+        <v>2024</v>
       </c>
       <c r="C490" t="n">
-        <v>68</v>
+        <v>293</v>
       </c>
       <c r="D490" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B491" t="n">
-        <v>2010</v>
+        <v>2025</v>
       </c>
       <c r="C491" t="n">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="D491" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="492">
@@ -7294,13 +7294,13 @@
         <v>24</v>
       </c>
       <c r="B492" t="n">
-        <v>2011</v>
+        <v>1972</v>
       </c>
       <c r="C492" t="n">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="D492" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="493">
@@ -7308,13 +7308,13 @@
         <v>24</v>
       </c>
       <c r="B493" t="n">
-        <v>2012</v>
+        <v>1973</v>
       </c>
       <c r="C493" t="n">
-        <v>84</v>
+        <v>3</v>
       </c>
       <c r="D493" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="494">
@@ -7322,13 +7322,13 @@
         <v>24</v>
       </c>
       <c r="B494" t="n">
-        <v>2013</v>
+        <v>1974</v>
       </c>
       <c r="C494" t="n">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="D494" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="495">
@@ -7336,13 +7336,13 @@
         <v>24</v>
       </c>
       <c r="B495" t="n">
-        <v>2014</v>
+        <v>1977</v>
       </c>
       <c r="C495" t="n">
-        <v>138</v>
+        <v>5</v>
       </c>
       <c r="D495" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="496">
@@ -7350,13 +7350,13 @@
         <v>24</v>
       </c>
       <c r="B496" t="n">
-        <v>2015</v>
+        <v>1981</v>
       </c>
       <c r="C496" t="n">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="D496" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="497">
@@ -7364,13 +7364,13 @@
         <v>24</v>
       </c>
       <c r="B497" t="n">
-        <v>2016</v>
+        <v>1983</v>
       </c>
       <c r="C497" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="D497" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="498">
@@ -7378,13 +7378,13 @@
         <v>24</v>
       </c>
       <c r="B498" t="n">
-        <v>2017</v>
+        <v>1993</v>
       </c>
       <c r="C498" t="n">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="D498" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="499">
@@ -7392,13 +7392,13 @@
         <v>24</v>
       </c>
       <c r="B499" t="n">
-        <v>2018</v>
+        <v>1994</v>
       </c>
       <c r="C499" t="n">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="D499" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="500">
@@ -7406,13 +7406,13 @@
         <v>24</v>
       </c>
       <c r="B500" t="n">
-        <v>2019</v>
+        <v>1995</v>
       </c>
       <c r="C500" t="n">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="D500" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="501">
@@ -7420,13 +7420,13 @@
         <v>24</v>
       </c>
       <c r="B501" t="n">
-        <v>2020</v>
+        <v>1998</v>
       </c>
       <c r="C501" t="n">
-        <v>193</v>
+        <v>114</v>
       </c>
       <c r="D501" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="502">
@@ -7434,13 +7434,13 @@
         <v>24</v>
       </c>
       <c r="B502" t="n">
-        <v>2021</v>
+        <v>1999</v>
       </c>
       <c r="C502" t="n">
-        <v>124</v>
+        <v>52</v>
       </c>
       <c r="D502" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="503">
@@ -7448,13 +7448,13 @@
         <v>24</v>
       </c>
       <c r="B503" t="n">
-        <v>2022</v>
+        <v>2000</v>
       </c>
       <c r="C503" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D503" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="504">
@@ -7462,13 +7462,13 @@
         <v>24</v>
       </c>
       <c r="B504" t="n">
-        <v>2023</v>
+        <v>2001</v>
       </c>
       <c r="C504" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="D504" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="505">
@@ -7476,13 +7476,13 @@
         <v>24</v>
       </c>
       <c r="B505" t="n">
-        <v>2024</v>
+        <v>2002</v>
       </c>
       <c r="C505" t="n">
-        <v>155</v>
+        <v>13</v>
       </c>
       <c r="D505" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="506">
@@ -7490,12 +7490,306 @@
         <v>24</v>
       </c>
       <c r="B506" t="n">
+        <v>2004</v>
+      </c>
+      <c r="C506" t="n">
+        <v>89</v>
+      </c>
+      <c r="D506" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="s">
+        <v>24</v>
+      </c>
+      <c r="B507" t="n">
+        <v>2005</v>
+      </c>
+      <c r="C507" t="n">
+        <v>53</v>
+      </c>
+      <c r="D507" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="s">
+        <v>24</v>
+      </c>
+      <c r="B508" t="n">
+        <v>2006</v>
+      </c>
+      <c r="C508" t="n">
+        <v>34</v>
+      </c>
+      <c r="D508" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="s">
+        <v>24</v>
+      </c>
+      <c r="B509" t="n">
+        <v>2007</v>
+      </c>
+      <c r="C509" t="n">
+        <v>41</v>
+      </c>
+      <c r="D509" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="s">
+        <v>24</v>
+      </c>
+      <c r="B510" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C510" t="n">
+        <v>19</v>
+      </c>
+      <c r="D510" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="s">
+        <v>24</v>
+      </c>
+      <c r="B511" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C511" t="n">
+        <v>75</v>
+      </c>
+      <c r="D511" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="s">
+        <v>24</v>
+      </c>
+      <c r="B512" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C512" t="n">
+        <v>53</v>
+      </c>
+      <c r="D512" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="s">
+        <v>24</v>
+      </c>
+      <c r="B513" t="n">
+        <v>2011</v>
+      </c>
+      <c r="C513" t="n">
+        <v>117</v>
+      </c>
+      <c r="D513" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="s">
+        <v>24</v>
+      </c>
+      <c r="B514" t="n">
+        <v>2012</v>
+      </c>
+      <c r="C514" t="n">
+        <v>77</v>
+      </c>
+      <c r="D514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="s">
+        <v>24</v>
+      </c>
+      <c r="B515" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C515" t="n">
+        <v>12</v>
+      </c>
+      <c r="D515" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="s">
+        <v>24</v>
+      </c>
+      <c r="B516" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C516" t="n">
+        <v>38</v>
+      </c>
+      <c r="D516" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="s">
+        <v>24</v>
+      </c>
+      <c r="B517" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C517" t="n">
+        <v>58</v>
+      </c>
+      <c r="D517" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="s">
+        <v>24</v>
+      </c>
+      <c r="B518" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C518" t="n">
+        <v>95</v>
+      </c>
+      <c r="D518" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="s">
+        <v>24</v>
+      </c>
+      <c r="B519" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C519" t="n">
+        <v>168</v>
+      </c>
+      <c r="D519" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="s">
+        <v>24</v>
+      </c>
+      <c r="B520" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C520" t="n">
+        <v>121</v>
+      </c>
+      <c r="D520" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="s">
+        <v>24</v>
+      </c>
+      <c r="B521" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C521" t="n">
+        <v>166</v>
+      </c>
+      <c r="D521" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="s">
+        <v>24</v>
+      </c>
+      <c r="B522" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C522" t="n">
+        <v>123</v>
+      </c>
+      <c r="D522" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="s">
+        <v>24</v>
+      </c>
+      <c r="B523" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C523" t="n">
+        <v>60</v>
+      </c>
+      <c r="D523" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="s">
+        <v>24</v>
+      </c>
+      <c r="B524" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C524" t="n">
+        <v>197</v>
+      </c>
+      <c r="D524" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="s">
+        <v>24</v>
+      </c>
+      <c r="B525" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C525" t="n">
+        <v>83</v>
+      </c>
+      <c r="D525" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="s">
+        <v>24</v>
+      </c>
+      <c r="B526" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C526" t="n">
+        <v>132</v>
+      </c>
+      <c r="D526" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="s">
+        <v>24</v>
+      </c>
+      <c r="B527" t="n">
         <v>2025</v>
       </c>
-      <c r="C506" t="n">
-        <v>101</v>
-      </c>
-      <c r="D506" t="s">
+      <c r="C527" t="n">
+        <v>71</v>
+      </c>
+      <c r="D527" t="s">
         <v>10</v>
       </c>
     </row>
